--- a/structure.xlsx
+++ b/structure.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReadMe" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kinds" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KindAxes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sections" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RepeatGroups" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="5" state="visible" r:id="rId5"/>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -481,53 +481,65 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Defines every section, field, and branching rule in the submission form, plus how answers lay out on the generated PDF. Edit this file, then run build_schema.py to regenerate form-schema.json, which the HTML/JS form reads at runtime. The HTML/JS engine itself should not need to change for ordinary revisions — only this spreadsheet does.</t>
+          <t>Defines every section, field, and branching rule in the submission form, plus how answers lay out on the generated PDF. Edit this file, then run build_schema.py to regenerate form-schema.json, which the HTML/JS form reads at runtime.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Sheet: Kinds</t>
+          <t>The kind-axis model (no single 'kind' anymore)</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Five real submission kinds: activity_idea, traditional_review, collaborative_peer_feedback, classroom_testing, approval_review. activity_idea uses its own three sections (idea_contact/idea_context/idea_details) and nothing else — it does not share the detailed authors/objectives/implementation sections used by the other four kinds, which still all show the same content as each other (that finer-grained differentiation is still open).</t>
+          <t>There is no longer one global 'kind' selector. Instead, any ordinary radio/select field can act as a KIND AXIS — its option values become valid entries for every applies_to_kinds / required_for_kinds column in this workbook. Which fields are axes is declared in the KindAxes sheet. There are currently two: 'review_kind' (Traditional Review / Collaborative Peer Feedback / Classroom Testing — a classification tag with no branching effect of its own) and 'readiness' (Activity Idea / Activity for Review / Activity for Testing / Approved Activity — this is what actually drives section/field visibility and requirements). A section or field's applies_to_kinds list can mix values from any axis; at runtime a section/field is visible if the CURRENT value of ANY axis field matches ANY value in the list (or the list is 'all').</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Sheet: Sections</t>
+          <t>Sheet: KindAxes</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>One row per group of questions (maps to the numbered questions in the original PDF). 'applies_to_kinds' = 'all' or a comma-separated list of kind_id values from the Kinds sheet.</t>
+          <t>One row per field_id that acts as a kind axis. The field must be type radio/select/checkbox_group (checkbox_group is unusual as an axis since it's multi-value, but allowed). build_schema.py collects the union of all its options as valid kind values — there is no separate 'Kinds' sheet anymore.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Sheet: Fields</t>
+          <t>Sheet: Sections</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>One row per question/input. 'type' must be one of: text, email, tel, textarea, date, radio, select, checkbox_group, info (info = static instructional text, not an input). 'options' only applies to radio / select / checkbox_group, format: value:Label text|value:Label text  (pipe-separated, colon between value and label). 'required' is one of: TRUE, FALSE, IF_VISIBLE (required only when show_if makes it visible). 'applies_to_kinds' same convention as Sections — a field can narrow further than its section.</t>
+          <t>One row per group of questions. 'applies_to_kinds' = 'all' or a comma-separated list of kind-axis option values (from any axis).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>Sheet: Fields</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>One row per question/input. 'type' must be one of: text, email, tel, textarea, date, radio, select, checkbox_group, info. 'options' only applies to radio/select/checkbox_group, format: value:Label text|value:Label text. 'required' is TRUE, FALSE, or IF_VISIBLE. 'ui_style' is optional — blank for a normal radio/checkbox list, or 'toggle' to render as a row of toggle-buttons (used for the top-level kind-axis fields, matching the Galley Merge Tool's selector style).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>show_if syntax</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Leave blank = always visible (given its section/kind already apply). Supported forms:   field_id == 'value'        (radio/select equals)
   field_id != 'value'        (radio/select not equals)
@@ -535,31 +547,19 @@
   field_id not_in [a,b,c]    (radio/select: value is NOT one of these)
   field_id all [a,b,c]       (checkbox_group: every listed value is checked)
   field_id not_all [a,b,c]   (checkbox_group: at least one listed value is NOT checked)
-field_id must refer to another field defined earlier in the Fields sheet. Example already encoded: q5 shows only when q4 == 'c'; q9 shows when q8 not_all [a,c,d]; q10 shows when q8 not_all [a,b,c,d,e,f,g,h]; the AI-use statement shows when ai_use_level in [substantive,extensive]. Restriction: a field inside a repeat group may only reference another field in the SAME group (same author instance); a field outside any group cannot reference one inside a group (which instance would it mean?).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: RepeatGroups</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Defines a repeatable block of fields — e.g. 'Author' or 'Image' — that the author can click '+ Add another' to duplicate. One row per group. 'order' places the whole group among the other items in its section (same numbering space as Fields.order within that section). min_instances is how many copies show by default and is the structural floor for every kind (e.g. 1 = always at least one author, 0 = starts empty and is optional). max_instances blank = unlimited. 'required_for_kinds' is optional: a comma-separated list of kind_id values (or 'all') for which at least ONE instance becomes mandatory even though min_instances is 0 — this is how 'optional for most kinds, required for one specific kind' is expressed without duplicating the whole group. 'show_if' (optional) hides the entire group unless another field's answer matches — same syntax as Fields.show_if, but the referenced field must be ungrouped (a repeating group's visibility can't depend on one instance of another group).</t>
+field_id must refer to another field defined earlier in the Fields sheet. Restriction: a field inside a repeat group may only reference another field in the SAME group; a field outside any group cannot reference one inside a group.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Fields: group_id column</t>
+          <t>Sheet: RepeatGroups</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Leave blank for an ordinary, non-repeating field. Set to a RepeatGroups.group_id to make this field repeat once per instance of that group — e.g. author_name/author_email/author_phone all set group_id='authors_group'. section_id must still be filled in and must match that group's own section_id (checked by build_schema.py).</t>
+          <t>Defines a repeatable block of fields — e.g. 'Author', 'Image', or 'Learning Objective' — that the author can click '+ Add another' to duplicate. min_instances is the structural floor shown by default (0 = starts empty and optional). required_for_kinds (comma list of kind-axis values, or 'all') makes at least ONE instance mandatory even when min_instances is 0. show_if (optional) hides the entire group unless another field's answer matches — the referenced field must be ungrouped.</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Only meaningful when required=TRUE on a grouped field. TRUE means the requirement applies to instance #1 only — every instance added after that is optional. This is how 'first author required, added authors optional' is expressed without a separate role field. Leave FALSE (or blank) for fields that should stay required (or stay optional) on every instance.</t>
+          <t>Only meaningful when required=TRUE on a grouped field. TRUE means the requirement applies to instance #1 only — every instance added after that is optional. This is how 'first author required, added authors optional' (and 'one learning objective required, more optional') is expressed without a separate role field.</t>
         </is>
       </c>
     </row>
@@ -583,43 +583,19 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Optional. Only meaningful when required=FALSE. A comma-separated list of kind_id values (or 'all') for which this field becomes mandatory even though it's optional for every other kind that can see it. This is how 'optional for most kinds, required for one specific kind' is expressed for an ordinary field (the matching concept for a repeat group is RepeatGroups.required_for_kinds).</t>
+          <t>Optional. Only meaningful when required=FALSE. A comma-separated list of kind-axis values (or 'all') for which this field becomes mandatory even though it's optional for every other active kind combination. Used heavily in the Checklist section, where each document's requirement varies by 'readiness'.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Sheet: PDF_Layout</t>
+          <t>Revision workflow</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Optional per-field overrides for the generated PDF. If a field_id has no row here, the build script infers a sensible default from its type (textarea -&gt; paragraph, radio/checkbox_group -&gt; checklist, text/email/tel/date -&gt; table_row). Only add a row when you need to force a page break before a field, or override the default pdf_format.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Validation</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>build_schema.py checks: every field_id is unique; every section_id a field references exists; every kind_id referenced exists; every show_if references an existing field_id and, where relevant, an option value that field actually defines; every PDF_Layout field_id exists in Fields. It reports ALL problems found, not just the first, and refuses to write form-schema.json until the sheet is clean.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Revision workflow</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>1. Edit structure.xlsx.  2. Run `python build_schema.py structure.xlsx`.  3. Fix anything it flags.  4. Commit both the .xlsx and the regenerated form-schema.json. The HTML page fetches form-schema.json at load time, same pattern as the galley tool's default-file fetching from GitHub Pages.</t>
+          <t>1. Edit structure.xlsx.  2. Run `python build_schema.py structure.xlsx`.  3. Fix anything it flags.  4. Commit both the .xlsx and the regenerated form-schema.json.</t>
         </is>
       </c>
     </row>
@@ -634,126 +610,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="65" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>kind_id</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>display_name</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>notes</t>
+          <t>field_id</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>activity_idea</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>Activity Idea</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>Early-stage idea submission, before a full activity is developed.</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr"/>
+          <t>review_kind</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>traditional_review</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Traditional Review</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Standard written review of a completed activity by PAC writing consultants.</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>collaborative_peer_feedback</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Collaborative Peer Feedback</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Informal peer feedback exchange between authors ahead of formal review.</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>classroom_testing</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Classroom Testing</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Activity is being piloted in a live classroom; submission centers on implementation and testing notes.</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>approval_review</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Approval Review</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Final review for formal approval/designation as a vetted POGIL activity.</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr"/>
+          <t>readiness</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -769,10 +651,10 @@
   <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -808,19 +690,19 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Authors &amp; Activity Identification</t>
+          <t>Authors</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>traditional_review,collaborative_peer_feedback,classroom_testing,approval_review</t>
+          <t>all</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>course_context</t>
+          <t>submission_kind</t>
         </is>
       </c>
       <c r="B3" s="5" t="n">
@@ -828,19 +710,19 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Course Context</t>
+          <t>Submission Kind</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>traditional_review,collaborative_peer_feedback,classroom_testing,approval_review</t>
+          <t>all</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>student_background</t>
+          <t>supplemental</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
@@ -848,19 +730,19 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Student Background</t>
+          <t>Checklist for Submission</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>traditional_review,collaborative_peer_feedback,classroom_testing,approval_review</t>
+          <t>all</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>activity_purpose</t>
+          <t>activity_identification</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
@@ -868,19 +750,19 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Activity Purpose</t>
+          <t>Activity Identification</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>traditional_review,collaborative_peer_feedback,classroom_testing,approval_review</t>
+          <t>activity_for_review,activity_for_testing,approved_activity</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>objectives_goals</t>
+          <t>idea_context</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
@@ -888,19 +770,19 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Learning Objectives &amp; Process Skill Goals</t>
+          <t>Classroom Context</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>traditional_review,collaborative_peer_feedback,classroom_testing,approval_review</t>
+          <t>all</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>course_context</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
@@ -908,19 +790,19 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>POGIL Classroom Implementation</t>
+          <t>Course Context</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>traditional_review,collaborative_peer_feedback,classroom_testing,approval_review</t>
+          <t>activity_for_review,activity_for_testing,approved_activity</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>supplemental</t>
+          <t>student_background</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
@@ -928,19 +810,19 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Supplemental Materials Checklist</t>
+          <t>Student Background</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>traditional_review,collaborative_peer_feedback,classroom_testing,approval_review</t>
+          <t>activity_for_review,activity_for_testing,approved_activity</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>idea_contact</t>
+          <t>objectives_goals</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
@@ -948,19 +830,19 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Contact Information</t>
+          <t>Learning Objectives &amp; Process Skill Goals</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>activity_idea</t>
+          <t>activity_for_review,activity_for_testing,approved_activity</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>idea_context</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
@@ -968,19 +850,19 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Classroom Context</t>
+          <t>POGIL Classroom Implementation</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>activity_idea</t>
+          <t>activity_for_review,activity_for_testing,approved_activity</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>idea_details</t>
+          <t>image_source</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
@@ -988,19 +870,19 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Activity Idea</t>
+          <t>Image Source</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>activity_idea</t>
+          <t>activity_for_review,activity_for_testing,approved_activity</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>image_source</t>
+          <t>ai_use</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
@@ -1008,19 +890,19 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Image Source</t>
+          <t>Generative AI Use</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>traditional_review,collaborative_peer_feedback,classroom_testing,approval_review</t>
+          <t>activity_for_review,activity_for_testing,approved_activity</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>ai_use</t>
+          <t>idea_details</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
@@ -1028,12 +910,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Generative AI Use</t>
+          <t>Activity Idea</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>traditional_review,collaborative_peer_feedback,classroom_testing,approval_review</t>
+          <t>activity_idea</t>
         </is>
       </c>
     </row>
@@ -1048,17 +930,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -1143,41 +1025,165 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>image_source_group</t>
+          <t>content_objectives_group</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>image_source</t>
+          <t>objectives_goals</t>
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Image</t>
+          <t>Learning Objective</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="5" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr">
         <is>
+          <t>+ Add learning objective</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr"/>
+      <c r="I3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>process_skills_group</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>objectives_goals</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Process Skill Goal</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>+ Add process skill goal</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>image_source_group</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>image_source</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
           <t>+ Add image</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>approval_review</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>approved_activity</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>image_authorship_mode == 'specify'</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>idea_content_objectives_group</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>idea_details</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Content Objective</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>+ Add content objective</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>idea_process_skills_group</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>idea_details</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Process Objective</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>+ Add process objective</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1190,22 +1196,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="36" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1274,37 +1281,42 @@
           <t>help_text</t>
         </is>
       </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>ui_style</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>author_name</t>
+          <t>review_kind</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>authors</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>authors_group</t>
-        </is>
-      </c>
+          <t>submission_kind</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr"/>
       <c r="D2" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Kind of Review</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr"/>
+          <t>radio</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>traditional_review:Traditional Review|collaborative_peer_feedback:Collaborative Peer Feedback|classroom_testing:Classroom Testing</t>
+        </is>
+      </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -1312,7 +1324,7 @@
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr"/>
@@ -1323,37 +1335,42 @@
       </c>
       <c r="L2" s="5" t="inlineStr"/>
       <c r="M2" s="5" t="inlineStr"/>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>toggle</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>author_email</t>
+          <t>readiness</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>authors</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>authors_group</t>
-        </is>
-      </c>
+          <t>submission_kind</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr"/>
       <c r="D3" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Activity Readiness</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr"/>
+          <t>radio</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>activity_idea:Activity Idea|activity_for_review:Activity for Review|activity_for_testing:Activity for Testing|approved_activity:Approved Activity</t>
+        </is>
+      </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -1361,7 +1378,7 @@
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr"/>
@@ -1372,37 +1389,42 @@
       </c>
       <c r="L3" s="5" t="inlineStr"/>
       <c r="M3" s="5" t="inlineStr"/>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>toggle</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>author_phone</t>
+          <t>posting_goal</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>authors</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>authors_group</t>
-        </is>
-      </c>
+          <t>submission_kind</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Posting Goal</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>tel</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr"/>
+          <t>checkbox_group</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>intend_to_post:I intend the activity to be posted on the PAC.</t>
+        </is>
+      </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -1421,36 +1443,37 @@
       </c>
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>title_activity</t>
+          <t>posting_goal_intro</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>authors</t>
+          <t>submission_kind</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr"/>
       <c r="D5" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Title of Activity</t>
+          <t>The PAC serves authors with many goals. Some authors want PAC feedback and may not intend to post the activity on the PAC (e.g., activities for Endorsed Collections).</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>info</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr"/>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -1466,35 +1489,36 @@
       </c>
       <c r="L5" s="5" t="inlineStr"/>
       <c r="M5" s="5" t="inlineStr"/>
+      <c r="N5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>discipline</t>
+          <t>submission_form_pdf</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>authors</t>
+          <t>supplemental</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Submission Form (PDF)</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>radio</t>
+          <t>checkbox_group</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>anatomy_physiology:Anatomy &amp; Physiology|astronomy:Astronomy|biology:Biology|chemistry:Chemistry|computer_science:Computer Science|economics:Economics|environmental_science:Environmental Science|exercise_science:Exercise Science|fine_arts:Fine Arts|general:General|general_education:General Education|general_science:General Science|language_arts:Language Arts|mathematics:Mathematics|music:Music|neuroscience:Neuroscience|physics:Physics|psychology:Psychology|statistics:Statistics</t>
+          <t>yes:Submission Form (PDF)</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -1515,33 +1539,38 @@
       </c>
       <c r="L6" s="5" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>topic</t>
+          <t>submission_form_json</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>authors</t>
+          <t>supplemental</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr"/>
       <c r="D7" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Topic</t>
+          <t>Submission Form (JSON)</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr"/>
+          <t>checkbox_group</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>yes:Submission Form (JSON)</t>
+        </is>
+      </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -1560,36 +1589,41 @@
       </c>
       <c r="L7" s="5" t="inlineStr"/>
       <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>idea_name</t>
+          <t>activity_document</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>idea_contact</t>
+          <t>supplemental</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr"/>
       <c r="D8" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr"/>
+          <t>checkbox_group</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>yes:Activity</t>
+        </is>
+      </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -1597,7 +1631,11 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>activity_for_review,activity_for_testing,approved_activity</t>
+        </is>
+      </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
           <t>all</t>
@@ -1605,36 +1643,41 @@
       </c>
       <c r="L8" s="5" t="inlineStr"/>
       <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>idea_email</t>
+          <t>toc_graphic</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>idea_contact</t>
+          <t>supplemental</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr"/>
       <c r="D9" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>TOC Graphic</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr"/>
+          <t>checkbox_group</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>yes:TOC Graphic</t>
+        </is>
+      </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -1642,7 +1685,11 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>activity_for_review,activity_for_testing,approved_activity</t>
+        </is>
+      </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
           <t>all</t>
@@ -1650,25 +1697,26 @@
       </c>
       <c r="L9" s="5" t="inlineStr"/>
       <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>idea_activity_type</t>
+          <t>answer_key</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>idea_context</t>
+          <t>supplemental</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr"/>
       <c r="D10" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Activity Type (choose as many or as few as appropriate)</t>
+          <t>Student Answers (Key)</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -1678,7 +1726,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>learning_cycle:Learning Cycle|application:Application|swh_lab:Science Writing Heuristic Lab|pogil_lab:POGIL Lab|other:Other</t>
+          <t>yes:Student Answers (Key)</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -1691,7 +1739,11 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>activity_for_review,activity_for_testing,approved_activity</t>
+        </is>
+      </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
           <t>all</t>
@@ -1699,36 +1751,41 @@
       </c>
       <c r="L10" s="5" t="inlineStr"/>
       <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>idea_activity_type_other</t>
+          <t>facilitation_guide</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>idea_context</t>
+          <t>supplemental</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr"/>
       <c r="D11" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>If Other, please specify</t>
+          <t>Facilitation Guide</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr"/>
+          <t>checkbox_group</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>yes:Facilitation Guide</t>
+        </is>
+      </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>IF_VISIBLE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -1736,57 +1793,58 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>activity_for_testing,approved_activity</t>
+        </is>
+      </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>idea_activity_type all [other]</t>
-        </is>
-      </c>
+      <c r="L11" s="5" t="inlineStr"/>
       <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>idea_discipline</t>
+          <t>author_name</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>idea_context</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr"/>
+          <t>authors</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>authors_group</t>
+        </is>
+      </c>
       <c r="D12" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>radio</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>anatomy_physiology:Anatomy &amp; Physiology|astronomy:Astronomy|biology:Biology|chemistry:Chemistry|computer_science:Computer Science|economics:Economics|environmental_science:Environmental Science|exercise_science:Exercise Science|fine_arts:Fine Arts|general:General|general_education:General Education|general_science:General Science|language_arts:Language Arts|mathematics:Mathematics|music:Music|neuroscience:Neuroscience|physics:Physics|psychology:Psychology|statistics:Statistics</t>
-        </is>
-      </c>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr"/>
@@ -1797,45 +1855,46 @@
       </c>
       <c r="L12" s="5" t="inlineStr"/>
       <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>idea_setting</t>
+          <t>author_email</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>idea_context</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr"/>
+          <t>authors</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>authors_group</t>
+        </is>
+      </c>
       <c r="D13" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>checkbox_group</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>laboratory:Laboratory|classroom:Classroom</t>
-        </is>
-      </c>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr"/>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr"/>
@@ -1846,30 +1905,35 @@
       </c>
       <c r="L13" s="5" t="inlineStr"/>
       <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>idea_course</t>
+          <t>author_phone</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>idea_context</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr"/>
+          <t>authors</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>authors_group</t>
+        </is>
+      </c>
       <c r="D14" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Course (e.g., Physical Chemistry, General Biology)</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>tel</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr"/>
@@ -1891,40 +1955,37 @@
       </c>
       <c r="L14" s="5" t="inlineStr"/>
       <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>idea_level</t>
+          <t>title_activity</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>idea_context</t>
+          <t>activity_identification</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr"/>
       <c r="D15" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Level</t>
+          <t>Title of Activity</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>checkbox_group</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>k5:K-5|middle:Middle School|high:High School|undergrad:Undergraduate|grad:Graduate</t>
-        </is>
-      </c>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr"/>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -1940,33 +2001,38 @@
       </c>
       <c r="L15" s="5" t="inlineStr"/>
       <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>idea_title</t>
+          <t>discipline</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>idea_details</t>
+          <t>activity_identification</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Discipline</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr"/>
+          <t>select</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>anatomy_physiology:Anatomy &amp; Physiology|astronomy:Astronomy|biology:Biology|chemistry:Chemistry|computer_science:Computer Science|economics:Economics|environmental_science:Environmental Science|exercise_science:Exercise Science|fine_arts:Fine Arts|general:General|general_education:General Education|general_science:General Science|language_arts:Language Arts|mathematics:Mathematics|music:Music|neuroscience:Neuroscience|physics:Physics|psychology:Psychology|statistics:Statistics</t>
+        </is>
+      </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -1985,25 +2051,26 @@
       </c>
       <c r="L16" s="5" t="inlineStr"/>
       <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>idea_content_obj_a</t>
+          <t>topic</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>idea_details</t>
+          <t>activity_identification</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Content Objective (a)</t>
+          <t>Topic</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -2030,33 +2097,38 @@
       </c>
       <c r="L17" s="5" t="inlineStr"/>
       <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>idea_content_obj_b</t>
+          <t>idea_activity_type</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>idea_details</t>
+          <t>idea_context</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr"/>
       <c r="D18" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Content Objective (b)</t>
+          <t>Activity Type (choose as many or as few as appropriate)</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr"/>
+          <t>checkbox_group</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>learning_cycle:Learning Cycle|application:Application|swh_lab:Science Writing Heuristic Lab|pogil_lab:POGIL Lab|other:Other</t>
+        </is>
+      </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -2075,25 +2147,26 @@
       </c>
       <c r="L18" s="5" t="inlineStr"/>
       <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>idea_content_obj_c</t>
+          <t>idea_activity_type_other</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>idea_details</t>
+          <t>idea_context</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr"/>
       <c r="D19" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Content Objective (c)</t>
+          <t>If Other, please specify</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -2104,7 +2177,7 @@
       <c r="G19" s="5" t="inlineStr"/>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>IF_VISIBLE</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -2118,38 +2191,47 @@
           <t>all</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>idea_activity_type all [other]</t>
+        </is>
+      </c>
       <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>idea_process_obj_a</t>
+          <t>idea_discipline</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>idea_details</t>
+          <t>idea_context</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr"/>
       <c r="D20" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Process Objective (a)</t>
+          <t>Discipline</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr"/>
+          <t>select</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>anatomy_physiology:Anatomy &amp; Physiology|astronomy:Astronomy|biology:Biology|chemistry:Chemistry|computer_science:Computer Science|economics:Economics|environmental_science:Environmental Science|exercise_science:Exercise Science|fine_arts:Fine Arts|general:General|general_education:General Education|general_science:General Science|language_arts:Language Arts|mathematics:Mathematics|music:Music|neuroscience:Neuroscience|physics:Physics|psychology:Psychology|statistics:Statistics</t>
+        </is>
+      </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -2165,33 +2247,38 @@
       </c>
       <c r="L20" s="5" t="inlineStr"/>
       <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>idea_process_obj_b</t>
+          <t>idea_setting</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>idea_details</t>
+          <t>idea_context</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr"/>
       <c r="D21" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Process Objective (b)</t>
+          <t>Setting</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr"/>
+          <t>checkbox_group</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>laboratory:Laboratory|classroom:Classroom</t>
+        </is>
+      </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -2210,25 +2297,26 @@
       </c>
       <c r="L21" s="5" t="inlineStr"/>
       <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>idea_process_obj_c</t>
+          <t>idea_course</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>idea_details</t>
+          <t>idea_context</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr"/>
       <c r="D22" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Process Objective (c)</t>
+          <t>Course (e.g., Physical Chemistry, General Biology)</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -2255,36 +2343,41 @@
       </c>
       <c r="L22" s="5" t="inlineStr"/>
       <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>idea_description</t>
+          <t>idea_level</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>idea_details</t>
+          <t>idea_context</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr"/>
       <c r="D23" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Level</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>textarea</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr"/>
+          <t>checkbox_group</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>k5:K-5|middle:Middle School|high:High School|undergrad_intro:Undergraduate (introductory-level)|undergrad_upper:Undergraduate (upper-level)|grad:Graduate</t>
+        </is>
+      </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -2299,21 +2392,18 @@
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr"/>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>250 words or less</t>
-        </is>
-      </c>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>image_authorship_mode</t>
+          <t>idea_title</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>image_source</t>
+          <t>idea_details</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr"/>
@@ -2322,22 +2412,18 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Image Authorship</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>radio</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>blanket_author:I am the author of all images in the activity|specify:Specify image authorship</t>
-        </is>
-      </c>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr"/>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -2345,11 +2431,7 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>approval_review</t>
-        </is>
-      </c>
+      <c r="J24" s="5" t="inlineStr"/>
       <c r="K24" s="5" t="inlineStr">
         <is>
           <t>all</t>
@@ -2357,21 +2439,22 @@
       </c>
       <c r="L24" s="5" t="inlineStr"/>
       <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>image_description</t>
+          <t>idea_objective_text</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>image_source</t>
+          <t>idea_details</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>image_source_group</t>
+          <t>idea_content_objectives_group</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -2379,7 +2462,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Image</t>
+          <t>Content Objective</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -2395,7 +2478,7 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr"/>
@@ -2405,46 +2488,39 @@
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr"/>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>A short description or filename identifying the image.</t>
-        </is>
-      </c>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>image_role</t>
+          <t>idea_skill_text</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>image_source</t>
+          <t>idea_details</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>image_source_group</t>
+          <t>idea_process_skills_group</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Image Credit</t>
+          <t>Process Objective</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>radio</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>author:I am the author of this image|source:Image source</t>
-        </is>
-      </c>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -2452,7 +2528,7 @@
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr"/>
@@ -2463,40 +2539,37 @@
       </c>
       <c r="L26" s="5" t="inlineStr"/>
       <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>image_source_detail</t>
+          <t>idea_description</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>image_source</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>image_source_group</t>
-        </is>
-      </c>
+          <t>idea_details</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr"/>
       <c r="D27" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Source (URL or description)</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>textarea</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>IF_VISIBLE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -2510,22 +2583,23 @@
           <t>all</t>
         </is>
       </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>image_role == 'source'</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>250 words or less</t>
+        </is>
+      </c>
+      <c r="N27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>ai_use_intro</t>
+          <t>image_authorship_mode</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>ai_use</t>
+          <t>image_source</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr"/>
@@ -2534,15 +2608,19 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Generative AI can support activity development, but it should support — not replace — your own instructional design, disciplinary judgment, and critical thinking. As AI plays a larger role in producing content, the expectation for your review, verification, and disclosure increases. Select the level that best describes how AI was used in developing this activity. Routine or Supportive use covers things like brainstorming, wording suggestions, grammar/clarity checks, or formatting on work you conceived and directed. Substantive Developmental use means AI helped develop or revise real components — drafting objectives, generating questions from your objectives, building datasets, or suggesting scaffolding — requiring your careful review and verification. Extensive Generative use means AI generated substantial portions of the activity (e.g. a full question sequence or draft) with limited initial input from you.</t>
+          <t>Image Authorship</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>info</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr"/>
+          <t>radio</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>blanket_author:I am the author of all images in the activity|specify:Specify image authorship</t>
+        </is>
+      </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -2553,7 +2631,11 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="J28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>approved_activity</t>
+        </is>
+      </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
           <t>all</t>
@@ -2561,37 +2643,38 @@
       </c>
       <c r="L28" s="5" t="inlineStr"/>
       <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>ai_use_level</t>
+          <t>image_description</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>ai_use</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr"/>
+          <t>image_source</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>image_source_group</t>
+        </is>
+      </c>
       <c r="D29" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Level of AI use</t>
+          <t>Image</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>radio</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>no_ai:No AI was used|routine:Routine or Supportive use|substantive:Substantive development use|extensive:Extensive generative AI use</t>
-        </is>
-      </c>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -2609,37 +2692,50 @@
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr"/>
-      <c r="M29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>A short description or filename identifying the image.</t>
+        </is>
+      </c>
+      <c r="N29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>ai_responsibility_statement</t>
+          <t>image_role</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>ai_use</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr"/>
+          <t>image_source</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>image_source_group</t>
+        </is>
+      </c>
       <c r="D30" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Author Responsibility Statement: By selecting this level, I affirm that I have critically reviewed, verified, and substantively revised any AI-assisted content in this activity. My own intellectual and creative contribution to this activity is substantial enough that I hold copyright in the final work, and I accept full responsibility for the accuracy, originality, instructional design, and POGIL alignment of the submitted activity.</t>
+          <t>Image Credit</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>info</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr"/>
+          <t>radio</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>author:I am the author of this image|source:I am not the author of this image. Image source:</t>
+        </is>
+      </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -2653,43 +2749,40 @@
           <t>all</t>
         </is>
       </c>
-      <c r="L30" s="5" t="inlineStr">
-        <is>
-          <t>ai_use_level in [substantive,extensive]</t>
-        </is>
-      </c>
+      <c r="L30" s="5" t="inlineStr"/>
       <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>ai_responsibility_checkbox</t>
+          <t>image_source_detail</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>ai_use</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr"/>
+          <t>image_source</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>image_source_group</t>
+        </is>
+      </c>
       <c r="D31" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Affirmation</t>
+          <t>Source (URL or description)</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>checkbox_group</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>affirmed:I affirm the statement above.</t>
-        </is>
-      </c>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr">
         <is>
           <t>IF_VISIBLE</t>
@@ -2708,15 +2801,16 @@
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>ai_use_level in [substantive,extensive]</t>
+          <t>image_role == 'source'</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>ai_use_description</t>
+          <t>ai_use_intro</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -2726,22 +2820,22 @@
       </c>
       <c r="C32" s="5" t="inlineStr"/>
       <c r="D32" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Briefly describe how AI was used in developing this activity.</t>
+          <t>Generative AI can support activity development, but it should support — not replace — your own instructional design, disciplinary judgment, and critical thinking. As AI plays a larger role in producing content, the expectation for your review, verification, and disclosure increases. Select the level that best describes how AI was used in developing this activity. Routine or Supportive use covers things like brainstorming, wording suggestions, grammar/clarity checks, or formatting on work you conceived and directed. Substantive Developmental use means AI helped develop or revise real components — drafting objectives, generating questions from your objectives, building datasets, or suggesting scaffolding — requiring your careful review and verification. Extensive Generative use means AI generated substantial portions of the activity (e.g. a full question sequence or draft) with limited initial input from you.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>textarea</t>
+          <t>info</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr"/>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>IF_VISIBLE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
@@ -2755,39 +2849,40 @@
           <t>all</t>
         </is>
       </c>
-      <c r="L32" s="5" t="inlineStr">
-        <is>
-          <t>ai_use_level in [substantive,extensive]</t>
-        </is>
-      </c>
+      <c r="L32" s="5" t="inlineStr"/>
       <c r="M32" s="5" t="inlineStr"/>
+      <c r="N32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>q1a</t>
+          <t>ai_use_level</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>course_context</t>
+          <t>ai_use</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr"/>
       <c r="D33" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>The student population for your course.</t>
+          <t>Level of AI use</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>textarea</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr"/>
+          <t>radio</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>no_ai:No AI was used|routine:Routine or Supportive use|substantive:Substantive development use|extensive:Extensive generative AI use</t>
+        </is>
+      </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -2806,36 +2901,37 @@
       </c>
       <c r="L33" s="5" t="inlineStr"/>
       <c r="M33" s="5" t="inlineStr"/>
+      <c r="N33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>q1b</t>
+          <t>ai_responsibility_statement</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>course_context</t>
+          <t>ai_use</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr"/>
       <c r="D34" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>How the course fits into your departmental curriculum.</t>
+          <t>Author Responsibility Statement: By selecting this level, I affirm that I have critically reviewed, verified, and substantively revised any AI-assisted content in this activity. My own intellectual and creative contribution to this activity is substantial enough that I hold copyright in the final work, and I accept full responsibility for the accuracy, originality, instructional design, and POGIL alignment of the submitted activity.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>textarea</t>
+          <t>info</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr"/>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -2849,38 +2945,47 @@
           <t>all</t>
         </is>
       </c>
-      <c r="L34" s="5" t="inlineStr"/>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>ai_use_level in [substantive,extensive]</t>
+        </is>
+      </c>
       <c r="M34" s="5" t="inlineStr"/>
+      <c r="N34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>q1c</t>
+          <t>ai_responsibility_checkbox</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>course_context</t>
+          <t>ai_use</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr"/>
       <c r="D35" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>The course setting (room description, class size, frequency and length of meeting times, etc.).</t>
+          <t>Affirmation</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>textarea</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr"/>
+          <t>checkbox_group</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>affirmed:I affirm the statement above.</t>
+        </is>
+      </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>IF_VISIBLE</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
@@ -2894,42 +2999,43 @@
           <t>all</t>
         </is>
       </c>
-      <c r="L35" s="5" t="inlineStr"/>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>ai_use_level in [substantive,extensive]</t>
+        </is>
+      </c>
       <c r="M35" s="5" t="inlineStr"/>
+      <c r="N35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>q2</t>
+          <t>ai_use_description</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>student_background</t>
+          <t>ai_use</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr"/>
       <c r="D36" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Have students used and/or reviewed this activity?</t>
+          <t>Briefly describe how AI was used in developing this activity.</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>radio</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>yes:Yes|no:No</t>
-        </is>
-      </c>
+          <t>textarea</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr"/>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>IF_VISIBLE</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
@@ -2943,35 +3049,44 @@
           <t>all</t>
         </is>
       </c>
-      <c r="L36" s="5" t="inlineStr"/>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>ai_use_level in [substantive,extensive]</t>
+        </is>
+      </c>
       <c r="M36" s="5" t="inlineStr"/>
+      <c r="N36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>q3a</t>
+          <t>course_level</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>student_background</t>
+          <t>course_context</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr"/>
       <c r="D37" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Key knowledge students should have as a prerequisite.</t>
+          <t>Course Level</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>textarea</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr"/>
+          <t>radio</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>high_school:High school|undergrad_intro:Undergraduate course (introductory-level)|undergrad_upper:Undergraduate course (upper-level)|grad:Graduate course</t>
+        </is>
+      </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -2990,25 +3105,26 @@
       </c>
       <c r="L37" s="5" t="inlineStr"/>
       <c r="M37" s="5" t="inlineStr"/>
+      <c r="N37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>q3b</t>
+          <t>q1a</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>student_background</t>
+          <t>course_context</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr"/>
       <c r="D38" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Knowledge students are not expected to have prior to activity.</t>
+          <t>The student population for your course.</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -3035,37 +3151,34 @@
       </c>
       <c r="L38" s="5" t="inlineStr"/>
       <c r="M38" s="5" t="inlineStr"/>
+      <c r="N38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>q4</t>
+          <t>q1b</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>activity_purpose</t>
+          <t>course_context</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr"/>
       <c r="D39" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>This activity is primarily designed:</t>
+          <t>How the course fits into your departmental curriculum.</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>radio</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>a:To develop content knowledge through a Learning Cycle structure.|b:To deepen or refine understanding through application of relevant process skills.|c:For a different purpose than a or b.</t>
-        </is>
-      </c>
+          <t>textarea</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr"/>
       <c r="H39" s="5" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -3083,30 +3196,27 @@
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr"/>
-      <c r="M39" s="5" t="inlineStr">
-        <is>
-          <t>For assistance, refer to the Guide for POGIL Activity Submission.</t>
-        </is>
-      </c>
+      <c r="M39" s="5" t="inlineStr"/>
+      <c r="N39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>q5</t>
+          <t>q1c</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>activity_purpose</t>
+          <t>course_context</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr"/>
       <c r="D40" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>If you checked (c), provide details explaining the primary purpose of the activity.</t>
+          <t>The course setting (room description, class size, frequency and length of meeting times, etc.).</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -3117,7 +3227,7 @@
       <c r="G40" s="5" t="inlineStr"/>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>IF_VISIBLE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
@@ -3131,22 +3241,19 @@
           <t>all</t>
         </is>
       </c>
-      <c r="L40" s="5" t="inlineStr">
-        <is>
-          <t>q4 == 'c'</t>
-        </is>
-      </c>
+      <c r="L40" s="5" t="inlineStr"/>
       <c r="M40" s="5" t="inlineStr"/>
+      <c r="N40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>q6a</t>
+          <t>q2</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>objectives_goals</t>
+          <t>student_background</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr"/>
@@ -3155,15 +3262,19 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Content Learning Objective (a)</t>
+          <t>Have students used and/or reviewed this activity?</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr"/>
+          <t>radio</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>yes:Yes|no:No</t>
+        </is>
+      </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -3181,21 +3292,18 @@
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr"/>
-      <c r="M41" s="5" t="inlineStr">
-        <is>
-          <t>No more than three key learning objectives.</t>
-        </is>
-      </c>
+      <c r="M41" s="5" t="inlineStr"/>
+      <c r="N41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>q6b</t>
+          <t>q3a</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>objectives_goals</t>
+          <t>student_background</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr"/>
@@ -3204,18 +3312,18 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Content Learning Objective (b)</t>
+          <t>Key knowledge students should have as a prerequisite.</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>textarea</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
@@ -3231,16 +3339,17 @@
       </c>
       <c r="L42" s="5" t="inlineStr"/>
       <c r="M42" s="5" t="inlineStr"/>
+      <c r="N42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>q6c</t>
+          <t>q3b</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>objectives_goals</t>
+          <t>student_background</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr"/>
@@ -3249,18 +3358,18 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Content Learning Objective (c)</t>
+          <t>Knowledge students are not expected to have prior to activity.</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>textarea</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr"/>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
@@ -3276,33 +3385,38 @@
       </c>
       <c r="L43" s="5" t="inlineStr"/>
       <c r="M43" s="5" t="inlineStr"/>
+      <c r="N43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>q7a</t>
+          <t>q8</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>objectives_goals</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr"/>
       <c r="D44" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>Process Skill Goal (a)</t>
+          <t>Is this activity intended for use with the eight characteristics of the Basic POGIL Classroom Implementation? Check all that apply.</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr"/>
+          <t>checkbox_group</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>a:Students are expected to work cooperatively, generally in groups of three or four.|b:The activity is a POGIL activity, specifically designed for POGIL implementation.|c:The students work on the activity during class time with a facilitator present.|d:The dominant mode of instruction is not lecture or instructor-centered; the instructor serves predominantly as a facilitator of student learning.|e:Students have assigned roles within their groups.|f:The activity is designed to be the first introduction to the topic or specific content.|g:The students are not expected to have worked on any part of the activity prior to class meeting time.|h:Groups are expected to complete all of the Critical Thinking Questions (or equivalently designated questions) during class, but they are not expected to work on any of the Exercises or Problems.</t>
+        </is>
+      </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -3320,41 +3434,38 @@
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr"/>
-      <c r="M44" s="5" t="inlineStr">
-        <is>
-          <t>One or two process skills.</t>
-        </is>
-      </c>
+      <c r="M44" s="5" t="inlineStr"/>
+      <c r="N44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>q7b</t>
+          <t>q9</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>objectives_goals</t>
+          <t>implementation</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr"/>
       <c r="D45" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Process Skill Goal (b)</t>
+          <t>If you did not check boxes (a), (c), and (d) above, submit an implementation plan describing specifically how you implement this activity within your classroom.</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>textarea</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr"/>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>IF_VISIBLE</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
@@ -3368,13 +3479,18 @@
           <t>all</t>
         </is>
       </c>
-      <c r="L45" s="5" t="inlineStr"/>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>q8 not_all [a,c,d]</t>
+        </is>
+      </c>
       <c r="M45" s="5" t="inlineStr"/>
+      <c r="N45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>q8</t>
+          <t>q10</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -3384,26 +3500,22 @@
       </c>
       <c r="C46" s="5" t="inlineStr"/>
       <c r="D46" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Is this activity intended for use with the eight characteristics of the Basic POGIL Classroom Implementation? Check all that apply.</t>
+          <t>For those boxes above that you did not check, briefly describe how and/or why your activity is not implemented in that way.</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>checkbox_group</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>a:Students are expected to work cooperatively, generally in groups of three or four.|b:The activity is a POGIL activity, specifically designed for POGIL implementation.|c:The students work on the activity during class time with a facilitator present.|d:The dominant mode of instruction is not lecture or instructor-centered; the instructor serves predominantly as a facilitator of student learning.|e:Students have assigned roles within their groups.|f:The activity is designed to be the first introduction to the topic or specific content.|g:The students are not expected to have worked on any part of the activity prior to class meeting time.|h:Groups are expected to complete all of the Critical Thinking Questions (or equivalently designated questions) during class, but they are not expected to work on any of the Exercises or Problems.</t>
-        </is>
-      </c>
+          <t>textarea</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>IF_VISIBLE</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
@@ -3417,13 +3529,18 @@
           <t>all</t>
         </is>
       </c>
-      <c r="L46" s="5" t="inlineStr"/>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>q8 not_all [a,b,c,d,e,f,g,h]</t>
+        </is>
+      </c>
       <c r="M46" s="5" t="inlineStr"/>
+      <c r="N46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>q9</t>
+          <t>approval_testing_evidence</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -3433,11 +3550,11 @@
       </c>
       <c r="C47" s="5" t="inlineStr"/>
       <c r="D47" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>If you did not check boxes (a), (c), and (d) above, submit an implementation plan describing specifically how you implement this activity within your classroom.</t>
+          <t>Provide evidence that this activity has been tested in the classroom, and describe how it has been revised based on that feedback.</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
@@ -3448,7 +3565,7 @@
       <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>IF_VISIBLE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
@@ -3459,207 +3576,16 @@
       <c r="J47" s="5" t="inlineStr"/>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="L47" s="5" t="inlineStr">
-        <is>
-          <t>q8 not_all [a,c,d]</t>
-        </is>
-      </c>
-      <c r="M47" s="5" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>q10</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>implementation</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr"/>
-      <c r="D48" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>For those boxes above that you did not check, briefly describe how and/or why your activity is not implemented in that way.</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>textarea</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr"/>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>IF_VISIBLE</t>
-        </is>
-      </c>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="J48" s="5" t="inlineStr"/>
-      <c r="K48" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="L48" s="5" t="inlineStr">
-        <is>
-          <t>q8 not_all [a,b,c,d,e,f,g,h]</t>
-        </is>
-      </c>
-      <c r="M48" s="5" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>approval_testing_evidence</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>implementation</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr"/>
-      <c r="D49" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>Provide evidence that this activity has been tested in the classroom, and describe how it has been revised based on that feedback.</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>textarea</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr"/>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="I49" s="5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="J49" s="5" t="inlineStr"/>
-      <c r="K49" s="5" t="inlineStr">
-        <is>
-          <t>approval_review</t>
-        </is>
-      </c>
-      <c r="L49" s="5" t="inlineStr"/>
-      <c r="M49" s="5" t="inlineStr">
+          <t>approved_activity</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr"/>
+      <c r="M47" s="5" t="inlineStr">
         <is>
           <t>Include student performance data, instructor observations, or facilitator notes as applicable.</t>
         </is>
       </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>supp_note</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>supplemental</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr"/>
-      <c r="D50" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>If there are special aspects of implementation important to accomplishing the content or process goals of your activity, provide an Implementation Plan describing them. Please include a set of answers with your submission so writing consultants understand the expected level of student response.</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>info</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr"/>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="I50" s="5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="J50" s="5" t="inlineStr"/>
-      <c r="K50" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="L50" s="5" t="inlineStr"/>
-      <c r="M50" s="5" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>checklist</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>supplemental</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr"/>
-      <c r="D51" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>Check List for Submission</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>checkbox_group</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr">
-        <is>
-          <t>classroom_activity:Classroom Activity|submission_form:POGIL Activity Submission Form (this form)|answer_key:Activity Answer Key|implementation_plan:Implementation Plan (optional; see above and question 9)</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="I51" s="5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="J51" s="5" t="inlineStr"/>
-      <c r="K51" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="L51" s="5" t="inlineStr"/>
-      <c r="M51" s="5" t="inlineStr"/>
+      <c r="N47" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3672,7 +3598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3706,7 +3632,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>q2</t>
+          <t>submission_form_pdf</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -3717,43 +3643,7 @@
       <c r="C2" s="5" t="inlineStr"/>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Mirrors original form's page break before 'Have students used...' section.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>q4</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr"/>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Mirrors original form's page 2 start.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>checklist</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Mirrors original form's page 3 start.</t>
+          <t>Checklist starts its own page.</t>
         </is>
       </c>
     </row>

--- a/structure.xlsx
+++ b/structure.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -493,7 +493,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>There is no longer one global 'kind' selector. Instead, any ordinary radio/select field can act as a KIND AXIS — its option values become valid entries for every applies_to_kinds / required_for_kinds column in this workbook. Which fields are axes is declared in the KindAxes sheet. There are currently two: 'review_kind' (Traditional Review / Collaborative Peer Feedback / Classroom Testing — a classification tag with no branching effect of its own) and 'readiness' (Activity Idea / Activity for Review / Activity for Testing / Approved Activity — this is what actually drives section/field visibility and requirements). A section or field's applies_to_kinds list can mix values from any axis; at runtime a section/field is visible if the CURRENT value of ANY axis field matches ANY value in the list (or the list is 'all').</t>
+          <t>There is no longer one global 'kind' selector. Instead, any ordinary radio/select field can act as a KIND AXIS — its option values become valid entries for every applies_to_kinds / required_for_kinds column in this workbook. Which fields are axes is declared in the KindAxes sheet. There are currently two: 'review_kind' (Traditional Review / Collaborative Activity Feedback / Classroom Testing — a classification tag with no branching effect of its own) and 'readiness' (Activity Idea / Activity for Review / Activity for Testing / Approved Activity — this is what actually drives section/field visibility and requirements). A section or field's applies_to_kinds list can mix values from any axis; at runtime a section/field is visible if the CURRENT value of ANY axis field matches ANY value in the list (or the list is 'all').</t>
         </is>
       </c>
     </row>
@@ -554,46 +554,58 @@
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Sheet: RepeatGroups</t>
+          <t>Fields: disabled_if column</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Defines a repeatable block of fields — e.g. 'Author', 'Image', or 'Learning Objective' — that the author can click '+ Add another' to duplicate. min_instances is the structural floor shown by default (0 = starts empty and optional). required_for_kinds (comma list of kind-axis values, or 'all') makes at least ONE instance mandatory even when min_instances is 0. show_if (optional) hides the entire group unless another field's answer matches — the referenced field must be ungrouped.</t>
+          <t>Optional. Same syntax and scoping rules as show_if, but the field stays VISIBLE and is instead rendered non-interactive (greyed out, un-clickable) when the condition is true, rather than being hidden. Used for 'Kind of Review' — it's disabled while Activity Readiness is 'Activity Idea', since review kind doesn't apply yet at the idea stage, but hiding it entirely would be more jarring than just greying it out in place.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Fields: required_first_only column</t>
+          <t>Sheet: RepeatGroups</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Only meaningful when required=TRUE on a grouped field. TRUE means the requirement applies to instance #1 only — every instance added after that is optional. This is how 'first author required, added authors optional' (and 'one learning objective required, more optional') is expressed without a separate role field.</t>
+          <t>Defines a repeatable block of fields — e.g. 'Author', 'Image', or 'Learning Objective' — that the author can click '+ Add another' to duplicate. min_instances is the structural floor shown by default (0 = starts empty and optional). required_for_kinds (comma list of kind-axis values, or 'all') makes at least ONE instance mandatory even when min_instances is 0. show_if (optional) hides the entire group unless another field's answer matches — the referenced field must be ungrouped.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Fields: required_for_kinds column</t>
+          <t>Fields: required_first_only column</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Optional. Only meaningful when required=FALSE. A comma-separated list of kind-axis values (or 'all') for which this field becomes mandatory even though it's optional for every other active kind combination. Used heavily in the Checklist section, where each document's requirement varies by 'readiness'.</t>
+          <t>Only meaningful when required=TRUE on a grouped field. TRUE means the requirement applies to instance #1 only — every instance added after that is optional. This is how 'first author required, added authors optional' (and 'one learning objective required, more optional') is expressed without a separate role field.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>Fields: required_for_kinds column</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Optional. Only meaningful when required=FALSE. A comma-separated list of kind-axis values (or 'all') for which this field becomes mandatory even though it's optional for every other active kind combination. Used heavily in the Checklist section, where each document's requirement varies by 'readiness'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>Revision workflow</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>1. Edit structure.xlsx.  2. Run `python build_schema.py structure.xlsx`.  3. Fix anything it flags.  4. Commit both the .xlsx and the regenerated form-schema.json.</t>
         </is>
@@ -648,7 +660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -770,7 +782,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Classroom Context</t>
+          <t>Activity Type and Classroom Context</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -782,15 +794,15 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>course_context</t>
+          <t>student_background</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Course Context</t>
+          <t>Student Background</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -802,15 +814,15 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>student_background</t>
+          <t>objectives_goals</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Student Background</t>
+          <t>Learning Objectives &amp; Process Skill Goals</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -822,35 +834,35 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>objectives_goals</t>
+          <t>approval_evidence</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Learning Objectives &amp; Process Skill Goals</t>
+          <t>Classroom Testing &amp; Revision</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>activity_for_review,activity_for_testing,approved_activity</t>
+          <t>approved_activity</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>implementation</t>
+          <t>image_source</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>POGIL Classroom Implementation</t>
+          <t>Image Source</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -862,15 +874,15 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>image_source</t>
+          <t>ai_use</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Image Source</t>
+          <t>Generative AI Use</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -882,38 +894,18 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>ai_use</t>
+          <t>idea_details</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Generative AI Use</t>
+          <t>Activity Idea</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>activity_for_review,activity_for_testing,approved_activity</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>idea_details</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Activity Idea</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>activity_idea</t>
         </is>
@@ -1196,7 +1188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1213,6 +1205,7 @@
     <col width="28" customWidth="1" min="12" max="12"/>
     <col width="36" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1286,11 +1279,16 @@
           <t>ui_style</t>
         </is>
       </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>disabled_if</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>review_kind</t>
+          <t>readiness</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -1304,7 +1302,7 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Kind of Review</t>
+          <t>Activity Readiness</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
@@ -1314,7 +1312,7 @@
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>traditional_review:Traditional Review|collaborative_peer_feedback:Collaborative Peer Feedback|classroom_testing:Classroom Testing</t>
+          <t>activity_idea:Activity Idea|activity_for_review:Activity for Review|activity_for_testing:Activity for Testing|approved_activity:Approved Activity</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
@@ -1340,11 +1338,12 @@
           <t>toggle</t>
         </is>
       </c>
+      <c r="O2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>readiness</t>
+          <t>review_kind</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -1358,7 +1357,7 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Activity Readiness</t>
+          <t>Kind of Review</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -1368,7 +1367,7 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>activity_idea:Activity Idea|activity_for_review:Activity for Review|activity_for_testing:Activity for Testing|approved_activity:Approved Activity</t>
+          <t>traditional_review:Traditional Review|collaborative_peer_feedback:Collaborative Activity Feedback|classroom_testing:Classroom Testing</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -1394,6 +1393,11 @@
           <t>toggle</t>
         </is>
       </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>readiness == 'activity_idea'</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -1442,38 +1446,47 @@
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>The PAC serves authors with many goals. Some authors want PAC feedback and may not intend to post the activity on the PAC (e.g., activities for Endorsed Collections). Indicate your preference.</t>
+        </is>
+      </c>
       <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>posting_goal_intro</t>
+          <t>submission_form_pdf</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>submission_kind</t>
+          <t>supplemental</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr"/>
       <c r="D5" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>The PAC serves authors with many goals. Some authors want PAC feedback and may not intend to post the activity on the PAC (e.g., activities for Endorsed Collections).</t>
+          <t>Submission Form (PDF)</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>info</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr"/>
+          <t>checkbox_group</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>yes:Submission Form (PDF)</t>
+        </is>
+      </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -1490,11 +1503,12 @@
       <c r="L5" s="5" t="inlineStr"/>
       <c r="M5" s="5" t="inlineStr"/>
       <c r="N5" s="5" t="inlineStr"/>
+      <c r="O5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>submission_form_pdf</t>
+          <t>submission_form_json</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -1504,11 +1518,11 @@
       </c>
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Submission Form (PDF)</t>
+          <t>Submission Form (JSON)</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -1518,7 +1532,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>yes:Submission Form (PDF)</t>
+          <t>yes:Submission Form (JSON)</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -1540,11 +1554,12 @@
       <c r="L6" s="5" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr"/>
       <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>submission_form_json</t>
+          <t>activity_document</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -1554,11 +1569,11 @@
       </c>
       <c r="C7" s="5" t="inlineStr"/>
       <c r="D7" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Submission Form (JSON)</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -1568,12 +1583,12 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>yes:Submission Form (JSON)</t>
+          <t>yes:Activity</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -1581,7 +1596,11 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>activity_for_review,activity_for_testing,approved_activity</t>
+        </is>
+      </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
           <t>all</t>
@@ -1590,11 +1609,12 @@
       <c r="L7" s="5" t="inlineStr"/>
       <c r="M7" s="5" t="inlineStr"/>
       <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>activity_document</t>
+          <t>toc_graphic</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -1604,11 +1624,11 @@
       </c>
       <c r="C8" s="5" t="inlineStr"/>
       <c r="D8" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>TOC Graphic</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -1618,7 +1638,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>yes:Activity</t>
+          <t>yes:TOC Graphic</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -1644,11 +1664,12 @@
       <c r="L8" s="5" t="inlineStr"/>
       <c r="M8" s="5" t="inlineStr"/>
       <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>toc_graphic</t>
+          <t>answer_key</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -1658,11 +1679,11 @@
       </c>
       <c r="C9" s="5" t="inlineStr"/>
       <c r="D9" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>TOC Graphic</t>
+          <t>Student Answers (Key)</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -1672,7 +1693,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>yes:TOC Graphic</t>
+          <t>yes:Student Answers (Key)</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -1698,11 +1719,12 @@
       <c r="L9" s="5" t="inlineStr"/>
       <c r="M9" s="5" t="inlineStr"/>
       <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>answer_key</t>
+          <t>facilitation_guide</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -1712,11 +1734,11 @@
       </c>
       <c r="C10" s="5" t="inlineStr"/>
       <c r="D10" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Student Answers (Key)</t>
+          <t>Facilitation Guide</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -1726,7 +1748,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>yes:Student Answers (Key)</t>
+          <t>yes:Facilitation Guide</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -1741,7 +1763,7 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>activity_for_review,activity_for_testing,approved_activity</t>
+          <t>activity_for_testing,approved_activity</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
@@ -1752,52 +1774,49 @@
       <c r="L10" s="5" t="inlineStr"/>
       <c r="M10" s="5" t="inlineStr"/>
       <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>facilitation_guide</t>
+          <t>author_name</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>supplemental</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr"/>
+          <t>authors</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>authors_group</t>
+        </is>
+      </c>
       <c r="D11" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Facilitation Guide</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>checkbox_group</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>yes:Facilitation Guide</t>
-        </is>
-      </c>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr"/>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>activity_for_testing,approved_activity</t>
-        </is>
-      </c>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr"/>
       <c r="K11" s="5" t="inlineStr">
         <is>
           <t>all</t>
@@ -1806,11 +1825,12 @@
       <c r="L11" s="5" t="inlineStr"/>
       <c r="M11" s="5" t="inlineStr"/>
       <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>author_name</t>
+          <t>author_email</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -1824,16 +1844,16 @@
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
@@ -1856,11 +1876,12 @@
       <c r="L12" s="5" t="inlineStr"/>
       <c r="M12" s="5" t="inlineStr"/>
       <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>author_email</t>
+          <t>author_phone</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -1874,27 +1895,27 @@
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>tel</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr"/>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr"/>
@@ -1906,40 +1927,37 @@
       <c r="L13" s="5" t="inlineStr"/>
       <c r="M13" s="5" t="inlineStr"/>
       <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>author_phone</t>
+          <t>title_activity</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>authors</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>authors_group</t>
-        </is>
-      </c>
+          <t>activity_identification</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr"/>
       <c r="D14" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Title of Activity</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>tel</t>
+          <t>text</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr"/>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1956,11 +1974,12 @@
       <c r="L14" s="5" t="inlineStr"/>
       <c r="M14" s="5" t="inlineStr"/>
       <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>title_activity</t>
+          <t>discipline</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -1970,19 +1989,23 @@
       </c>
       <c r="C15" s="5" t="inlineStr"/>
       <c r="D15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Title of Activity</t>
+          <t>Discipline</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr"/>
+          <t>select</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>anatomy_physiology:Anatomy &amp; Physiology|astronomy:Astronomy|biology:Biology|chemistry:Chemistry|computer_science:Computer Science|economics:Economics|environmental_science:Environmental Science|exercise_science:Exercise Science|fine_arts:Fine Arts|general:General|general_education:General Education|general_science:General Science|language_arts:Language Arts|mathematics:Mathematics|music:Music|neuroscience:Neuroscience|physics:Physics|psychology:Psychology|statistics:Statistics</t>
+        </is>
+      </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -2002,11 +2025,12 @@
       <c r="L15" s="5" t="inlineStr"/>
       <c r="M15" s="5" t="inlineStr"/>
       <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>discipline</t>
+          <t>topic</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -2016,23 +2040,19 @@
       </c>
       <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Topic</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>select</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>anatomy_physiology:Anatomy &amp; Physiology|astronomy:Astronomy|biology:Biology|chemistry:Chemistry|computer_science:Computer Science|economics:Economics|environmental_science:Environmental Science|exercise_science:Exercise Science|fine_arts:Fine Arts|general:General|general_education:General Education|general_science:General Science|language_arts:Language Arts|mathematics:Mathematics|music:Music|neuroscience:Neuroscience|physics:Physics|psychology:Psychology|statistics:Statistics</t>
-        </is>
-      </c>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -2052,33 +2072,38 @@
       <c r="L16" s="5" t="inlineStr"/>
       <c r="M16" s="5" t="inlineStr"/>
       <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>topic</t>
+          <t>idea_activity_type</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>activity_identification</t>
+          <t>idea_context</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Topic</t>
+          <t>Activity Type</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr"/>
+          <t>checkbox_group</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>learning_cycle:Learning Cycle|application:Application</t>
+        </is>
+      </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -2098,11 +2123,12 @@
       <c r="L17" s="5" t="inlineStr"/>
       <c r="M17" s="5" t="inlineStr"/>
       <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>idea_activity_type</t>
+          <t>idea_discipline</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -2112,26 +2138,26 @@
       </c>
       <c r="C18" s="5" t="inlineStr"/>
       <c r="D18" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Activity Type (choose as many or as few as appropriate)</t>
+          <t>Discipline</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>checkbox_group</t>
+          <t>select</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>learning_cycle:Learning Cycle|application:Application|swh_lab:Science Writing Heuristic Lab|pogil_lab:POGIL Lab|other:Other</t>
+          <t>anatomy_physiology:Anatomy &amp; Physiology|astronomy:Astronomy|biology:Biology|chemistry:Chemistry|computer_science:Computer Science|economics:Economics|environmental_science:Environmental Science|exercise_science:Exercise Science|fine_arts:Fine Arts|general:General|general_education:General Education|general_science:General Science|language_arts:Language Arts|mathematics:Mathematics|music:Music|neuroscience:Neuroscience|physics:Physics|psychology:Psychology|statistics:Statistics</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -2148,11 +2174,12 @@
       <c r="L18" s="5" t="inlineStr"/>
       <c r="M18" s="5" t="inlineStr"/>
       <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>idea_activity_type_other</t>
+          <t>idea_setting</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -2162,22 +2189,26 @@
       </c>
       <c r="C19" s="5" t="inlineStr"/>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>If Other, please specify</t>
+          <t>Setting</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr"/>
+          <t>checkbox_group</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>laboratory:Laboratory|classroom:Classroom</t>
+        </is>
+      </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>IF_VISIBLE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -2191,18 +2222,15 @@
           <t>all</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>idea_activity_type all [other]</t>
-        </is>
-      </c>
+      <c r="L19" s="5" t="inlineStr"/>
       <c r="M19" s="5" t="inlineStr"/>
       <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>idea_discipline</t>
+          <t>course</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -2212,26 +2240,22 @@
       </c>
       <c r="C20" s="5" t="inlineStr"/>
       <c r="D20" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Course (e.g., Physical Chemistry, General Biology)</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>select</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>anatomy_physiology:Anatomy &amp; Physiology|astronomy:Astronomy|biology:Biology|chemistry:Chemistry|computer_science:Computer Science|economics:Economics|environmental_science:Environmental Science|exercise_science:Exercise Science|fine_arts:Fine Arts|general:General|general_education:General Education|general_science:General Science|language_arts:Language Arts|mathematics:Mathematics|music:Music|neuroscience:Neuroscience|physics:Physics|psychology:Psychology|statistics:Statistics</t>
-        </is>
-      </c>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr"/>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -2248,11 +2272,12 @@
       <c r="L20" s="5" t="inlineStr"/>
       <c r="M20" s="5" t="inlineStr"/>
       <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>idea_setting</t>
+          <t>idea_level</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -2262,11 +2287,11 @@
       </c>
       <c r="C21" s="5" t="inlineStr"/>
       <c r="D21" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>Level</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -2276,12 +2301,12 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>laboratory:Laboratory|classroom:Classroom</t>
+          <t>k5:K-5|middle:Middle School|high:High School|undergrad_intro:Undergraduate (introductory-level)|undergrad_upper:Undergraduate (upper-level)|grad:Graduate</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -2298,25 +2323,26 @@
       <c r="L21" s="5" t="inlineStr"/>
       <c r="M21" s="5" t="inlineStr"/>
       <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>idea_course</t>
+          <t>idea_title</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>idea_context</t>
+          <t>idea_details</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr"/>
       <c r="D22" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Course (e.g., Physical Chemistry, General Biology)</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -2327,7 +2353,7 @@
       <c r="G22" s="5" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -2344,45 +2370,46 @@
       <c r="L22" s="5" t="inlineStr"/>
       <c r="M22" s="5" t="inlineStr"/>
       <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>idea_level</t>
+          <t>idea_objective_text</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>idea_context</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr"/>
+          <t>idea_details</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>idea_content_objectives_group</t>
+        </is>
+      </c>
       <c r="D23" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Level</t>
+          <t>Content Objective</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>checkbox_group</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>k5:K-5|middle:Middle School|high:High School|undergrad_intro:Undergraduate (introductory-level)|undergrad_upper:Undergraduate (upper-level)|grad:Graduate</t>
-        </is>
-      </c>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr"/>
@@ -2394,11 +2421,12 @@
       <c r="L23" s="5" t="inlineStr"/>
       <c r="M23" s="5" t="inlineStr"/>
       <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>idea_title</t>
+          <t>idea_skill_text</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -2406,13 +2434,17 @@
           <t>idea_details</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>idea_process_skills_group</t>
+        </is>
+      </c>
       <c r="D24" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Process Objective</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -2428,7 +2460,7 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr"/>
@@ -2440,11 +2472,12 @@
       <c r="L24" s="5" t="inlineStr"/>
       <c r="M24" s="5" t="inlineStr"/>
       <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>idea_objective_text</t>
+          <t>idea_description</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -2452,22 +2485,18 @@
           <t>idea_details</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>idea_content_objectives_group</t>
-        </is>
-      </c>
+      <c r="C25" s="5" t="inlineStr"/>
       <c r="D25" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Content Objective</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>textarea</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr"/>
@@ -2478,7 +2507,7 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr"/>
@@ -2488,50 +2517,59 @@
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr"/>
-      <c r="M25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>250 words or less</t>
+        </is>
+      </c>
       <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>idea_skill_text</t>
+          <t>image_authorship_mode</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>idea_details</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>idea_process_skills_group</t>
-        </is>
-      </c>
+          <t>image_source</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr"/>
       <c r="D26" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Process Objective</t>
+          <t>Image Authorship</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr"/>
+          <t>radio</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>blanket_author:I am the author of all images in the activity|specify:Specify image authorship</t>
+        </is>
+      </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr"/>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>approved_activity</t>
+        </is>
+      </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
           <t>all</t>
@@ -2540,30 +2578,35 @@
       <c r="L26" s="5" t="inlineStr"/>
       <c r="M26" s="5" t="inlineStr"/>
       <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>idea_description</t>
+          <t>image_description</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>idea_details</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr"/>
+          <t>image_source</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>image_source_group</t>
+        </is>
+      </c>
       <c r="D27" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Image</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>textarea</t>
+          <t>text</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr"/>
@@ -2586,15 +2629,16 @@
       <c r="L27" s="5" t="inlineStr"/>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>250 words or less</t>
+          <t>A short description or filename identifying the image.</t>
         </is>
       </c>
       <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>image_authorship_mode</t>
+          <t>image_role</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -2602,13 +2646,17 @@
           <t>image_source</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>image_source_group</t>
+        </is>
+      </c>
       <c r="D28" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Image Authorship</t>
+          <t>Image Credit</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -2618,12 +2666,12 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>blanket_author:I am the author of all images in the activity|specify:Specify image authorship</t>
+          <t>author:I am the author of this image|source:I am not the author of this image. Image source:</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -2631,11 +2679,7 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>approved_activity</t>
-        </is>
-      </c>
+      <c r="J28" s="5" t="inlineStr"/>
       <c r="K28" s="5" t="inlineStr">
         <is>
           <t>all</t>
@@ -2644,11 +2688,12 @@
       <c r="L28" s="5" t="inlineStr"/>
       <c r="M28" s="5" t="inlineStr"/>
       <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>image_description</t>
+          <t>image_source_detail</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -2662,11 +2707,11 @@
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Image</t>
+          <t>Source (URL or description)</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -2677,7 +2722,7 @@
       <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>IF_VISIBLE</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -2691,51 +2736,44 @@
           <t>all</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr"/>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>A short description or filename identifying the image.</t>
-        </is>
-      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>image_role == 'source'</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr"/>
       <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>image_role</t>
+          <t>ai_use_intro</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>image_source</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>image_source_group</t>
-        </is>
-      </c>
+          <t>ai_use</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr"/>
       <c r="D30" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Image Credit</t>
+          <t>Generative AI can support activity development, but it should support — not replace — your own instructional design, disciplinary judgment, and critical thinking. As AI plays a larger role in producing content, the expectation for your review, verification, and disclosure increases. Select the level that best describes how AI was used in developing this activity. Routine or Supportive use covers things like brainstorming, wording suggestions, grammar/clarity checks, or formatting on work you conceived and directed. Substantive Developmental use means AI helped develop or revise real components — drafting objectives, generating questions from your objectives, building datasets, or suggesting scaffolding — requiring your careful review and verification. Extensive Generative use means AI generated substantial portions of the activity (e.g. a full question sequence or draft) with limited initial input from you.</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>radio</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>author:I am the author of this image|source:I am not the author of this image. Image source:</t>
-        </is>
-      </c>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr"/>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -2752,40 +2790,41 @@
       <c r="L30" s="5" t="inlineStr"/>
       <c r="M30" s="5" t="inlineStr"/>
       <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>image_source_detail</t>
+          <t>ai_use_level</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>image_source</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>image_source_group</t>
-        </is>
-      </c>
+          <t>ai_use</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr"/>
       <c r="D31" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Source (URL or description)</t>
+          <t>Level of AI use</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr"/>
+          <t>radio</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>no_ai:No AI was used|routine:Routine or Supportive use|substantive:Substantive development use|extensive:Extensive generative AI use</t>
+        </is>
+      </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>IF_VISIBLE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -2799,18 +2838,15 @@
           <t>all</t>
         </is>
       </c>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>image_role == 'source'</t>
-        </is>
-      </c>
+      <c r="L31" s="5" t="inlineStr"/>
       <c r="M31" s="5" t="inlineStr"/>
       <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>ai_use_intro</t>
+          <t>ai_responsibility_statement</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -2820,11 +2856,11 @@
       </c>
       <c r="C32" s="5" t="inlineStr"/>
       <c r="D32" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Generative AI can support activity development, but it should support — not replace — your own instructional design, disciplinary judgment, and critical thinking. As AI plays a larger role in producing content, the expectation for your review, verification, and disclosure increases. Select the level that best describes how AI was used in developing this activity. Routine or Supportive use covers things like brainstorming, wording suggestions, grammar/clarity checks, or formatting on work you conceived and directed. Substantive Developmental use means AI helped develop or revise real components — drafting objectives, generating questions from your objectives, building datasets, or suggesting scaffolding — requiring your careful review and verification. Extensive Generative use means AI generated substantial portions of the activity (e.g. a full question sequence or draft) with limited initial input from you.</t>
+          <t>Author Responsibility Statement: By selecting this level, I affirm that I have critically reviewed, verified, and substantively revised any AI-assisted content in this activity. My own intellectual and creative contribution to this activity is substantial enough that I hold copyright in the final work, and I accept full responsibility for the accuracy, originality, instructional design, and POGIL alignment of the submitted activity.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -2849,14 +2885,19 @@
           <t>all</t>
         </is>
       </c>
-      <c r="L32" s="5" t="inlineStr"/>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>ai_use_level in [substantive,extensive]</t>
+        </is>
+      </c>
       <c r="M32" s="5" t="inlineStr"/>
       <c r="N32" s="5" t="inlineStr"/>
+      <c r="O32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>ai_use_level</t>
+          <t>ai_responsibility_checkbox</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -2866,26 +2907,26 @@
       </c>
       <c r="C33" s="5" t="inlineStr"/>
       <c r="D33" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Level of AI use</t>
+          <t>Affirmation</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>radio</t>
+          <t>checkbox_group</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>no_ai:No AI was used|routine:Routine or Supportive use|substantive:Substantive development use|extensive:Extensive generative AI use</t>
+          <t>affirmed:I affirm the statement above.</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>IF_VISIBLE</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
@@ -2899,14 +2940,19 @@
           <t>all</t>
         </is>
       </c>
-      <c r="L33" s="5" t="inlineStr"/>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>ai_use_level in [substantive,extensive]</t>
+        </is>
+      </c>
       <c r="M33" s="5" t="inlineStr"/>
       <c r="N33" s="5" t="inlineStr"/>
+      <c r="O33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>ai_responsibility_statement</t>
+          <t>ai_use_description</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -2916,22 +2962,22 @@
       </c>
       <c r="C34" s="5" t="inlineStr"/>
       <c r="D34" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Author Responsibility Statement: By selecting this level, I affirm that I have critically reviewed, verified, and substantively revised any AI-assisted content in this activity. My own intellectual and creative contribution to this activity is substantial enough that I hold copyright in the final work, and I accept full responsibility for the accuracy, originality, instructional design, and POGIL alignment of the submitted activity.</t>
+          <t>Briefly describe how AI was used in developing this activity.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>textarea</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr"/>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>IF_VISIBLE</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -2952,40 +2998,41 @@
       </c>
       <c r="M34" s="5" t="inlineStr"/>
       <c r="N34" s="5" t="inlineStr"/>
+      <c r="O34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>ai_responsibility_checkbox</t>
+          <t>q2</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>ai_use</t>
+          <t>student_background</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr"/>
       <c r="D35" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Affirmation</t>
+          <t>Have students used and/or reviewed this activity?</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>checkbox_group</t>
+          <t>radio</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>affirmed:I affirm the statement above.</t>
+          <t>yes:Yes|no:No</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>IF_VISIBLE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
@@ -2999,32 +3046,29 @@
           <t>all</t>
         </is>
       </c>
-      <c r="L35" s="5" t="inlineStr">
-        <is>
-          <t>ai_use_level in [substantive,extensive]</t>
-        </is>
-      </c>
+      <c r="L35" s="5" t="inlineStr"/>
       <c r="M35" s="5" t="inlineStr"/>
       <c r="N35" s="5" t="inlineStr"/>
+      <c r="O35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>ai_use_description</t>
+          <t>q3a</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>ai_use</t>
+          <t>student_background</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr"/>
       <c r="D36" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Briefly describe how AI was used in developing this activity.</t>
+          <t>Key knowledge students should have as a prerequisite.</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -3035,7 +3079,7 @@
       <c r="G36" s="5" t="inlineStr"/>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>IF_VISIBLE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
@@ -3049,44 +3093,37 @@
           <t>all</t>
         </is>
       </c>
-      <c r="L36" s="5" t="inlineStr">
-        <is>
-          <t>ai_use_level in [substantive,extensive]</t>
-        </is>
-      </c>
+      <c r="L36" s="5" t="inlineStr"/>
       <c r="M36" s="5" t="inlineStr"/>
       <c r="N36" s="5" t="inlineStr"/>
+      <c r="O36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>course_level</t>
+          <t>q3b</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>course_context</t>
+          <t>student_background</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr"/>
       <c r="D37" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Course Level</t>
+          <t>Knowledge students are not expected to have prior to activity.</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>radio</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>high_school:High school|undergrad_intro:Undergraduate course (introductory-level)|undergrad_upper:Undergraduate course (upper-level)|grad:Graduate course</t>
-        </is>
-      </c>
+          <t>textarea</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr"/>
       <c r="H37" s="5" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -3106,25 +3143,26 @@
       <c r="L37" s="5" t="inlineStr"/>
       <c r="M37" s="5" t="inlineStr"/>
       <c r="N37" s="5" t="inlineStr"/>
+      <c r="O37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>q1a</t>
+          <t>approval_testing_evidence</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>course_context</t>
+          <t>approval_evidence</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr"/>
       <c r="D38" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>The student population for your course.</t>
+          <t>Provide evidence that this activity has been tested in the classroom, and describe how it has been revised based on that feedback.</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -3150,442 +3188,13 @@
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr"/>
-      <c r="M38" s="5" t="inlineStr"/>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>Include student performance data, instructor observations, or facilitator notes as applicable.</t>
+        </is>
+      </c>
       <c r="N38" s="5" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>q1b</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>course_context</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr"/>
-      <c r="D39" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>How the course fits into your departmental curriculum.</t>
-        </is>
-      </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>textarea</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr"/>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="J39" s="5" t="inlineStr"/>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="L39" s="5" t="inlineStr"/>
-      <c r="M39" s="5" t="inlineStr"/>
-      <c r="N39" s="5" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>q1c</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>course_context</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr"/>
-      <c r="D40" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>The course setting (room description, class size, frequency and length of meeting times, etc.).</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>textarea</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr"/>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="J40" s="5" t="inlineStr"/>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="L40" s="5" t="inlineStr"/>
-      <c r="M40" s="5" t="inlineStr"/>
-      <c r="N40" s="5" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>q2</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>student_background</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr"/>
-      <c r="D41" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>Have students used and/or reviewed this activity?</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>radio</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>yes:Yes|no:No</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="I41" s="5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="J41" s="5" t="inlineStr"/>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="L41" s="5" t="inlineStr"/>
-      <c r="M41" s="5" t="inlineStr"/>
-      <c r="N41" s="5" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>q3a</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>student_background</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr"/>
-      <c r="D42" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>Key knowledge students should have as a prerequisite.</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>textarea</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr"/>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="J42" s="5" t="inlineStr"/>
-      <c r="K42" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="L42" s="5" t="inlineStr"/>
-      <c r="M42" s="5" t="inlineStr"/>
-      <c r="N42" s="5" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>q3b</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>student_background</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr"/>
-      <c r="D43" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>Knowledge students are not expected to have prior to activity.</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>textarea</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr"/>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="J43" s="5" t="inlineStr"/>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="L43" s="5" t="inlineStr"/>
-      <c r="M43" s="5" t="inlineStr"/>
-      <c r="N43" s="5" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>q8</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>implementation</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr"/>
-      <c r="D44" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>Is this activity intended for use with the eight characteristics of the Basic POGIL Classroom Implementation? Check all that apply.</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>checkbox_group</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>a:Students are expected to work cooperatively, generally in groups of three or four.|b:The activity is a POGIL activity, specifically designed for POGIL implementation.|c:The students work on the activity during class time with a facilitator present.|d:The dominant mode of instruction is not lecture or instructor-centered; the instructor serves predominantly as a facilitator of student learning.|e:Students have assigned roles within their groups.|f:The activity is designed to be the first introduction to the topic or specific content.|g:The students are not expected to have worked on any part of the activity prior to class meeting time.|h:Groups are expected to complete all of the Critical Thinking Questions (or equivalently designated questions) during class, but they are not expected to work on any of the Exercises or Problems.</t>
-        </is>
-      </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="I44" s="5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="J44" s="5" t="inlineStr"/>
-      <c r="K44" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="L44" s="5" t="inlineStr"/>
-      <c r="M44" s="5" t="inlineStr"/>
-      <c r="N44" s="5" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>q9</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>implementation</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr"/>
-      <c r="D45" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>If you did not check boxes (a), (c), and (d) above, submit an implementation plan describing specifically how you implement this activity within your classroom.</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>textarea</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr"/>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>IF_VISIBLE</t>
-        </is>
-      </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="J45" s="5" t="inlineStr"/>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="L45" s="5" t="inlineStr">
-        <is>
-          <t>q8 not_all [a,c,d]</t>
-        </is>
-      </c>
-      <c r="M45" s="5" t="inlineStr"/>
-      <c r="N45" s="5" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>q10</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>implementation</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr"/>
-      <c r="D46" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>For those boxes above that you did not check, briefly describe how and/or why your activity is not implemented in that way.</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>textarea</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr"/>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>IF_VISIBLE</t>
-        </is>
-      </c>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="J46" s="5" t="inlineStr"/>
-      <c r="K46" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="L46" s="5" t="inlineStr">
-        <is>
-          <t>q8 not_all [a,b,c,d,e,f,g,h]</t>
-        </is>
-      </c>
-      <c r="M46" s="5" t="inlineStr"/>
-      <c r="N46" s="5" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>approval_testing_evidence</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>implementation</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr"/>
-      <c r="D47" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>Provide evidence that this activity has been tested in the classroom, and describe how it has been revised based on that feedback.</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>textarea</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr"/>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="J47" s="5" t="inlineStr"/>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>approved_activity</t>
-        </is>
-      </c>
-      <c r="L47" s="5" t="inlineStr"/>
-      <c r="M47" s="5" t="inlineStr">
-        <is>
-          <t>Include student performance data, instructor observations, or facilitator notes as applicable.</t>
-        </is>
-      </c>
-      <c r="N47" s="5" t="inlineStr"/>
+      <c r="O38" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/structure.xlsx
+++ b/structure.xlsx
@@ -660,7 +660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -754,7 +754,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>activity_identification</t>
+          <t>activity_title_objectives</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
@@ -762,19 +762,19 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Activity Identification</t>
+          <t>Activity Title and Learning Objectives</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>activity_for_review,activity_for_testing,approved_activity</t>
+          <t>all</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>idea_context</t>
+          <t>classroom_context</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
@@ -794,35 +794,35 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>student_background</t>
+          <t>activity_description</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Student Background</t>
+          <t>Activity Description</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>activity_for_review,activity_for_testing,approved_activity</t>
+          <t>activity_idea</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>objectives_goals</t>
+          <t>student_background</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Learning Objectives &amp; Process Skill Goals</t>
+          <t>Student Background</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -888,26 +888,6 @@
       <c r="D11" s="5" t="inlineStr">
         <is>
           <t>activity_for_review,activity_for_testing,approved_activity</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>idea_details</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Activity Idea</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>activity_idea</t>
         </is>
       </c>
     </row>
@@ -922,7 +902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1017,43 +997,51 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>content_objectives_group</t>
+          <t>image_source_group</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>objectives_goals</t>
+          <t>image_source</t>
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Learning Objective</t>
+          <t>Image</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="5" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>+ Add learning objective</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr"/>
+          <t>+ Add image</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>approved_activity</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>image_authorship_mode == 'specify'</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>process_skills_group</t>
+          <t>content_objectives_group</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>objectives_goals</t>
+          <t>activity_title_objectives</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
@@ -1061,7 +1049,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Process Skill Goal</t>
+          <t>Content Objective</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
@@ -1070,7 +1058,7 @@
       <c r="F4" s="5" t="inlineStr"/>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>+ Add process skill goal</t>
+          <t>+ Add content objective</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr"/>
@@ -1079,103 +1067,33 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>image_source_group</t>
+          <t>process_skills_group</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>image_source</t>
+          <t>activity_title_objectives</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Image</t>
+          <t>Process Objective</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="5" t="inlineStr"/>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>+ Add image</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>approved_activity</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>image_authorship_mode == 'specify'</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>idea_content_objectives_group</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>idea_details</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Content Objective</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>+ Add content objective</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>idea_process_skills_group</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>idea_details</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Process Objective</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="5" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
           <t>+ Add process objective</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
+      <c r="H5" s="5" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1188,7 +1106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1932,12 +1850,12 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>title_activity</t>
+          <t>activity_type</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>activity_identification</t>
+          <t>classroom_context</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr"/>
@@ -1946,15 +1864,19 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Title of Activity</t>
+          <t>Activity Type</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr"/>
+          <t>checkbox_group</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>learning_cycle:Learning Cycle|application:Application</t>
+        </is>
+      </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -1984,12 +1906,12 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>activity_identification</t>
+          <t>classroom_context</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr"/>
       <c r="D15" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
@@ -2030,29 +1952,33 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>topic</t>
+          <t>setting</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>activity_identification</t>
+          <t>classroom_context</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Topic</t>
+          <t>Setting</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr"/>
+          <t>checkbox_group</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>laboratory:Laboratory|classroom:Classroom</t>
+        </is>
+      </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -2077,33 +2003,29 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>idea_activity_type</t>
+          <t>course</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>idea_context</t>
+          <t>classroom_context</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Activity Type</t>
+          <t>Course (e.g., Physical Chemistry, General Biology)</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>checkbox_group</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>learning_cycle:Learning Cycle|application:Application</t>
-        </is>
-      </c>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr"/>
       <c r="H17" s="5" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -2128,31 +2050,31 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>idea_discipline</t>
+          <t>level</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>idea_context</t>
+          <t>classroom_context</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr"/>
       <c r="D18" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Level</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>checkbox_group</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>anatomy_physiology:Anatomy &amp; Physiology|astronomy:Astronomy|biology:Biology|chemistry:Chemistry|computer_science:Computer Science|economics:Economics|environmental_science:Environmental Science|exercise_science:Exercise Science|fine_arts:Fine Arts|general:General|general_education:General Education|general_science:General Science|language_arts:Language Arts|mathematics:Mathematics|music:Music|neuroscience:Neuroscience|physics:Physics|psychology:Psychology|statistics:Statistics</t>
+          <t>k5:K-5|middle:Middle School|high:High School|undergrad_intro:Undergraduate (introductory-level)|undergrad_upper:Undergraduate (upper-level)|grad:Graduate</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
@@ -2179,33 +2101,29 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>idea_setting</t>
+          <t>title</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>idea_context</t>
+          <t>activity_title_objectives</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr"/>
       <c r="D19" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>checkbox_group</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>laboratory:Laboratory|classroom:Classroom</t>
-        </is>
-      </c>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr"/>
       <c r="H19" s="5" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -2230,21 +2148,25 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>course</t>
+          <t>objective_text</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>idea_context</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr"/>
+          <t>activity_title_objectives</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>content_objectives_group</t>
+        </is>
+      </c>
       <c r="D20" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Course (e.g., Physical Chemistry, General Biology)</t>
+          <t>Content Objective</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -2260,7 +2182,7 @@
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr"/>
@@ -2277,33 +2199,33 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>idea_level</t>
+          <t>skill_text</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>idea_context</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr"/>
+          <t>activity_title_objectives</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>process_skills_group</t>
+        </is>
+      </c>
       <c r="D21" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Level</t>
+          <t>Process Objective</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>checkbox_group</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>k5:K-5|middle:Middle School|high:High School|undergrad_intro:Undergraduate (introductory-level)|undergrad_upper:Undergraduate (upper-level)|grad:Graduate</t>
-        </is>
-      </c>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr"/>
       <c r="H21" s="5" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -2311,7 +2233,7 @@
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr"/>
@@ -2328,12 +2250,12 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>idea_title</t>
+          <t>idea_description</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>idea_details</t>
+          <t>activity_description</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr"/>
@@ -2342,12 +2264,12 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>textarea</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr"/>
@@ -2368,51 +2290,59 @@
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr"/>
-      <c r="M22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>250 words or less</t>
+        </is>
+      </c>
       <c r="N22" s="5" t="inlineStr"/>
       <c r="O22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>idea_objective_text</t>
+          <t>image_authorship_mode</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>idea_details</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>idea_content_objectives_group</t>
-        </is>
-      </c>
+          <t>image_source</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr"/>
       <c r="D23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Content Objective</t>
+          <t>Image Authorship</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr"/>
+          <t>radio</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>blanket_author:I am the author of all images in the activity|specify:Specify image authorship</t>
+        </is>
+      </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr"/>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>approved_activity</t>
+        </is>
+      </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
           <t>all</t>
@@ -2426,17 +2356,17 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>idea_skill_text</t>
+          <t>image_description</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>idea_details</t>
+          <t>image_source</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>idea_process_skills_group</t>
+          <t>image_source_group</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
@@ -2444,7 +2374,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Process Objective</t>
+          <t>Image</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -2460,7 +2390,7 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr"/>
@@ -2470,36 +2400,48 @@
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr"/>
-      <c r="M24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>A short description or filename identifying the image.</t>
+        </is>
+      </c>
       <c r="N24" s="5" t="inlineStr"/>
       <c r="O24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>idea_description</t>
+          <t>image_role</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>idea_details</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr"/>
+          <t>image_source</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>image_source_group</t>
+        </is>
+      </c>
       <c r="D25" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Image Credit</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>textarea</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr"/>
+          <t>radio</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>author:I am the author of this image|source:I am not the author of this image. Image source:</t>
+        </is>
+      </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -2517,18 +2459,14 @@
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr"/>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>250 words or less</t>
-        </is>
-      </c>
+      <c r="M25" s="5" t="inlineStr"/>
       <c r="N25" s="5" t="inlineStr"/>
       <c r="O25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>image_authorship_mode</t>
+          <t>image_source_detail</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -2536,28 +2474,28 @@
           <t>image_source</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>image_source_group</t>
+        </is>
+      </c>
       <c r="D26" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Image Authorship</t>
+          <t>Source (URL or description)</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>radio</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>blanket_author:I am the author of all images in the activity|specify:Specify image authorship</t>
-        </is>
-      </c>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>IF_VISIBLE</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -2565,17 +2503,17 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>approved_activity</t>
-        </is>
-      </c>
+      <c r="J26" s="5" t="inlineStr"/>
       <c r="K26" s="5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="L26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>image_role == 'source'</t>
+        </is>
+      </c>
       <c r="M26" s="5" t="inlineStr"/>
       <c r="N26" s="5" t="inlineStr"/>
       <c r="O26" s="5" t="inlineStr"/>
@@ -2583,36 +2521,32 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>image_description</t>
+          <t>ai_use_intro</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>image_source</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>image_source_group</t>
-        </is>
-      </c>
+          <t>ai_use</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr"/>
       <c r="D27" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Image</t>
+          <t>Generative AI can support activity development, but it should support — not replace — your own instructional design, disciplinary judgment, and critical thinking. As AI plays a larger role in producing content, the expectation for your review, verification, and disclosure increases. Select the level that best describes how AI was used in developing this activity. Routine or Supportive use covers things like brainstorming, wording suggestions, grammar/clarity checks, or formatting on work you conceived and directed. Substantive Developmental use means AI helped develop or revise real components — drafting objectives, generating questions from your objectives, building datasets, or suggesting scaffolding — requiring your careful review and verification. Extensive Generative use means AI generated substantial portions of the activity (e.g. a full question sequence or draft) with limited initial input from you.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>info</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -2627,36 +2561,28 @@
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr"/>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>A short description or filename identifying the image.</t>
-        </is>
-      </c>
+      <c r="M27" s="5" t="inlineStr"/>
       <c r="N27" s="5" t="inlineStr"/>
       <c r="O27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>image_role</t>
+          <t>ai_use_level</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>image_source</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>image_source_group</t>
-        </is>
-      </c>
+          <t>ai_use</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr"/>
       <c r="D28" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Image Credit</t>
+          <t>Level of AI use</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -2666,7 +2592,7 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>author:I am the author of this image|source:I am not the author of this image. Image source:</t>
+          <t>no_ai:No AI was used|routine:Routine or Supportive use|substantive:Substantive development use|extensive:Extensive generative AI use</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
@@ -2693,36 +2619,32 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>image_source_detail</t>
+          <t>ai_responsibility_statement</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>image_source</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>image_source_group</t>
-        </is>
-      </c>
+          <t>ai_use</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr"/>
       <c r="D29" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Source (URL or description)</t>
+          <t>Author Responsibility Statement: By selecting this level, I affirm that I have critically reviewed, verified, and substantively revised any AI-assisted content in this activity. My own intellectual and creative contribution to this activity is substantial enough that I hold copyright in the final work, and I accept full responsibility for the accuracy, originality, instructional design, and POGIL alignment of the submitted activity.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>info</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>IF_VISIBLE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -2738,7 +2660,7 @@
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>image_role == 'source'</t>
+          <t>ai_use_level in [substantive,extensive]</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr"/>
@@ -2748,7 +2670,7 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>ai_use_intro</t>
+          <t>ai_responsibility_checkbox</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -2758,22 +2680,26 @@
       </c>
       <c r="C30" s="5" t="inlineStr"/>
       <c r="D30" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Generative AI can support activity development, but it should support — not replace — your own instructional design, disciplinary judgment, and critical thinking. As AI plays a larger role in producing content, the expectation for your review, verification, and disclosure increases. Select the level that best describes how AI was used in developing this activity. Routine or Supportive use covers things like brainstorming, wording suggestions, grammar/clarity checks, or formatting on work you conceived and directed. Substantive Developmental use means AI helped develop or revise real components — drafting objectives, generating questions from your objectives, building datasets, or suggesting scaffolding — requiring your careful review and verification. Extensive Generative use means AI generated substantial portions of the activity (e.g. a full question sequence or draft) with limited initial input from you.</t>
+          <t>Affirmation</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>info</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr"/>
+          <t>checkbox_group</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>affirmed:I affirm the statement above.</t>
+        </is>
+      </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>IF_VISIBLE</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -2787,7 +2713,11 @@
           <t>all</t>
         </is>
       </c>
-      <c r="L30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>ai_use_level in [substantive,extensive]</t>
+        </is>
+      </c>
       <c r="M30" s="5" t="inlineStr"/>
       <c r="N30" s="5" t="inlineStr"/>
       <c r="O30" s="5" t="inlineStr"/>
@@ -2795,7 +2725,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>ai_use_level</t>
+          <t>ai_use_description</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -2805,26 +2735,22 @@
       </c>
       <c r="C31" s="5" t="inlineStr"/>
       <c r="D31" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Level of AI use</t>
+          <t>Briefly describe how AI was used in developing this activity.</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>radio</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>no_ai:No AI was used|routine:Routine or Supportive use|substantive:Substantive development use|extensive:Extensive generative AI use</t>
-        </is>
-      </c>
+          <t>textarea</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>IF_VISIBLE</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -2838,7 +2764,11 @@
           <t>all</t>
         </is>
       </c>
-      <c r="L31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>ai_use_level in [substantive,extensive]</t>
+        </is>
+      </c>
       <c r="M31" s="5" t="inlineStr"/>
       <c r="N31" s="5" t="inlineStr"/>
       <c r="O31" s="5" t="inlineStr"/>
@@ -2846,32 +2776,36 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>ai_responsibility_statement</t>
+          <t>q2</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>ai_use</t>
+          <t>student_background</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr"/>
       <c r="D32" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Author Responsibility Statement: By selecting this level, I affirm that I have critically reviewed, verified, and substantively revised any AI-assisted content in this activity. My own intellectual and creative contribution to this activity is substantial enough that I hold copyright in the final work, and I accept full responsibility for the accuracy, originality, instructional design, and POGIL alignment of the submitted activity.</t>
+          <t>Have students used and/or reviewed this activity?</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>info</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr"/>
+          <t>radio</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>yes:Yes|no:No</t>
+        </is>
+      </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
@@ -2885,11 +2819,7 @@
           <t>all</t>
         </is>
       </c>
-      <c r="L32" s="5" t="inlineStr">
-        <is>
-          <t>ai_use_level in [substantive,extensive]</t>
-        </is>
-      </c>
+      <c r="L32" s="5" t="inlineStr"/>
       <c r="M32" s="5" t="inlineStr"/>
       <c r="N32" s="5" t="inlineStr"/>
       <c r="O32" s="5" t="inlineStr"/>
@@ -2897,36 +2827,32 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>ai_responsibility_checkbox</t>
+          <t>q3a</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>ai_use</t>
+          <t>student_background</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr"/>
       <c r="D33" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Affirmation</t>
+          <t>Key knowledge students should have as a prerequisite.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>checkbox_group</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>affirmed:I affirm the statement above.</t>
-        </is>
-      </c>
+          <t>textarea</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>IF_VISIBLE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
@@ -2940,11 +2866,7 @@
           <t>all</t>
         </is>
       </c>
-      <c r="L33" s="5" t="inlineStr">
-        <is>
-          <t>ai_use_level in [substantive,extensive]</t>
-        </is>
-      </c>
+      <c r="L33" s="5" t="inlineStr"/>
       <c r="M33" s="5" t="inlineStr"/>
       <c r="N33" s="5" t="inlineStr"/>
       <c r="O33" s="5" t="inlineStr"/>
@@ -2952,21 +2874,21 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>ai_use_description</t>
+          <t>q3b</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>ai_use</t>
+          <t>student_background</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr"/>
       <c r="D34" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Briefly describe how AI was used in developing this activity.</t>
+          <t>Knowledge students are not expected to have prior to activity.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -2977,7 +2899,7 @@
       <c r="G34" s="5" t="inlineStr"/>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>IF_VISIBLE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -2991,11 +2913,7 @@
           <t>all</t>
         </is>
       </c>
-      <c r="L34" s="5" t="inlineStr">
-        <is>
-          <t>ai_use_level in [substantive,extensive]</t>
-        </is>
-      </c>
+      <c r="L34" s="5" t="inlineStr"/>
       <c r="M34" s="5" t="inlineStr"/>
       <c r="N34" s="5" t="inlineStr"/>
       <c r="O34" s="5" t="inlineStr"/>
@@ -3003,12 +2921,12 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>q2</t>
+          <t>approval_testing_evidence</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>student_background</t>
+          <t>approval_evidence</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr"/>
@@ -3017,19 +2935,15 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Have students used and/or reviewed this activity?</t>
+          <t>Provide evidence that this activity has been tested in the classroom, and describe how it has been revised based on that feedback.</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>radio</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>yes:Yes|no:No</t>
-        </is>
-      </c>
+          <t>textarea</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr"/>
       <c r="H35" s="5" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -3047,154 +2961,13 @@
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr"/>
-      <c r="M35" s="5" t="inlineStr"/>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>Include student performance data, instructor observations, or facilitator notes as applicable.</t>
+        </is>
+      </c>
       <c r="N35" s="5" t="inlineStr"/>
       <c r="O35" s="5" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>q3a</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>student_background</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr"/>
-      <c r="D36" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>Key knowledge students should have as a prerequisite.</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>textarea</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr"/>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="J36" s="5" t="inlineStr"/>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="L36" s="5" t="inlineStr"/>
-      <c r="M36" s="5" t="inlineStr"/>
-      <c r="N36" s="5" t="inlineStr"/>
-      <c r="O36" s="5" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>q3b</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>student_background</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr"/>
-      <c r="D37" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>Knowledge students are not expected to have prior to activity.</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>textarea</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr"/>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="J37" s="5" t="inlineStr"/>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="L37" s="5" t="inlineStr"/>
-      <c r="M37" s="5" t="inlineStr"/>
-      <c r="N37" s="5" t="inlineStr"/>
-      <c r="O37" s="5" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>approval_testing_evidence</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>approval_evidence</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr"/>
-      <c r="D38" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>Provide evidence that this activity has been tested in the classroom, and describe how it has been revised based on that feedback.</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>textarea</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr"/>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="J38" s="5" t="inlineStr"/>
-      <c r="K38" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="L38" s="5" t="inlineStr"/>
-      <c r="M38" s="5" t="inlineStr">
-        <is>
-          <t>Include student performance data, instructor observations, or facilitator notes as applicable.</t>
-        </is>
-      </c>
-      <c r="N38" s="5" t="inlineStr"/>
-      <c r="O38" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/structure.xlsx
+++ b/structure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sgr/GitHub/pac-submission-form/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B0DB56-FCF0-5C4A-B2DF-FA838D646C44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DA63C45-9A0F-594A-973D-7D2A2E952DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="1" r:id="rId1"/>
@@ -138,9 +138,6 @@
     <t>Submission Kind</t>
   </si>
   <si>
-    <t>supplemental</t>
-  </si>
-  <si>
     <t>Checklist for Submission</t>
   </si>
   <si>
@@ -591,13 +588,16 @@
     <t>Checklist starts its own page.</t>
   </si>
   <si>
+    <t>A learning cycle activity takes students through one or more explore, invent, apply cycles. An application activity often guides the application of concepts without a complete learning cycle.</t>
+  </si>
+  <si>
+    <t>check_list</t>
+  </si>
+  <si>
     <t>Generative AI can support activity development, but it should support — not replace — your own instructional design, disciplinary judgment, and critical thinking. As AI plays a larger role in producing content, the expectation for your review, verification, and disclosure increases. Select the level that best describes how AI was used in developing this activity.
-• __Routine or Supportive use__ covers things like brainstorming, wording suggestions, grammar/clarity checks, or formatting on work you conceived and directed.
-• __Substantive Developmental use__ means AI helped develop or revise real components — drafting objectives, generating questions from your objectives, building datasets, or suggesting scaffolding — requiring your careful review and verification.
-• __Extensive Generative use__ means AI generated substantial portions of the activity (e.g. a full question sequence or draft) with limited initial input from you.</t>
-  </si>
-  <si>
-    <t>A learning cycle activity takes students through one or more explore, invent, apply cycles. An application activity often guides the application of concepts without a complete learning cycle.</t>
+• &lt;b&gt;Routine or Supportive use&lt;/b&gt; covers things like brainstorming, wording suggestions, grammar/clarity checks, or formatting on work you conceived and directed.
+• &lt;b&gt;Substantive Developmental use&lt;/b&gt; means AI helped develop or revise real components — drafting objectives, generating questions from your objectives, building datasets, or suggesting scaffolding — requiring your careful review and verification.
+• &lt;b&gt;Extensive Generative use&lt;/b&gt; means AI generated substantial portions of the activity (e.g. a full question sequence or draft) with limited initial input from you.</t>
   </si>
 </sst>
 </file>
@@ -1171,13 +1171,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B4" s="5">
+        <v>12</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="B4" s="5">
-        <v>3</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>36</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>32</v>
@@ -1185,13 +1185,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5" s="5">
         <v>4</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>32</v>
@@ -1199,13 +1199,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" s="5">
         <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>32</v>
@@ -1213,72 +1213,72 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B7" s="5">
         <v>6</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B8" s="5">
         <v>7</v>
       </c>
       <c r="C8" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B9" s="5">
         <v>9</v>
       </c>
       <c r="C9" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="28" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B10" s="5">
         <v>10</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="28" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B11" s="5">
         <v>11</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1303,7 +1303,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>26</v>
@@ -1312,27 +1312,27 @@
         <v>27</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>30</v>
@@ -1341,87 +1341,87 @@
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E2" s="5">
         <v>1</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C3" s="5">
         <v>2</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E3" s="5">
         <v>0</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C4" s="5">
         <v>2</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E4" s="5">
         <v>1</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5" s="5">
         <v>3</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
@@ -1461,43 +1461,43 @@
         <v>26</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>78</v>
-      </c>
       <c r="J1" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M1" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="42" x14ac:dyDescent="0.2">
@@ -1512,19 +1512,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="H2" s="5" t="s">
-        <v>85</v>
-      </c>
       <c r="I2" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J2" s="5"/>
       <c r="K2" s="5" t="s">
@@ -1533,7 +1533,7 @@
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O2" s="5"/>
     </row>
@@ -1549,19 +1549,19 @@
         <v>2</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>89</v>
-      </c>
       <c r="H3" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J3" s="5"/>
       <c r="K3" s="5" t="s">
@@ -1570,15 +1570,15 @@
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
       <c r="N3" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="70" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>33</v>
@@ -1588,19 +1588,19 @@
         <v>3</v>
       </c>
       <c r="E4" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>94</v>
-      </c>
       <c r="H4" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J4" s="5"/>
       <c r="K4" s="5" t="s">
@@ -1608,36 +1608,36 @@
       </c>
       <c r="L4" s="5"/>
       <c r="M4" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>35</v>
+        <v>186</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5">
         <v>1</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>98</v>
-      </c>
       <c r="H5" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J5" s="5"/>
       <c r="K5" s="5" t="s">
@@ -1650,29 +1650,29 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>35</v>
+        <v>186</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5">
         <v>2</v>
       </c>
       <c r="E6" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>101</v>
-      </c>
       <c r="H6" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J6" s="5"/>
       <c r="K6" s="5" t="s">
@@ -1685,32 +1685,32 @@
     </row>
     <row r="7" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>35</v>
+        <v>186</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5">
         <v>3</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>104</v>
-      </c>
       <c r="H7" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>32</v>
@@ -1722,32 +1722,32 @@
     </row>
     <row r="8" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>35</v>
+        <v>186</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5">
         <v>4</v>
       </c>
       <c r="E8" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>107</v>
-      </c>
       <c r="H8" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K8" s="5" t="s">
         <v>32</v>
@@ -1759,32 +1759,32 @@
     </row>
     <row r="9" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>35</v>
+        <v>186</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5">
         <v>5</v>
       </c>
       <c r="E9" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>110</v>
-      </c>
       <c r="H9" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>32</v>
@@ -1796,32 +1796,32 @@
     </row>
     <row r="10" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>35</v>
+        <v>186</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5">
         <v>6</v>
       </c>
       <c r="E10" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="G10" s="5" t="s">
+      <c r="H10" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="J10" s="5" t="s">
         <v>113</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>114</v>
       </c>
       <c r="K10" s="5" t="s">
         <v>32</v>
@@ -1833,29 +1833,29 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D11" s="5">
         <v>1</v>
       </c>
       <c r="E11" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>116</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>117</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="5" t="s">
@@ -1868,29 +1868,29 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D12" s="5">
         <v>2</v>
       </c>
       <c r="E12" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>119</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>120</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J12" s="5"/>
       <c r="K12" s="5" t="s">
@@ -1903,29 +1903,29 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D13" s="5">
         <v>3</v>
       </c>
       <c r="E13" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>122</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>123</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J13" s="5"/>
       <c r="K13" s="5" t="s">
@@ -1938,29 +1938,29 @@
     </row>
     <row r="14" spans="1:15" ht="70" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5">
         <v>1</v>
       </c>
       <c r="E14" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>126</v>
-      </c>
       <c r="H14" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5" t="s">
@@ -1968,36 +1968,36 @@
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
     </row>
     <row r="15" spans="1:15" ht="140" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5">
         <v>3</v>
       </c>
       <c r="E15" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="G15" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>130</v>
-      </c>
       <c r="H15" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="5" t="s">
@@ -2010,29 +2010,29 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="5">
         <v>4</v>
       </c>
       <c r="E16" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F16" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>133</v>
-      </c>
       <c r="H16" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5" t="s">
@@ -2045,27 +2045,27 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="5">
         <v>5</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J17" s="5"/>
       <c r="K17" s="5" t="s">
@@ -2078,29 +2078,29 @@
     </row>
     <row r="18" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5">
         <v>6</v>
       </c>
       <c r="E18" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="F18" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>138</v>
-      </c>
       <c r="H18" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J18" s="5"/>
       <c r="K18" s="5" t="s">
@@ -2116,24 +2116,24 @@
         <v>28</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="5">
         <v>1</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="5" t="s">
@@ -2146,29 +2146,29 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D20" s="5">
         <v>1</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J20" s="5"/>
       <c r="K20" s="5" t="s">
@@ -2181,29 +2181,29 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D21" s="5">
         <v>1</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J21" s="5"/>
       <c r="K21" s="5" t="s">
@@ -2216,27 +2216,27 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="5">
         <v>1</v>
       </c>
       <c r="E22" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>143</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>144</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J22" s="5"/>
       <c r="K22" s="5" t="s">
@@ -2244,39 +2244,39 @@
       </c>
       <c r="L22" s="5"/>
       <c r="M22" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N22" s="5"/>
       <c r="O22" s="5"/>
     </row>
     <row r="23" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5">
         <v>1</v>
       </c>
       <c r="E23" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="F23" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>148</v>
-      </c>
       <c r="H23" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K23" s="5" t="s">
         <v>32</v>
@@ -2288,29 +2288,29 @@
     </row>
     <row r="24" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D24" s="5">
         <v>1</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="5" t="s">
@@ -2318,38 +2318,38 @@
       </c>
       <c r="L24" s="5"/>
       <c r="M24" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N24" s="5"/>
       <c r="O24" s="5"/>
     </row>
     <row r="25" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D25" s="5">
         <v>2</v>
       </c>
       <c r="E25" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G25" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="F25" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>153</v>
-      </c>
       <c r="H25" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J25" s="5"/>
       <c r="K25" s="5" t="s">
@@ -2362,36 +2362,36 @@
     </row>
     <row r="26" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D26" s="5">
         <v>3</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J26" s="5"/>
       <c r="K26" s="5" t="s">
         <v>32</v>
       </c>
       <c r="L26" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M26" s="5"/>
       <c r="N26" s="5"/>
@@ -2399,27 +2399,27 @@
     </row>
     <row r="27" spans="1:15" ht="238" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5">
         <v>1</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="5" t="s">
@@ -2432,29 +2432,29 @@
     </row>
     <row r="28" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="5">
         <v>2</v>
       </c>
       <c r="E28" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G28" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="F28" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>162</v>
-      </c>
       <c r="H28" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J28" s="5"/>
       <c r="K28" s="5" t="s">
@@ -2467,34 +2467,34 @@
     </row>
     <row r="29" spans="1:15" ht="112" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5">
         <v>3</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J29" s="5"/>
       <c r="K29" s="5" t="s">
         <v>32</v>
       </c>
       <c r="L29" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
@@ -2502,36 +2502,36 @@
     </row>
     <row r="30" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5">
         <v>4</v>
       </c>
       <c r="E30" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="G30" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="F30" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>168</v>
-      </c>
       <c r="H30" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J30" s="5"/>
       <c r="K30" s="5" t="s">
         <v>32</v>
       </c>
       <c r="L30" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
@@ -2539,34 +2539,34 @@
     </row>
     <row r="31" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5">
         <v>5</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J31" s="5"/>
       <c r="K31" s="5" t="s">
         <v>32</v>
       </c>
       <c r="L31" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
@@ -2574,29 +2574,29 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5">
         <v>1</v>
       </c>
       <c r="E32" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G32" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="F32" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>173</v>
-      </c>
       <c r="H32" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J32" s="5"/>
       <c r="K32" s="5" t="s">
@@ -2609,27 +2609,27 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5">
         <v>2</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="5" t="s">
@@ -2642,27 +2642,27 @@
     </row>
     <row r="34" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="5">
         <v>3</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J34" s="5"/>
       <c r="K34" s="5" t="s">
@@ -2675,27 +2675,27 @@
     </row>
     <row r="35" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="5">
         <v>1</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J35" s="5"/>
       <c r="K35" s="5" t="s">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="L35" s="5"/>
       <c r="M35" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N35" s="5"/>
       <c r="O35" s="5"/>
@@ -2726,28 +2726,28 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>183</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>

--- a/structure.xlsx
+++ b/structure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sgr/GitHub/pac-submission-form/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DA63C45-9A0F-594A-973D-7D2A2E952DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46CEB753-241D-9645-88F7-E62834C8650D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="189">
   <si>
     <t>PAC Activity Submission Form — Structure Specification</t>
   </si>
@@ -598,6 +598,9 @@
 • &lt;b&gt;Routine or Supportive use&lt;/b&gt; covers things like brainstorming, wording suggestions, grammar/clarity checks, or formatting on work you conceived and directed.
 • &lt;b&gt;Substantive Developmental use&lt;/b&gt; means AI helped develop or revise real components — drafting objectives, generating questions from your objectives, building datasets, or suggesting scaffolding — requiring your careful review and verification.
 • &lt;b&gt;Extensive Generative use&lt;/b&gt; means AI generated substantial portions of the activity (e.g. a full question sequence or draft) with limited initial input from you.</t>
+  </si>
+  <si>
+    <t>Activity type and classroom context on new page</t>
   </si>
 </sst>
 </file>
@@ -2715,7 +2718,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -2750,6 +2753,17 @@
         <v>184</v>
       </c>
     </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>188</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/structure.xlsx
+++ b/structure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sgr/GitHub/pac-submission-form/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46CEB753-241D-9645-88F7-E62834C8650D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B4038F-0DC0-C542-9BBC-8F85817160D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="191">
   <si>
     <t>PAC Activity Submission Form — Structure Specification</t>
   </si>
@@ -339,36 +339,24 @@
     <t>activity_document</t>
   </si>
   <si>
-    <t>Activity</t>
-  </si>
-  <si>
     <t>yes:Activity</t>
   </si>
   <si>
     <t>toc_graphic</t>
   </si>
   <si>
-    <t>TOC Graphic</t>
-  </si>
-  <si>
     <t>yes:TOC Graphic</t>
   </si>
   <si>
     <t>answer_key</t>
   </si>
   <si>
-    <t>Student Answers (Key)</t>
-  </si>
-  <si>
     <t>yes:Student Answers (Key)</t>
   </si>
   <si>
     <t>facilitation_guide</t>
   </si>
   <si>
-    <t>Facilitation Guide</t>
-  </si>
-  <si>
     <t>yes:Facilitation Guide</t>
   </si>
   <si>
@@ -594,13 +582,31 @@
     <t>check_list</t>
   </si>
   <si>
+    <t>Activity type and classroom context on new page</t>
+  </si>
+  <si>
     <t>Generative AI can support activity development, but it should support — not replace — your own instructional design, disciplinary judgment, and critical thinking. As AI plays a larger role in producing content, the expectation for your review, verification, and disclosure increases. Select the level that best describes how AI was used in developing this activity.
-• &lt;b&gt;Routine or Supportive use&lt;/b&gt; covers things like brainstorming, wording suggestions, grammar/clarity checks, or formatting on work you conceived and directed.
-• &lt;b&gt;Substantive Developmental use&lt;/b&gt; means AI helped develop or revise real components — drafting objectives, generating questions from your objectives, building datasets, or suggesting scaffolding — requiring your careful review and verification.
-• &lt;b&gt;Extensive Generative use&lt;/b&gt; means AI generated substantial portions of the activity (e.g. a full question sequence or draft) with limited initial input from you.</t>
-  </si>
-  <si>
-    <t>Activity type and classroom context on new page</t>
+• ROUTINE or SUPPORTIVE use covers things like brainstorming, wording suggestions, grammar/clarity checks, or formatting on work you conceived and directed.
+• SUBSTANTIVE DEVELOPMENTAL use means AI helped develop or revise real components — drafting objectives, generating questions from your objectives, building datasets, or suggesting scaffolding — requiring your careful review and verification.
+• EXTENSIVE GENERATIVE use means AI generated substantial portions of the activity (e.g. a full question sequence or draft) with limited initial input from you.</t>
+  </si>
+  <si>
+    <t>check_list_intro</t>
+  </si>
+  <si>
+    <t>Activity (PDF)</t>
+  </si>
+  <si>
+    <t>TOC Graphic (PNG)</t>
+  </si>
+  <si>
+    <t>Student Answers / Key (PDF)</t>
+  </si>
+  <si>
+    <t>Facilitation Guide (PDF)</t>
+  </si>
+  <si>
+    <t>The following documents will be required during the upload. Requred documents are marked *. Ensure you have each required document in the indicated file format. (The submission form pdf and json are created by this web app when you click download.)</t>
   </si>
 </sst>
 </file>
@@ -1174,7 +1180,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B4" s="5">
         <v>12</v>
@@ -1436,7 +1442,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1616,28 +1622,26 @@
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" ht="70" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>95</v>
+        <v>185</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5">
         <v>1</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>96</v>
+        <v>190</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>97</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>85</v>
@@ -1653,23 +1657,23 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5">
         <v>2</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>92</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>84</v>
@@ -1686,35 +1690,33 @@
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
     </row>
-    <row r="7" spans="1:15" ht="42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5">
         <v>3</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>92</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="J7" s="5" t="s">
-        <v>45</v>
-      </c>
+      <c r="J7" s="5"/>
       <c r="K7" s="5" t="s">
         <v>32</v>
       </c>
@@ -1725,23 +1727,23 @@
     </row>
     <row r="8" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5">
         <v>4</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>92</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>85</v>
@@ -1762,23 +1764,23 @@
     </row>
     <row r="9" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5">
         <v>5</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>108</v>
+        <v>187</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>92</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>85</v>
@@ -1797,25 +1799,25 @@
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>
     </row>
-    <row r="10" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5">
         <v>6</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>111</v>
+        <v>188</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>92</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>85</v>
@@ -1824,7 +1826,7 @@
         <v>85</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>113</v>
+        <v>45</v>
       </c>
       <c r="K10" s="5" t="s">
         <v>32</v>
@@ -1834,33 +1836,35 @@
       <c r="N10" s="5"/>
       <c r="O10" s="5"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>60</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="C11" s="5"/>
       <c r="D11" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>115</v>
+        <v>189</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="G11" s="5"/>
+        <v>92</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>108</v>
+      </c>
       <c r="H11" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="J11" s="5"/>
+        <v>85</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>109</v>
+      </c>
       <c r="K11" s="5" t="s">
         <v>32</v>
       </c>
@@ -1871,7 +1875,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>30</v>
@@ -1880,13 +1884,13 @@
         <v>60</v>
       </c>
       <c r="D12" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
@@ -1906,7 +1910,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>30</v>
@@ -1915,20 +1919,20 @@
         <v>60</v>
       </c>
       <c r="D13" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J13" s="5"/>
       <c r="K13" s="5" t="s">
@@ -1939,28 +1943,28 @@
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
     </row>
-    <row r="14" spans="1:15" ht="70" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>60</v>
+      </c>
       <c r="D14" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>125</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>85</v>
@@ -1970,31 +1974,29 @@
         <v>32</v>
       </c>
       <c r="L14" s="5"/>
-      <c r="M14" s="5" t="s">
-        <v>185</v>
-      </c>
+      <c r="M14" s="5"/>
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
     </row>
-    <row r="15" spans="1:15" ht="140" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" ht="70" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>84</v>
@@ -2007,29 +2009,31 @@
         <v>32</v>
       </c>
       <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
+      <c r="M15" s="5" t="s">
+        <v>181</v>
+      </c>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" ht="140" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>84</v>
@@ -2048,22 +2052,24 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="G17" s="5"/>
+        <v>92</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>128</v>
+      </c>
       <c r="H17" s="5" t="s">
         <v>84</v>
       </c>
@@ -2079,26 +2085,24 @@
       <c r="N17" s="5"/>
       <c r="O17" s="5"/>
     </row>
-    <row r="18" spans="1:15" ht="42" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>137</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
         <v>84</v>
       </c>
@@ -2114,24 +2118,26 @@
       <c r="N18" s="5"/>
       <c r="O18" s="5"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>28</v>
+        <v>131</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="G19" s="5"/>
+        <v>92</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>133</v>
+      </c>
       <c r="H19" s="5" t="s">
         <v>84</v>
       </c>
@@ -2149,29 +2155,27 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>139</v>
+        <v>28</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>67</v>
-      </c>
+      <c r="C20" s="5"/>
       <c r="D20" s="5">
         <v>1</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>68</v>
+        <v>134</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5" t="s">
         <v>84</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J20" s="5"/>
       <c r="K20" s="5" t="s">
@@ -2184,22 +2188,22 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>36</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D21" s="5">
         <v>1</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5" t="s">
@@ -2219,116 +2223,114 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" s="5"/>
+        <v>36</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="D22" s="5">
         <v>1</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>142</v>
+        <v>71</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5" t="s">
         <v>84</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J22" s="5"/>
       <c r="K22" s="5" t="s">
         <v>32</v>
       </c>
       <c r="L22" s="5"/>
-      <c r="M22" s="5" t="s">
-        <v>144</v>
-      </c>
+      <c r="M22" s="5"/>
       <c r="N22" s="5"/>
       <c r="O22" s="5"/>
     </row>
-    <row r="23" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5">
         <v>1</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>147</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="J23" s="5" t="s">
-        <v>48</v>
-      </c>
+      <c r="J23" s="5"/>
       <c r="K23" s="5" t="s">
         <v>32</v>
       </c>
       <c r="L23" s="5"/>
-      <c r="M23" s="5"/>
+      <c r="M23" s="5" t="s">
+        <v>140</v>
+      </c>
       <c r="N23" s="5"/>
       <c r="O23" s="5"/>
     </row>
     <row r="24" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>63</v>
-      </c>
+      <c r="C24" s="5"/>
       <c r="D24" s="5">
         <v>1</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>64</v>
+        <v>142</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="G24" s="5"/>
+        <v>82</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>143</v>
+      </c>
       <c r="H24" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I24" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="J24" s="5"/>
+      <c r="J24" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="K24" s="5" t="s">
         <v>32</v>
       </c>
       <c r="L24" s="5"/>
-      <c r="M24" s="5" t="s">
-        <v>149</v>
-      </c>
+      <c r="M24" s="5"/>
       <c r="N24" s="5"/>
       <c r="O24" s="5"/>
     </row>
     <row r="25" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>49</v>
@@ -2337,17 +2339,15 @@
         <v>63</v>
       </c>
       <c r="D25" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>152</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="G25" s="5"/>
       <c r="H25" s="5" t="s">
         <v>84</v>
       </c>
@@ -2359,13 +2359,15 @@
         <v>32</v>
       </c>
       <c r="L25" s="5"/>
-      <c r="M25" s="5"/>
+      <c r="M25" s="5" t="s">
+        <v>145</v>
+      </c>
       <c r="N25" s="5"/>
       <c r="O25" s="5"/>
     </row>
     <row r="26" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>49</v>
@@ -2374,17 +2376,19 @@
         <v>63</v>
       </c>
       <c r="D26" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="G26" s="5"/>
+        <v>82</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>148</v>
+      </c>
       <c r="H26" s="5" t="s">
-        <v>155</v>
+        <v>84</v>
       </c>
       <c r="I26" s="5" t="s">
         <v>85</v>
@@ -2393,33 +2397,33 @@
       <c r="K26" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="L26" s="5" t="s">
-        <v>156</v>
-      </c>
+      <c r="L26" s="5"/>
       <c r="M26" s="5"/>
       <c r="N26" s="5"/>
       <c r="O26" s="5"/>
     </row>
-    <row r="27" spans="1:15" ht="238" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C27" s="5"/>
+        <v>49</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="D27" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>158</v>
+        <v>112</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5" t="s">
-        <v>85</v>
+        <v>151</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>85</v>
@@ -2428,33 +2432,33 @@
       <c r="K27" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="L27" s="5"/>
+      <c r="L27" s="5" t="s">
+        <v>152</v>
+      </c>
       <c r="M27" s="5"/>
       <c r="N27" s="5"/>
       <c r="O27" s="5"/>
     </row>
-    <row r="28" spans="1:15" ht="42" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" ht="238" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>51</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>161</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="G28" s="5"/>
       <c r="H28" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I28" s="5" t="s">
         <v>85</v>
@@ -2468,26 +2472,28 @@
       <c r="N28" s="5"/>
       <c r="O28" s="5"/>
     </row>
-    <row r="29" spans="1:15" ht="112" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>51</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="G29" s="5"/>
+        <v>82</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>157</v>
+      </c>
       <c r="H29" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I29" s="5" t="s">
         <v>85</v>
@@ -2496,35 +2502,31 @@
       <c r="K29" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="L29" s="5" t="s">
-        <v>164</v>
-      </c>
+      <c r="L29" s="5"/>
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
       <c r="O29" s="5"/>
     </row>
-    <row r="30" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15" ht="112" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>51</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>167</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="G30" s="5"/>
       <c r="H30" s="5" t="s">
-        <v>155</v>
+        <v>85</v>
       </c>
       <c r="I30" s="5" t="s">
         <v>85</v>
@@ -2534,7 +2536,7 @@
         <v>32</v>
       </c>
       <c r="L30" s="5" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
@@ -2542,24 +2544,26 @@
     </row>
     <row r="31" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>51</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="G31" s="5"/>
+        <v>92</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>163</v>
+      </c>
       <c r="H31" s="5" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>85</v>
@@ -2569,34 +2573,32 @@
         <v>32</v>
       </c>
       <c r="L31" s="5" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
       <c r="O31" s="5"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>172</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="G32" s="5"/>
       <c r="H32" s="5" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="I32" s="5" t="s">
         <v>85</v>
@@ -2605,29 +2607,33 @@
       <c r="K32" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="L32" s="5"/>
+      <c r="L32" s="5" t="s">
+        <v>160</v>
+      </c>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
       <c r="O32" s="5"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="G33" s="5"/>
+        <v>82</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>168</v>
+      </c>
       <c r="H33" s="5" t="s">
         <v>84</v>
       </c>
@@ -2643,22 +2649,22 @@
       <c r="N33" s="5"/>
       <c r="O33" s="5"/>
     </row>
-    <row r="34" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5" t="s">
@@ -2676,22 +2682,22 @@
       <c r="N34" s="5"/>
       <c r="O34" s="5"/>
     </row>
-    <row r="35" spans="1:15" ht="42" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5" t="s">
@@ -2705,11 +2711,44 @@
         <v>32</v>
       </c>
       <c r="L35" s="5"/>
-      <c r="M35" s="5" t="s">
-        <v>179</v>
-      </c>
+      <c r="M35" s="5"/>
       <c r="N35" s="5"/>
       <c r="O35" s="5"/>
+    </row>
+    <row r="36" spans="1:15" ht="42" x14ac:dyDescent="0.2">
+      <c r="A36" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5">
+        <v>1</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2729,16 +2768,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -2750,18 +2789,18 @@
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B3" t="b">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>

--- a/structure.xlsx
+++ b/structure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sgr/GitHub/pac-submission-form/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B4038F-0DC0-C542-9BBC-8F85817160D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73AB113F-21B3-DF47-903B-CEE796055818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -339,27 +339,15 @@
     <t>activity_document</t>
   </si>
   <si>
-    <t>yes:Activity</t>
-  </si>
-  <si>
     <t>toc_graphic</t>
   </si>
   <si>
-    <t>yes:TOC Graphic</t>
-  </si>
-  <si>
     <t>answer_key</t>
   </si>
   <si>
-    <t>yes:Student Answers (Key)</t>
-  </si>
-  <si>
     <t>facilitation_guide</t>
   </si>
   <si>
-    <t>yes:Facilitation Guide</t>
-  </si>
-  <si>
     <t>activity_for_testing,approved_activity</t>
   </si>
   <si>
@@ -462,9 +450,6 @@
     <t>Image Authorship</t>
   </si>
   <si>
-    <t>blanket_author:I am the author of all images in the activity|specify:Specify image authorship</t>
-  </si>
-  <si>
     <t>image_description</t>
   </si>
   <si>
@@ -585,28 +570,44 @@
     <t>Activity type and classroom context on new page</t>
   </si>
   <si>
-    <t>Generative AI can support activity development, but it should support — not replace — your own instructional design, disciplinary judgment, and critical thinking. As AI plays a larger role in producing content, the expectation for your review, verification, and disclosure increases. Select the level that best describes how AI was used in developing this activity.
+    <t>check_list_intro</t>
+  </si>
+  <si>
+    <t>Activity (PDF)</t>
+  </si>
+  <si>
+    <t>TOC Graphic (PNG)</t>
+  </si>
+  <si>
+    <t>Student Answers / Key (PDF)</t>
+  </si>
+  <si>
+    <t>Facilitation Guide (PDF)</t>
+  </si>
+  <si>
+    <t>The following documents will be required during the upload. Requred documents are marked *. Ensure you have each required document in the indicated file format. (The submission form pdf and json are created by this web app when you click download.)</t>
+  </si>
+  <si>
+    <t>yes:Activity (PDF)</t>
+  </si>
+  <si>
+    <t>yes:TOC Graphic (PNG)</t>
+  </si>
+  <si>
+    <t>yes:Student Answers / Key (PDF)</t>
+  </si>
+  <si>
+    <t>yes:Facilitation Guide (PDF)</t>
+  </si>
+  <si>
+    <t>blanket_author:I am the author of all images in the activity|specify:Specify image authorship individually</t>
+  </si>
+  <si>
+    <t>Generative AI can support activity development, but it should support — not replace — your own instructional design, disciplinary judgment, and critical thinking. As AI plays a larger role in producing content, the expectation for your review, verification, and disclosure increases. Three levels of AI use are
 • ROUTINE or SUPPORTIVE use covers things like brainstorming, wording suggestions, grammar/clarity checks, or formatting on work you conceived and directed.
 • SUBSTANTIVE DEVELOPMENTAL use means AI helped develop or revise real components — drafting objectives, generating questions from your objectives, building datasets, or suggesting scaffolding — requiring your careful review and verification.
-• EXTENSIVE GENERATIVE use means AI generated substantial portions of the activity (e.g. a full question sequence or draft) with limited initial input from you.</t>
-  </si>
-  <si>
-    <t>check_list_intro</t>
-  </si>
-  <si>
-    <t>Activity (PDF)</t>
-  </si>
-  <si>
-    <t>TOC Graphic (PNG)</t>
-  </si>
-  <si>
-    <t>Student Answers / Key (PDF)</t>
-  </si>
-  <si>
-    <t>Facilitation Guide (PDF)</t>
-  </si>
-  <si>
-    <t>The following documents will be required during the upload. Requred documents are marked *. Ensure you have each required document in the indicated file format. (The submission form pdf and json are created by this web app when you click download.)</t>
+• EXTENSIVE GENERATIVE use means AI generated substantial portions of the activity (e.g. a full question sequence or draft) with limited initial input from you.
+ Select the level that best describes how AI was used in developing this activity.</t>
   </si>
 </sst>
 </file>
@@ -1180,7 +1181,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B4" s="5">
         <v>12</v>
@@ -1624,20 +1625,20 @@
     </row>
     <row r="5" spans="1:15" ht="70" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5">
         <v>1</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
@@ -1660,7 +1661,7 @@
         <v>95</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5">
@@ -1695,7 +1696,7 @@
         <v>98</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5">
@@ -1730,20 +1731,20 @@
         <v>101</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5">
         <v>4</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>92</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>102</v>
+        <v>185</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>85</v>
@@ -1764,23 +1765,23 @@
     </row>
     <row r="9" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5">
         <v>5</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>92</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>104</v>
+        <v>186</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>85</v>
@@ -1801,23 +1802,23 @@
     </row>
     <row r="10" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5">
         <v>6</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>92</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>106</v>
+        <v>187</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>85</v>
@@ -1838,23 +1839,23 @@
     </row>
     <row r="11" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5">
         <v>7</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>92</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>108</v>
+        <v>188</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>85</v>
@@ -1863,7 +1864,7 @@
         <v>85</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="K11" s="5" t="s">
         <v>32</v>
@@ -1875,7 +1876,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>30</v>
@@ -1887,10 +1888,10 @@
         <v>1</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
@@ -1910,7 +1911,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>30</v>
@@ -1922,10 +1923,10 @@
         <v>2</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
@@ -1945,7 +1946,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>30</v>
@@ -1957,10 +1958,10 @@
         <v>3</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
@@ -1980,7 +1981,7 @@
     </row>
     <row r="15" spans="1:15" ht="70" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>38</v>
@@ -1990,13 +1991,13 @@
         <v>1</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>92</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>84</v>
@@ -2010,14 +2011,14 @@
       </c>
       <c r="L15" s="5"/>
       <c r="M15" s="5" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
     </row>
     <row r="16" spans="1:15" ht="140" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>38</v>
@@ -2027,13 +2028,13 @@
         <v>3</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>84</v>
@@ -2052,7 +2053,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>38</v>
@@ -2062,13 +2063,13 @@
         <v>4</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>92</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>84</v>
@@ -2087,7 +2088,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>38</v>
@@ -2097,10 +2098,10 @@
         <v>5</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
@@ -2120,7 +2121,7 @@
     </row>
     <row r="19" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>38</v>
@@ -2130,13 +2131,13 @@
         <v>6</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>92</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>84</v>
@@ -2165,10 +2166,10 @@
         <v>1</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5" t="s">
@@ -2188,7 +2189,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>36</v>
@@ -2203,7 +2204,7 @@
         <v>68</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5" t="s">
@@ -2223,7 +2224,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>36</v>
@@ -2238,7 +2239,7 @@
         <v>71</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5" t="s">
@@ -2258,7 +2259,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>40</v>
@@ -2268,10 +2269,10 @@
         <v>1</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
@@ -2286,14 +2287,14 @@
       </c>
       <c r="L23" s="5"/>
       <c r="M23" s="5" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N23" s="5"/>
       <c r="O23" s="5"/>
     </row>
     <row r="24" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>49</v>
@@ -2303,13 +2304,13 @@
         <v>1</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>82</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>143</v>
+        <v>189</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>85</v>
@@ -2330,7 +2331,7 @@
     </row>
     <row r="25" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>49</v>
@@ -2345,7 +2346,7 @@
         <v>64</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5" t="s">
@@ -2360,14 +2361,14 @@
       </c>
       <c r="L25" s="5"/>
       <c r="M25" s="5" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="N25" s="5"/>
       <c r="O25" s="5"/>
     </row>
     <row r="26" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>49</v>
@@ -2379,13 +2380,13 @@
         <v>2</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>82</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>84</v>
@@ -2404,7 +2405,7 @@
     </row>
     <row r="27" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>49</v>
@@ -2416,14 +2417,14 @@
         <v>3</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>85</v>
@@ -2433,15 +2434,15 @@
         <v>32</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="M27" s="5"/>
       <c r="N27" s="5"/>
       <c r="O27" s="5"/>
     </row>
-    <row r="28" spans="1:15" ht="238" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" ht="319" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>51</v>
@@ -2451,10 +2452,10 @@
         <v>1</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5" t="s">
@@ -2474,7 +2475,7 @@
     </row>
     <row r="29" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>51</v>
@@ -2484,13 +2485,13 @@
         <v>2</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>82</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>84</v>
@@ -2509,7 +2510,7 @@
     </row>
     <row r="30" spans="1:15" ht="112" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>51</v>
@@ -2519,10 +2520,10 @@
         <v>3</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5" t="s">
@@ -2536,7 +2537,7 @@
         <v>32</v>
       </c>
       <c r="L30" s="5" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
@@ -2544,7 +2545,7 @@
     </row>
     <row r="31" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>51</v>
@@ -2554,16 +2555,16 @@
         <v>4</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>92</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>85</v>
@@ -2573,7 +2574,7 @@
         <v>32</v>
       </c>
       <c r="L31" s="5" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
@@ -2581,7 +2582,7 @@
     </row>
     <row r="32" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>51</v>
@@ -2591,14 +2592,14 @@
         <v>5</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="I32" s="5" t="s">
         <v>85</v>
@@ -2608,7 +2609,7 @@
         <v>32</v>
       </c>
       <c r="L32" s="5" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
@@ -2616,7 +2617,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>43</v>
@@ -2626,13 +2627,13 @@
         <v>1</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>82</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="H33" s="5" t="s">
         <v>84</v>
@@ -2651,7 +2652,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>43</v>
@@ -2661,10 +2662,10 @@
         <v>2</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5" t="s">
@@ -2684,7 +2685,7 @@
     </row>
     <row r="35" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>43</v>
@@ -2694,10 +2695,10 @@
         <v>3</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5" t="s">
@@ -2717,7 +2718,7 @@
     </row>
     <row r="36" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>46</v>
@@ -2727,10 +2728,10 @@
         <v>1</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5" t="s">
@@ -2745,7 +2746,7 @@
       </c>
       <c r="L36" s="5"/>
       <c r="M36" s="5" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="N36" s="5"/>
       <c r="O36" s="5"/>
@@ -2768,16 +2769,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -2789,18 +2790,18 @@
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B3" t="b">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>

--- a/structure.xlsx
+++ b/structure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sgr/GitHub/pac-submission-form/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73AB113F-21B3-DF47-903B-CEE796055818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7FCC85A-E731-3646-BF55-53D7DCD8854C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="184">
   <si>
     <t>PAC Activity Submission Form — Structure Specification</t>
   </si>
@@ -162,12 +162,6 @@
     <t>activity_idea</t>
   </si>
   <si>
-    <t>student_background</t>
-  </si>
-  <si>
-    <t>Student Background</t>
-  </si>
-  <si>
     <t>activity_for_review,activity_for_testing,approved_activity</t>
   </si>
   <si>
@@ -516,25 +510,7 @@
     <t>Briefly describe how AI was used in developing this activity.</t>
   </si>
   <si>
-    <t>q2</t>
-  </si>
-  <si>
-    <t>Have students used and/or reviewed this activity?</t>
-  </si>
-  <si>
-    <t>yes:Yes|no:No</t>
-  </si>
-  <si>
-    <t>q3a</t>
-  </si>
-  <si>
     <t>Key knowledge students should have as a prerequisite.</t>
-  </si>
-  <si>
-    <t>q3b</t>
-  </si>
-  <si>
-    <t>Knowledge students are not expected to have prior to activity.</t>
   </si>
   <si>
     <t>approval_testing_evidence</t>
@@ -608,6 +584,9 @@
 • SUBSTANTIVE DEVELOPMENTAL use means AI helped develop or revise real components — drafting objectives, generating questions from your objectives, building datasets, or suggesting scaffolding — requiring your careful review and verification.
 • EXTENSIVE GENERATIVE use means AI generated substantial portions of the activity (e.g. a full question sequence or draft) with limited initial input from you.
  Select the level that best describes how AI was used in developing this activity.</t>
+  </si>
+  <si>
+    <t>prerequisite_knowledge</t>
   </si>
 </sst>
 </file>
@@ -1128,7 +1107,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -1181,7 +1160,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="B4" s="5">
         <v>12</v>
@@ -1235,32 +1214,32 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="5">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="28" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="5">
+        <v>10</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>43</v>
-      </c>
-      <c r="B8" s="5">
-        <v>7</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="5">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="28" x14ac:dyDescent="0.2">
@@ -1268,27 +1247,13 @@
         <v>49</v>
       </c>
       <c r="B10" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>50</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="28" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" s="5">
-        <v>11</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1313,7 +1278,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>26</v>
@@ -1322,27 +1287,27 @@
         <v>27</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>30</v>
@@ -1351,48 +1316,48 @@
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E2" s="5">
         <v>1</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C3" s="5">
         <v>2</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E3" s="5">
         <v>0</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>36</v>
@@ -1401,21 +1366,21 @@
         <v>2</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E4" s="5">
         <v>1</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>36</v>
@@ -1424,14 +1389,14 @@
         <v>3</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
@@ -1443,7 +1408,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:O36"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1471,43 +1436,43 @@
         <v>26</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>77</v>
-      </c>
       <c r="J1" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M1" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="O1" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="42" x14ac:dyDescent="0.2">
@@ -1522,19 +1487,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>84</v>
-      </c>
       <c r="I2" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J2" s="5"/>
       <c r="K2" s="5" t="s">
@@ -1543,7 +1508,7 @@
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="O2" s="5"/>
     </row>
@@ -1559,19 +1524,19 @@
         <v>2</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F3" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>84</v>
-      </c>
       <c r="I3" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J3" s="5"/>
       <c r="K3" s="5" t="s">
@@ -1580,15 +1545,15 @@
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
       <c r="N3" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="70" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>33</v>
@@ -1598,19 +1563,19 @@
         <v>3</v>
       </c>
       <c r="E4" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>93</v>
-      </c>
       <c r="H4" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J4" s="5"/>
       <c r="K4" s="5" t="s">
@@ -1618,34 +1583,34 @@
       </c>
       <c r="L4" s="5"/>
       <c r="M4" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
     </row>
     <row r="5" spans="1:15" ht="70" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5">
         <v>1</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J5" s="5"/>
       <c r="K5" s="5" t="s">
@@ -1658,29 +1623,29 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5">
         <v>2</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J6" s="5"/>
       <c r="K6" s="5" t="s">
@@ -1693,29 +1658,29 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5">
         <v>3</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5" t="s">
@@ -1728,32 +1693,32 @@
     </row>
     <row r="8" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5">
         <v>4</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K8" s="5" t="s">
         <v>32</v>
@@ -1765,32 +1730,32 @@
     </row>
     <row r="9" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5">
         <v>5</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>32</v>
@@ -1802,32 +1767,32 @@
     </row>
     <row r="10" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5">
         <v>6</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K10" s="5" t="s">
         <v>32</v>
@@ -1839,32 +1804,32 @@
     </row>
     <row r="11" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5">
         <v>7</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K11" s="5" t="s">
         <v>32</v>
@@ -1876,29 +1841,29 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D12" s="5">
         <v>1</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J12" s="5"/>
       <c r="K12" s="5" t="s">
@@ -1911,29 +1876,29 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D13" s="5">
         <v>2</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J13" s="5"/>
       <c r="K13" s="5" t="s">
@@ -1946,29 +1911,29 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D14" s="5">
         <v>3</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5" t="s">
@@ -1981,7 +1946,7 @@
     </row>
     <row r="15" spans="1:15" ht="70" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>38</v>
@@ -1991,19 +1956,19 @@
         <v>1</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="5" t="s">
@@ -2011,14 +1976,14 @@
       </c>
       <c r="L15" s="5"/>
       <c r="M15" s="5" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
     </row>
     <row r="16" spans="1:15" ht="140" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>38</v>
@@ -2028,19 +1993,19 @@
         <v>3</v>
       </c>
       <c r="E16" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="F16" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>121</v>
-      </c>
       <c r="H16" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5" t="s">
@@ -2053,7 +2018,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>38</v>
@@ -2063,19 +2028,19 @@
         <v>4</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J17" s="5"/>
       <c r="K17" s="5" t="s">
@@ -2088,7 +2053,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>38</v>
@@ -2098,17 +2063,17 @@
         <v>5</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J18" s="5"/>
       <c r="K18" s="5" t="s">
@@ -2121,7 +2086,7 @@
     </row>
     <row r="19" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>38</v>
@@ -2131,19 +2096,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="5" t="s">
@@ -2166,17 +2131,17 @@
         <v>1</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J20" s="5"/>
       <c r="K20" s="5" t="s">
@@ -2189,29 +2154,27 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>131</v>
+        <v>183</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>67</v>
-      </c>
+      <c r="C21" s="5"/>
       <c r="D21" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>68</v>
+        <v>159</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J21" s="5"/>
       <c r="K21" s="5" t="s">
@@ -2224,29 +2187,29 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>36</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D22" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J22" s="5"/>
       <c r="K22" s="5" t="s">
@@ -2259,245 +2222,245 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="5"/>
+        <v>36</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>68</v>
+      </c>
       <c r="D23" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>134</v>
+        <v>69</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="J23" s="5"/>
       <c r="K23" s="5" t="s">
         <v>32</v>
       </c>
       <c r="L23" s="5"/>
-      <c r="M23" s="5" t="s">
-        <v>136</v>
-      </c>
+      <c r="M23" s="5"/>
       <c r="N23" s="5"/>
       <c r="O23" s="5"/>
     </row>
-    <row r="24" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="5">
         <v>1</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="F24" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>85</v>
-      </c>
       <c r="I24" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>48</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="J24" s="5"/>
       <c r="K24" s="5" t="s">
         <v>32</v>
       </c>
       <c r="L24" s="5"/>
-      <c r="M24" s="5"/>
+      <c r="M24" s="5" t="s">
+        <v>134</v>
+      </c>
       <c r="N24" s="5"/>
       <c r="O24" s="5"/>
     </row>
     <row r="25" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>63</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="C25" s="5"/>
       <c r="D25" s="5">
         <v>1</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>64</v>
+        <v>136</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="G25" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>181</v>
+      </c>
       <c r="H25" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="J25" s="5"/>
+        <v>83</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="K25" s="5" t="s">
         <v>32</v>
       </c>
       <c r="L25" s="5"/>
-      <c r="M25" s="5" t="s">
-        <v>140</v>
-      </c>
+      <c r="M25" s="5"/>
       <c r="N25" s="5"/>
       <c r="O25" s="5"/>
     </row>
     <row r="26" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D26" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>142</v>
+        <v>62</v>
       </c>
       <c r="F26" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>84</v>
-      </c>
       <c r="I26" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J26" s="5"/>
       <c r="K26" s="5" t="s">
         <v>32</v>
       </c>
       <c r="L26" s="5"/>
-      <c r="M26" s="5"/>
+      <c r="M26" s="5" t="s">
+        <v>138</v>
+      </c>
       <c r="N26" s="5"/>
       <c r="O26" s="5"/>
     </row>
     <row r="27" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D27" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="G27" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>141</v>
+      </c>
       <c r="H27" s="5" t="s">
-        <v>146</v>
+        <v>82</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="L27" s="5" t="s">
-        <v>147</v>
-      </c>
+      <c r="L27" s="5"/>
       <c r="M27" s="5"/>
       <c r="N27" s="5"/>
       <c r="O27" s="5"/>
     </row>
-    <row r="28" spans="1:15" ht="319" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C28" s="5"/>
+        <v>47</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>61</v>
+      </c>
       <c r="D28" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>190</v>
+        <v>143</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>149</v>
+        <v>106</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J28" s="5"/>
       <c r="K28" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="L28" s="5"/>
+      <c r="L28" s="5" t="s">
+        <v>145</v>
+      </c>
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
       <c r="O28" s="5"/>
     </row>
-    <row r="29" spans="1:15" ht="42" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" ht="319" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>152</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="G29" s="5"/>
       <c r="H29" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J29" s="5"/>
       <c r="K29" s="5" t="s">
@@ -2508,73 +2471,71 @@
       <c r="N29" s="5"/>
       <c r="O29" s="5"/>
     </row>
-    <row r="30" spans="1:15" ht="112" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="G30" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>150</v>
+      </c>
       <c r="H30" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J30" s="5"/>
       <c r="K30" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="L30" s="5" t="s">
-        <v>155</v>
-      </c>
+      <c r="L30" s="5"/>
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
       <c r="O30" s="5"/>
     </row>
-    <row r="31" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15" ht="112" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>158</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="G31" s="5"/>
       <c r="H31" s="5" t="s">
-        <v>146</v>
+        <v>83</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J31" s="5"/>
       <c r="K31" s="5" t="s">
         <v>32</v>
       </c>
       <c r="L31" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
@@ -2582,174 +2543,110 @@
     </row>
     <row r="32" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="G32" s="5"/>
+        <v>90</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>156</v>
+      </c>
       <c r="H32" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J32" s="5"/>
       <c r="K32" s="5" t="s">
         <v>32</v>
       </c>
       <c r="L32" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
       <c r="O32" s="5"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>163</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="G33" s="5"/>
       <c r="H33" s="5" t="s">
-        <v>84</v>
+        <v>144</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="L33" s="5"/>
+      <c r="L33" s="5" t="s">
+        <v>153</v>
+      </c>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
       <c r="O33" s="5"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J34" s="5"/>
       <c r="K34" s="5" t="s">
         <v>32</v>
       </c>
       <c r="L34" s="5"/>
-      <c r="M34" s="5"/>
+      <c r="M34" s="5" t="s">
+        <v>162</v>
+      </c>
       <c r="N34" s="5"/>
       <c r="O34" s="5"/>
-    </row>
-    <row r="35" spans="1:15" ht="28" x14ac:dyDescent="0.2">
-      <c r="A35" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5">
-        <v>3</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="I35" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="J35" s="5"/>
-      <c r="K35" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="L35" s="5"/>
-      <c r="M35" s="5"/>
-      <c r="N35" s="5"/>
-      <c r="O35" s="5"/>
-    </row>
-    <row r="36" spans="1:15" ht="42" x14ac:dyDescent="0.2">
-      <c r="A36" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5">
-        <v>1</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="I36" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="J36" s="5"/>
-      <c r="K36" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="L36" s="5"/>
-      <c r="M36" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="N36" s="5"/>
-      <c r="O36" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2769,39 +2666,39 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B3" t="b">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/structure.xlsx
+++ b/structure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sgr/GitHub/pac-submission-form/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7FCC85A-E731-3646-BF55-53D7DCD8854C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC07AB00-37A2-494A-86C9-309CF3C4864A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="182">
   <si>
     <t>PAC Activity Submission Form — Structure Specification</t>
   </si>
@@ -486,12 +486,6 @@
     <t>no_ai:No AI was used|routine:Routine or Supportive use|substantive:Substantive development use|extensive:Extensive generative AI use</t>
   </si>
   <si>
-    <t>ai_responsibility_statement</t>
-  </si>
-  <si>
-    <t>Author Responsibility Statement: By selecting this level, I affirm that I have critically reviewed, verified, and substantively revised any AI-assisted content in this activity. My own intellectual and creative contribution to this activity is substantial enough that I hold copyright in the final work, and I accept full responsibility for the accuracy, originality, instructional design, and POGIL alignment of the submitted activity.</t>
-  </si>
-  <si>
     <t>ai_use_level in [substantive,extensive]</t>
   </si>
   <si>
@@ -501,9 +495,6 @@
     <t>Affirmation</t>
   </si>
   <si>
-    <t>affirmed:I affirm the statement above.</t>
-  </si>
-  <si>
     <t>ai_use_description</t>
   </si>
   <si>
@@ -579,14 +570,17 @@
     <t>blanket_author:I am the author of all images in the activity|specify:Specify image authorship individually</t>
   </si>
   <si>
-    <t>Generative AI can support activity development, but it should support — not replace — your own instructional design, disciplinary judgment, and critical thinking. As AI plays a larger role in producing content, the expectation for your review, verification, and disclosure increases. Three levels of AI use are
+    <t>prerequisite_knowledge</t>
+  </si>
+  <si>
+    <t>Generative AI can support activity development, but it should support, not replace, your own instructional design, disciplinary judgment, and critical thinking. As AI plays a larger role in producing content, the expectation for your review, verification, and disclosure increases. Three levels of AI use are
 • ROUTINE or SUPPORTIVE use covers things like brainstorming, wording suggestions, grammar/clarity checks, or formatting on work you conceived and directed.
-• SUBSTANTIVE DEVELOPMENTAL use means AI helped develop or revise real components — drafting objectives, generating questions from your objectives, building datasets, or suggesting scaffolding — requiring your careful review and verification.
+• SUBSTANTIVE DEVELOPMENTAL use means AI helped develop or revise real components such as drafting objectives, generating questions from your objectives, building datasets, or suggesting scaffolding.
 • EXTENSIVE GENERATIVE use means AI generated substantial portions of the activity (e.g. a full question sequence or draft) with limited initial input from you.
  Select the level that best describes how AI was used in developing this activity.</t>
   </si>
   <si>
-    <t>prerequisite_knowledge</t>
+    <t>affirmed: I affirm that I have critically reviewed, verified, and substantively revised any AI-assisted content in this activity. My own intellectual and creative contribution to this activity is substantial enough that I hold copyright in the final work, and I accept full responsibility for the accuracy, originality, instructional design, and POGIL alignment of the submitted activity.</t>
   </si>
 </sst>
 </file>
@@ -1160,7 +1154,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B4" s="5">
         <v>12</v>
@@ -1408,7 +1402,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1590,17 +1584,17 @@
     </row>
     <row r="5" spans="1:15" ht="70" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5">
         <v>1</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>147</v>
@@ -1626,7 +1620,7 @@
         <v>93</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5">
@@ -1661,7 +1655,7 @@
         <v>96</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5">
@@ -1696,20 +1690,20 @@
         <v>99</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5">
         <v>4</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>90</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>83</v>
@@ -1733,20 +1727,20 @@
         <v>100</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5">
         <v>5</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>90</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>83</v>
@@ -1770,20 +1764,20 @@
         <v>101</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5">
         <v>6</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>90</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>83</v>
@@ -1807,20 +1801,20 @@
         <v>102</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5">
         <v>7</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>90</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>83</v>
@@ -1976,7 +1970,7 @@
       </c>
       <c r="L15" s="5"/>
       <c r="M15" s="5" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
@@ -2154,7 +2148,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>36</v>
@@ -2164,7 +2158,7 @@
         <v>2</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>133</v>
@@ -2308,7 +2302,7 @@
         <v>80</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>83</v>
@@ -2438,7 +2432,7 @@
       <c r="N28" s="5"/>
       <c r="O28" s="5"/>
     </row>
-    <row r="29" spans="1:15" ht="319" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" ht="306" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>146</v>
       </c>
@@ -2450,7 +2444,7 @@
         <v>1</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>147</v>
@@ -2506,9 +2500,9 @@
       <c r="N30" s="5"/>
       <c r="O30" s="5"/>
     </row>
-    <row r="31" spans="1:15" ht="112" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15" ht="84" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>49</v>
@@ -2518,14 +2512,16 @@
         <v>3</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="G31" s="5"/>
+        <v>90</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>181</v>
+      </c>
       <c r="H31" s="5" t="s">
-        <v>83</v>
+        <v>144</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>83</v>
@@ -2535,7 +2531,7 @@
         <v>32</v>
       </c>
       <c r="L31" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
@@ -2556,11 +2552,9 @@
         <v>155</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>156</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="G32" s="5"/>
       <c r="H32" s="5" t="s">
         <v>144</v>
       </c>
@@ -2572,22 +2566,22 @@
         <v>32</v>
       </c>
       <c r="L32" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
       <c r="O32" s="5"/>
     </row>
-    <row r="33" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>157</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>158</v>
@@ -2597,7 +2591,7 @@
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5" t="s">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="I33" s="5" t="s">
         <v>83</v>
@@ -2606,47 +2600,12 @@
       <c r="K33" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="L33" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="M33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="N33" s="5"/>
       <c r="O33" s="5"/>
-    </row>
-    <row r="34" spans="1:15" ht="42" x14ac:dyDescent="0.2">
-      <c r="A34" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5">
-        <v>1</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="I34" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="J34" s="5"/>
-      <c r="K34" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="L34" s="5"/>
-      <c r="M34" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="N34" s="5"/>
-      <c r="O34" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2666,28 +2625,28 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>163</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>82</v>
+      <c r="B2" t="b">
+        <v>1</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -2698,7 +2657,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/structure.xlsx
+++ b/structure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sgr/GitHub/pac-submission-form/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC07AB00-37A2-494A-86C9-309CF3C4864A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD9492D8-5148-2B46-A58A-035C1895B052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -580,7 +580,7 @@
  Select the level that best describes how AI was used in developing this activity.</t>
   </si>
   <si>
-    <t>affirmed: I affirm that I have critically reviewed, verified, and substantively revised any AI-assisted content in this activity. My own intellectual and creative contribution to this activity is substantial enough that I hold copyright in the final work, and I accept full responsibility for the accuracy, originality, instructional design, and POGIL alignment of the submitted activity.</t>
+    <t>affirmed: I have critically reviewed, verified, and substantively revised any AI-assisted content in this activity. My own intellectual and creative contribution to this activity is substantial enough that I hold copyright in the final work, and I accept full responsibility for the accuracy, originality, instructional design, and POGIL alignment of the submitted activity.</t>
   </si>
 </sst>
 </file>

--- a/structure.xlsx
+++ b/structure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sgr/GitHub/pac-submission-form/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD9492D8-5148-2B46-A58A-035C1895B052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{586F2353-4D6C-1B44-9C47-F024DECEA138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="183">
   <si>
     <t>PAC Activity Submission Form — Structure Specification</t>
   </si>
@@ -552,9 +552,6 @@
     <t>Facilitation Guide (PDF)</t>
   </si>
   <si>
-    <t>The following documents will be required during the upload. Requred documents are marked *. Ensure you have each required document in the indicated file format. (The submission form pdf and json are created by this web app when you click download.)</t>
-  </si>
-  <si>
     <t>yes:Activity (PDF)</t>
   </si>
   <si>
@@ -581,6 +578,12 @@
   </si>
   <si>
     <t>affirmed: I have critically reviewed, verified, and substantively revised any AI-assisted content in this activity. My own intellectual and creative contribution to this activity is substantial enough that I hold copyright in the final work, and I accept full responsibility for the accuracy, originality, instructional design, and POGIL alignment of the submitted activity.</t>
+  </si>
+  <si>
+    <t>Documents marked * will be required during the upload. Ensure you have each required document in the indicated file format. (The submission form pdf and json are created by this web app when you click download.)</t>
+  </si>
+  <si>
+    <t>The PAC supports activity writing across all stages. What is your estimate for the stage of your activity?</t>
   </si>
 </sst>
 </file>
@@ -1500,7 +1503,9 @@
         <v>32</v>
       </c>
       <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
+      <c r="M2" s="5" t="s">
+        <v>182</v>
+      </c>
       <c r="N2" s="5" t="s">
         <v>84</v>
       </c>
@@ -1582,7 +1587,7 @@
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
     </row>
-    <row r="5" spans="1:15" ht="70" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" ht="56" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>168</v>
       </c>
@@ -1594,7 +1599,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>147</v>
@@ -1703,7 +1708,7 @@
         <v>90</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>83</v>
@@ -1740,7 +1745,7 @@
         <v>90</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>83</v>
@@ -1777,7 +1782,7 @@
         <v>90</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>83</v>
@@ -1814,7 +1819,7 @@
         <v>90</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>83</v>
@@ -2148,7 +2153,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>36</v>
@@ -2302,7 +2307,7 @@
         <v>80</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>83</v>
@@ -2444,7 +2449,7 @@
         <v>1</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>147</v>
@@ -2518,7 +2523,7 @@
         <v>90</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>144</v>

--- a/structure.xlsx
+++ b/structure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sgr/GitHub/pac-submission-form/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{586F2353-4D6C-1B44-9C47-F024DECEA138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{875E7DAF-12FE-F64A-9B7C-37E42B7A870B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="186">
   <si>
     <t>PAC Activity Submission Form — Structure Specification</t>
   </si>
@@ -583,7 +583,19 @@
     <t>Documents marked * will be required during the upload. Ensure you have each required document in the indicated file format. (The submission form pdf and json are created by this web app when you click download.)</t>
   </si>
   <si>
-    <t>The PAC supports activity writing across all stages. What is your estimate for the stage of your activity?</t>
+    <t>submission_kind_intro</t>
+  </si>
+  <si>
+    <t>The PAC supports activity writing across all stages of development. What is your estimate for the stage of your activity?</t>
+  </si>
+  <si>
+    <t>review_kind_intro</t>
+  </si>
+  <si>
+    <t>The PAC offers several kinds of activity feedback.
+• TRADITIONAL REVIEW: Reviewers provide written feedback based on the appropriate rubric.
+• COLLABORATIVE ACTIVITY FEEDBACK: Authors meet virtually and share feedback with each other in a facilitated session.
+• CLASSROOM TESTING: Activities are sent to testers, who provide feedback based on their classroom experiences.</t>
   </si>
 </sst>
 </file>
@@ -656,7 +668,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -667,6 +679,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1405,7 +1422,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1473,27 +1490,25 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="42" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="5" t="s">
+      <c r="A2" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5">
+      <c r="C2" s="6"/>
+      <c r="D2" s="8">
         <v>1</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>79</v>
+        <v>183</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>81</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="G2" s="5"/>
       <c r="H2" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>83</v>
@@ -1502,18 +1517,14 @@
       <c r="K2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="O2" s="5"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>33</v>
@@ -1523,13 +1534,13 @@
         <v>2</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>80</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>82</v>
@@ -1542,17 +1553,14 @@
         <v>32</v>
       </c>
       <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
       <c r="N3" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="O3" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="70" x14ac:dyDescent="0.2">
+      <c r="O3" s="5"/>
+    </row>
+    <row r="4" spans="1:15" ht="154" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>88</v>
+        <v>184</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>33</v>
@@ -1562,14 +1570,12 @@
         <v>3</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>89</v>
+        <v>185</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>91</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
         <v>83</v>
       </c>
@@ -1581,32 +1587,31 @@
         <v>32</v>
       </c>
       <c r="L4" s="5"/>
-      <c r="M4" s="5" t="s">
-        <v>92</v>
-      </c>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
     </row>
-    <row r="5" spans="1:15" ht="56" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>168</v>
+        <v>24</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>166</v>
+        <v>33</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>181</v>
+        <v>85</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="G5" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>86</v>
+      </c>
       <c r="H5" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>83</v>
@@ -1617,31 +1622,35 @@
       </c>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N5" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="70" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>166</v>
+        <v>33</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>90</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>83</v>
@@ -1651,32 +1660,32 @@
         <v>32</v>
       </c>
       <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
+      <c r="M6" s="5" t="s">
+        <v>92</v>
+      </c>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" ht="56" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>96</v>
+        <v>168</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>166</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>97</v>
+        <v>181</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>98</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>83</v>
@@ -1690,35 +1699,33 @@
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
     </row>
-    <row r="8" spans="1:15" ht="42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>166</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>169</v>
+        <v>94</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>90</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>173</v>
+        <v>95</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="J8" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="J8" s="5"/>
       <c r="K8" s="5" t="s">
         <v>32</v>
       </c>
@@ -1727,35 +1734,33 @@
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
     </row>
-    <row r="9" spans="1:15" ht="42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>166</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>170</v>
+        <v>97</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>90</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="J9" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="J9" s="5"/>
       <c r="K9" s="5" t="s">
         <v>32</v>
       </c>
@@ -1766,23 +1771,23 @@
     </row>
     <row r="10" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>166</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>90</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>83</v>
@@ -1801,25 +1806,25 @@
       <c r="N10" s="5"/>
       <c r="O10" s="5"/>
     </row>
-    <row r="11" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>166</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>90</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>83</v>
@@ -1828,7 +1833,7 @@
         <v>83</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="K11" s="5" t="s">
         <v>32</v>
@@ -1838,33 +1843,35 @@
       <c r="N11" s="5"/>
       <c r="O11" s="5"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>58</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="C12" s="5"/>
       <c r="D12" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>105</v>
+        <v>171</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="G12" s="5"/>
+        <v>90</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>175</v>
+      </c>
       <c r="H12" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="J12" s="5"/>
+        <v>83</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>43</v>
+      </c>
       <c r="K12" s="5" t="s">
         <v>32</v>
       </c>
@@ -1873,33 +1880,35 @@
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>58</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="C13" s="5"/>
       <c r="D13" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>108</v>
+        <v>172</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="G13" s="5"/>
+        <v>90</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>176</v>
+      </c>
       <c r="H13" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="J13" s="5"/>
+        <v>83</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>103</v>
+      </c>
       <c r="K13" s="5" t="s">
         <v>32</v>
       </c>
@@ -1910,7 +1919,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>30</v>
@@ -1919,20 +1928,20 @@
         <v>58</v>
       </c>
       <c r="D14" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5" t="s">
@@ -1943,65 +1952,63 @@
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
     </row>
-    <row r="15" spans="1:15" ht="70" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="D15" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>115</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
         <v>82</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="5" t="s">
         <v>32</v>
       </c>
       <c r="L15" s="5"/>
-      <c r="M15" s="5" t="s">
-        <v>165</v>
-      </c>
+      <c r="M15" s="5"/>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
     </row>
-    <row r="16" spans="1:15" ht="140" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="D16" s="5">
         <v>3</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>119</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="G16" s="5"/>
       <c r="H16" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>83</v>
@@ -2015,25 +2022,25 @@
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" ht="70" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>90</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>82</v>
@@ -2046,28 +2053,32 @@
         <v>32</v>
       </c>
       <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
+      <c r="M17" s="5" t="s">
+        <v>165</v>
+      </c>
       <c r="N17" s="5"/>
       <c r="O17" s="5"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" ht="140" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="G18" s="5"/>
+        <v>118</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>119</v>
+      </c>
       <c r="H18" s="5" t="s">
         <v>82</v>
       </c>
@@ -2083,25 +2094,25 @@
       <c r="N18" s="5"/>
       <c r="O18" s="5"/>
     </row>
-    <row r="19" spans="1:15" ht="42" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>90</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>82</v>
@@ -2120,17 +2131,17 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>28</v>
+        <v>123</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>106</v>
@@ -2151,24 +2162,26 @@
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>178</v>
+        <v>125</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="G21" s="5"/>
+        <v>90</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>127</v>
+      </c>
       <c r="H21" s="5" t="s">
         <v>82</v>
       </c>
@@ -2186,19 +2199,17 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>65</v>
-      </c>
+      <c r="C22" s="5"/>
       <c r="D22" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>66</v>
+        <v>128</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>106</v>
@@ -2208,7 +2219,7 @@
         <v>82</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J22" s="5"/>
       <c r="K22" s="5" t="s">
@@ -2221,29 +2232,27 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>130</v>
+        <v>178</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>68</v>
-      </c>
+      <c r="C23" s="5"/>
       <c r="D23" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>69</v>
+        <v>156</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
         <v>82</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J23" s="5"/>
       <c r="K23" s="5" t="s">
@@ -2256,68 +2265,66 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="5"/>
+        <v>36</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>65</v>
+      </c>
       <c r="D24" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>132</v>
+        <v>66</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5" t="s">
         <v>82</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="5" t="s">
         <v>32</v>
       </c>
       <c r="L24" s="5"/>
-      <c r="M24" s="5" t="s">
-        <v>134</v>
-      </c>
+      <c r="M24" s="5"/>
       <c r="N24" s="5"/>
       <c r="O24" s="5"/>
     </row>
-    <row r="25" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" s="5"/>
+        <v>36</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>68</v>
+      </c>
       <c r="D25" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>136</v>
+        <v>69</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>177</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="G25" s="5"/>
       <c r="H25" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>46</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="J25" s="5"/>
       <c r="K25" s="5" t="s">
         <v>32</v>
       </c>
@@ -2326,24 +2333,22 @@
       <c r="N25" s="5"/>
       <c r="O25" s="5"/>
     </row>
-    <row r="26" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>61</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="C26" s="5"/>
       <c r="D26" s="5">
         <v>1</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>62</v>
+        <v>132</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5" t="s">
@@ -2358,40 +2363,40 @@
       </c>
       <c r="L26" s="5"/>
       <c r="M26" s="5" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="N26" s="5"/>
       <c r="O26" s="5"/>
     </row>
     <row r="27" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>61</v>
-      </c>
+      <c r="C27" s="5"/>
       <c r="D27" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>80</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>141</v>
+        <v>177</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="J27" s="5"/>
+      <c r="J27" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="K27" s="5" t="s">
         <v>32</v>
       </c>
@@ -2402,7 +2407,7 @@
     </row>
     <row r="28" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>47</v>
@@ -2411,17 +2416,17 @@
         <v>61</v>
       </c>
       <c r="D28" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>143</v>
+        <v>62</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>106</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5" t="s">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="I28" s="5" t="s">
         <v>83</v>
@@ -2430,33 +2435,37 @@
       <c r="K28" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="L28" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="M28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5" t="s">
+        <v>138</v>
+      </c>
       <c r="N28" s="5"/>
       <c r="O28" s="5"/>
     </row>
-    <row r="29" spans="1:15" ht="306" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C29" s="5"/>
+        <v>47</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>61</v>
+      </c>
       <c r="D29" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="G29" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>141</v>
+      </c>
       <c r="H29" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I29" s="5" t="s">
         <v>83</v>
@@ -2470,28 +2479,28 @@
       <c r="N29" s="5"/>
       <c r="O29" s="5"/>
     </row>
-    <row r="30" spans="1:15" ht="42" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" s="5"/>
+        <v>47</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>61</v>
+      </c>
       <c r="D30" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>150</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="G30" s="5"/>
       <c r="H30" s="5" t="s">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="I30" s="5" t="s">
         <v>83</v>
@@ -2500,33 +2509,33 @@
       <c r="K30" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="L30" s="5"/>
+      <c r="L30" s="5" t="s">
+        <v>145</v>
+      </c>
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
       <c r="O30" s="5"/>
     </row>
-    <row r="31" spans="1:15" ht="84" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15" ht="306" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>49</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>153</v>
+        <v>179</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>180</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="G31" s="5"/>
       <c r="H31" s="5" t="s">
-        <v>144</v>
+        <v>83</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>83</v>
@@ -2535,33 +2544,33 @@
       <c r="K31" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="L31" s="5" t="s">
-        <v>151</v>
-      </c>
+      <c r="L31" s="5"/>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
       <c r="O31" s="5"/>
     </row>
-    <row r="32" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>49</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="G32" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>150</v>
+      </c>
       <c r="H32" s="5" t="s">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="I32" s="5" t="s">
         <v>83</v>
@@ -2570,33 +2579,33 @@
       <c r="K32" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="L32" s="5" t="s">
-        <v>151</v>
-      </c>
+      <c r="L32" s="5"/>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
       <c r="O32" s="5"/>
     </row>
-    <row r="33" spans="1:15" ht="42" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" ht="84" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="G33" s="5"/>
+        <v>90</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>180</v>
+      </c>
       <c r="H33" s="5" t="s">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="I33" s="5" t="s">
         <v>83</v>
@@ -2605,12 +2614,82 @@
       <c r="K33" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="L33" s="5"/>
-      <c r="M33" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="L33" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="M33" s="5"/>
       <c r="N33" s="5"/>
       <c r="O33" s="5"/>
+    </row>
+    <row r="34" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5">
+        <v>4</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="J34" s="5"/>
+      <c r="K34" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L34" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+    </row>
+    <row r="35" spans="1:15" ht="42" x14ac:dyDescent="0.2">
+      <c r="A35" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5">
+        <v>1</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/structure.xlsx
+++ b/structure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sgr/GitHub/pac-submission-form/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{875E7DAF-12FE-F64A-9B7C-37E42B7A870B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77C9803A-D6AD-CF4C-8B89-08C8D7F15F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="189">
   <si>
     <t>PAC Activity Submission Form — Structure Specification</t>
   </si>
@@ -596,6 +596,15 @@
 • TRADITIONAL REVIEW: Reviewers provide written feedback based on the appropriate rubric.
 • COLLABORATIVE ACTIVITY FEEDBACK: Authors meet virtually and share feedback with each other in a facilitated session.
 • CLASSROOM TESTING: Activities are sent to testers, who provide feedback based on their classroom experiences.</t>
+  </si>
+  <si>
+    <t>Kind of Feedback</t>
+  </si>
+  <si>
+    <t>kind_of_feedback</t>
+  </si>
+  <si>
+    <t>posting_goal_intro</t>
   </si>
 </sst>
 </file>
@@ -1121,7 +1130,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -1172,43 +1181,43 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B4" s="5">
-        <v>12</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>35</v>
+    <row r="4" spans="1:4" ht="28" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>186</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="5">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="28" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5">
         <v>4</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>37</v>
+      <c r="C5" t="s">
+        <v>89</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B6" s="5">
         <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>32</v>
@@ -1216,58 +1225,86 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B7" s="5">
         <v>6</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="5">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="28" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="5">
-        <v>10</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="28" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="28" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="5">
+        <v>10</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1422,7 +1459,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1562,12 +1599,12 @@
       <c r="A4" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>33</v>
+      <c r="B4" t="s">
+        <v>187</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>185</v>
@@ -1594,12 +1631,12 @@
       <c r="A5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>33</v>
+      <c r="B5" t="s">
+        <v>187</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>85</v>
@@ -1629,26 +1666,24 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="70" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" ht="56" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>33</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>91</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
         <v>83</v>
       </c>
@@ -1660,30 +1695,30 @@
         <v>32</v>
       </c>
       <c r="L6" s="5"/>
-      <c r="M6" s="5" t="s">
-        <v>92</v>
-      </c>
+      <c r="M6" s="5"/>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
     </row>
-    <row r="7" spans="1:15" ht="56" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>166</v>
+        <v>88</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>181</v>
+        <v>89</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="G7" s="5"/>
+        <v>90</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="H7" s="5" t="s">
         <v>83</v>
       </c>
@@ -1695,32 +1730,29 @@
         <v>32</v>
       </c>
       <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" ht="56" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>93</v>
+        <v>168</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>166</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>94</v>
+        <v>181</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>95</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>83</v>
@@ -1736,23 +1768,23 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>166</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>90</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>82</v>
@@ -1769,35 +1801,33 @@
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>
     </row>
-    <row r="10" spans="1:15" ht="42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>166</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>169</v>
+        <v>97</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>90</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>173</v>
+        <v>98</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="J10" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="J10" s="5"/>
       <c r="K10" s="5" t="s">
         <v>32</v>
       </c>
@@ -1808,23 +1838,23 @@
     </row>
     <row r="11" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>166</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>90</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>83</v>
@@ -1845,23 +1875,23 @@
     </row>
     <row r="12" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>166</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>90</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>83</v>
@@ -1880,25 +1910,25 @@
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
     </row>
-    <row r="13" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>166</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>90</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>83</v>
@@ -1907,7 +1937,7 @@
         <v>83</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="K13" s="5" t="s">
         <v>32</v>
@@ -1917,33 +1947,35 @@
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>58</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="C14" s="5"/>
       <c r="D14" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="G14" s="5"/>
+        <v>90</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>176</v>
+      </c>
       <c r="H14" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="J14" s="5"/>
+        <v>83</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>103</v>
+      </c>
       <c r="K14" s="5" t="s">
         <v>32</v>
       </c>
@@ -1954,7 +1986,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>30</v>
@@ -1963,13 +1995,13 @@
         <v>58</v>
       </c>
       <c r="D15" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
@@ -1989,7 +2021,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>30</v>
@@ -1998,20 +2030,20 @@
         <v>58</v>
       </c>
       <c r="D16" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5" t="s">
@@ -2022,28 +2054,28 @@
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
     </row>
-    <row r="17" spans="1:15" ht="70" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="D17" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>115</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>83</v>
@@ -2053,31 +2085,29 @@
         <v>32</v>
       </c>
       <c r="L17" s="5"/>
-      <c r="M17" s="5" t="s">
-        <v>165</v>
-      </c>
+      <c r="M17" s="5"/>
       <c r="N17" s="5"/>
       <c r="O17" s="5"/>
     </row>
-    <row r="18" spans="1:15" ht="140" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" ht="70" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>82</v>
@@ -2090,29 +2120,31 @@
         <v>32</v>
       </c>
       <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
+      <c r="M18" s="5" t="s">
+        <v>165</v>
+      </c>
       <c r="N18" s="5"/>
       <c r="O18" s="5"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" ht="140" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>82</v>
@@ -2131,22 +2163,24 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="G20" s="5"/>
+        <v>90</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>122</v>
+      </c>
       <c r="H20" s="5" t="s">
         <v>82</v>
       </c>
@@ -2162,26 +2196,24 @@
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
     </row>
-    <row r="21" spans="1:15" ht="42" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>127</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="G21" s="5"/>
       <c r="H21" s="5" t="s">
         <v>82</v>
       </c>
@@ -2197,24 +2229,26 @@
       <c r="N21" s="5"/>
       <c r="O21" s="5"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>28</v>
+        <v>125</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="G22" s="5"/>
+        <v>90</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>127</v>
+      </c>
       <c r="H22" s="5" t="s">
         <v>82</v>
       </c>
@@ -2232,20 +2266,20 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>178</v>
+        <v>28</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>36</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
@@ -2265,29 +2299,27 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>129</v>
+        <v>178</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>65</v>
-      </c>
+      <c r="C24" s="5"/>
       <c r="D24" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>66</v>
+        <v>156</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5" t="s">
         <v>82</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="5" t="s">
@@ -2300,19 +2332,19 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>36</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D25" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>106</v>
@@ -2335,116 +2367,114 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C26" s="5"/>
+        <v>36</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>68</v>
+      </c>
       <c r="D26" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>132</v>
+        <v>69</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5" t="s">
         <v>82</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J26" s="5"/>
       <c r="K26" s="5" t="s">
         <v>32</v>
       </c>
       <c r="L26" s="5"/>
-      <c r="M26" s="5" t="s">
-        <v>134</v>
-      </c>
+      <c r="M26" s="5"/>
       <c r="N26" s="5"/>
       <c r="O26" s="5"/>
     </row>
-    <row r="27" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5">
         <v>1</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>177</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="G27" s="5"/>
       <c r="H27" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="J27" s="5" t="s">
-        <v>46</v>
-      </c>
+      <c r="J27" s="5"/>
       <c r="K27" s="5" t="s">
         <v>32</v>
       </c>
       <c r="L27" s="5"/>
-      <c r="M27" s="5"/>
+      <c r="M27" s="5" t="s">
+        <v>134</v>
+      </c>
       <c r="N27" s="5"/>
       <c r="O27" s="5"/>
     </row>
     <row r="28" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>61</v>
-      </c>
+      <c r="C28" s="5"/>
       <c r="D28" s="5">
         <v>1</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="G28" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>177</v>
+      </c>
       <c r="H28" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I28" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="J28" s="5"/>
+      <c r="J28" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="K28" s="5" t="s">
         <v>32</v>
       </c>
       <c r="L28" s="5"/>
-      <c r="M28" s="5" t="s">
-        <v>138</v>
-      </c>
+      <c r="M28" s="5"/>
       <c r="N28" s="5"/>
       <c r="O28" s="5"/>
     </row>
     <row r="29" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>47</v>
@@ -2453,17 +2483,15 @@
         <v>61</v>
       </c>
       <c r="D29" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>140</v>
+        <v>62</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>141</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="G29" s="5"/>
       <c r="H29" s="5" t="s">
         <v>82</v>
       </c>
@@ -2475,13 +2503,15 @@
         <v>32</v>
       </c>
       <c r="L29" s="5"/>
-      <c r="M29" s="5"/>
+      <c r="M29" s="5" t="s">
+        <v>138</v>
+      </c>
       <c r="N29" s="5"/>
       <c r="O29" s="5"/>
     </row>
     <row r="30" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>47</v>
@@ -2490,17 +2520,19 @@
         <v>61</v>
       </c>
       <c r="D30" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="G30" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>141</v>
+      </c>
       <c r="H30" s="5" t="s">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="I30" s="5" t="s">
         <v>83</v>
@@ -2509,33 +2541,33 @@
       <c r="K30" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="L30" s="5" t="s">
-        <v>145</v>
-      </c>
+      <c r="L30" s="5"/>
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
       <c r="O30" s="5"/>
     </row>
-    <row r="31" spans="1:15" ht="306" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C31" s="5"/>
+        <v>47</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>61</v>
+      </c>
       <c r="D31" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>179</v>
+        <v>143</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5" t="s">
-        <v>83</v>
+        <v>144</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>83</v>
@@ -2544,33 +2576,33 @@
       <c r="K31" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="L31" s="5"/>
+      <c r="L31" s="5" t="s">
+        <v>145</v>
+      </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
       <c r="O31" s="5"/>
     </row>
-    <row r="32" spans="1:15" ht="42" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15" ht="306" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>49</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>150</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="G32" s="5"/>
       <c r="H32" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I32" s="5" t="s">
         <v>83</v>
@@ -2584,28 +2616,28 @@
       <c r="N32" s="5"/>
       <c r="O32" s="5"/>
     </row>
-    <row r="33" spans="1:15" ht="84" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>49</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="I33" s="5" t="s">
         <v>83</v>
@@ -2614,31 +2646,31 @@
       <c r="K33" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="L33" s="5" t="s">
-        <v>151</v>
-      </c>
+      <c r="L33" s="5"/>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
       <c r="O33" s="5"/>
     </row>
-    <row r="34" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" ht="84" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>49</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="G34" s="5"/>
+        <v>90</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>180</v>
+      </c>
       <c r="H34" s="5" t="s">
         <v>144</v>
       </c>
@@ -2656,26 +2688,26 @@
       <c r="N34" s="5"/>
       <c r="O34" s="5"/>
     </row>
-    <row r="35" spans="1:15" ht="42" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>133</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5" t="s">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="I35" s="5" t="s">
         <v>83</v>
@@ -2684,12 +2716,47 @@
       <c r="K35" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="L35" s="5"/>
-      <c r="M35" s="5" t="s">
-        <v>159</v>
-      </c>
+      <c r="L35" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="M35" s="5"/>
       <c r="N35" s="5"/>
       <c r="O35" s="5"/>
+    </row>
+    <row r="36" spans="1:15" ht="42" x14ac:dyDescent="0.2">
+      <c r="A36" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5">
+        <v>1</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/structure.xlsx
+++ b/structure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sgr/GitHub/pac-submission-form/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77C9803A-D6AD-CF4C-8B89-08C8D7F15F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6DE6A27-7BB7-AD4F-901C-ED563E25D17D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="190">
   <si>
     <t>PAC Activity Submission Form — Structure Specification</t>
   </si>
@@ -605,6 +605,9 @@
   </si>
   <si>
     <t>posting_goal_intro</t>
+  </si>
+  <si>
+    <t>posting_goal_choice</t>
   </si>
 </sst>
 </file>
@@ -1701,7 +1704,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>88</v>
+        <v>189</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>88</v>

--- a/structure.xlsx
+++ b/structure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sgr/GitHub/pac-submission-form/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6DE6A27-7BB7-AD4F-901C-ED563E25D17D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{799A54E4-6E53-E94E-AB71-44E1AB08ED95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="1" r:id="rId1"/>
@@ -435,9 +435,6 @@
     <t>textarea</t>
   </si>
   <si>
-    <t>250 words or less</t>
-  </si>
-  <si>
     <t>image_authorship_mode</t>
   </si>
   <si>
@@ -608,6 +605,9 @@
   </si>
   <si>
     <t>posting_goal_choice</t>
+  </si>
+  <si>
+    <t>500 words or less</t>
   </si>
 </sst>
 </file>
@@ -1186,13 +1186,13 @@
     </row>
     <row r="4" spans="1:4" ht="28" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>43</v>
@@ -1298,7 +1298,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B12">
         <v>11</v>
@@ -1531,7 +1531,7 @@
     </row>
     <row r="2" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>33</v>
@@ -1541,10 +1541,10 @@
         <v>1</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5" t="s">
@@ -1600,20 +1600,20 @@
     </row>
     <row r="4" spans="1:15" ht="154" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5">
         <v>1</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
@@ -1635,7 +1635,7 @@
         <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5">
@@ -1671,7 +1671,7 @@
     </row>
     <row r="6" spans="1:15" ht="56" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>88</v>
@@ -1684,7 +1684,7 @@
         <v>92</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
@@ -1704,7 +1704,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>88</v>
@@ -1738,20 +1738,20 @@
     </row>
     <row r="8" spans="1:15" ht="56" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5">
         <v>1</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
@@ -1774,7 +1774,7 @@
         <v>93</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5">
@@ -1809,7 +1809,7 @@
         <v>96</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5">
@@ -1844,20 +1844,20 @@
         <v>99</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5">
         <v>4</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>90</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>83</v>
@@ -1881,20 +1881,20 @@
         <v>100</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5">
         <v>5</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>90</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>83</v>
@@ -1918,20 +1918,20 @@
         <v>101</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5">
         <v>6</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>90</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>83</v>
@@ -1955,20 +1955,20 @@
         <v>102</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5">
         <v>7</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>90</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>83</v>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="L18" s="5"/>
       <c r="M18" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N18" s="5"/>
       <c r="O18" s="5"/>
@@ -2302,7 +2302,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>36</v>
@@ -2312,7 +2312,7 @@
         <v>2</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>133</v>
@@ -2433,14 +2433,14 @@
       </c>
       <c r="L27" s="5"/>
       <c r="M27" s="5" t="s">
-        <v>134</v>
+        <v>189</v>
       </c>
       <c r="N27" s="5"/>
       <c r="O27" s="5"/>
     </row>
     <row r="28" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>47</v>
@@ -2450,13 +2450,13 @@
         <v>1</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>80</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>83</v>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="29" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>47</v>
@@ -2507,14 +2507,14 @@
       </c>
       <c r="L29" s="5"/>
       <c r="M29" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="N29" s="5"/>
       <c r="O29" s="5"/>
     </row>
     <row r="30" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>47</v>
@@ -2526,13 +2526,13 @@
         <v>2</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>80</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>82</v>
@@ -2551,7 +2551,7 @@
     </row>
     <row r="31" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>47</v>
@@ -2563,14 +2563,14 @@
         <v>3</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>106</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>83</v>
@@ -2580,7 +2580,7 @@
         <v>32</v>
       </c>
       <c r="L31" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
@@ -2588,7 +2588,7 @@
     </row>
     <row r="32" spans="1:15" ht="306" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>49</v>
@@ -2598,10 +2598,10 @@
         <v>1</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5" t="s">
@@ -2621,7 +2621,7 @@
     </row>
     <row r="33" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>49</v>
@@ -2631,13 +2631,13 @@
         <v>2</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>80</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H33" s="5" t="s">
         <v>82</v>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="34" spans="1:15" ht="84" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>49</v>
@@ -2666,16 +2666,16 @@
         <v>3</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>90</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I34" s="5" t="s">
         <v>83</v>
@@ -2685,7 +2685,7 @@
         <v>32</v>
       </c>
       <c r="L34" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
@@ -2693,7 +2693,7 @@
     </row>
     <row r="35" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>49</v>
@@ -2703,14 +2703,14 @@
         <v>4</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>133</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I35" s="5" t="s">
         <v>83</v>
@@ -2720,7 +2720,7 @@
         <v>32</v>
       </c>
       <c r="L35" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
@@ -2728,7 +2728,7 @@
     </row>
     <row r="36" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>44</v>
@@ -2738,7 +2738,7 @@
         <v>1</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>133</v>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="L36" s="5"/>
       <c r="M36" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N36" s="5"/>
       <c r="O36" s="5"/>
@@ -2779,16 +2779,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>162</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -2811,7 +2811,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>

--- a/structure.xlsx
+++ b/structure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sgr/GitHub/pac-submission-form/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A755D121-4773-BF45-B10A-CF5018AAF84C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267675D8-2C51-4648-9347-190E30C61747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="191">
   <si>
     <t>field_id</t>
   </si>
@@ -608,6 +608,9 @@
   </si>
   <si>
     <t>Start of editorial content: submission kind</t>
+  </si>
+  <si>
+    <t>Break before Activity Type Info</t>
   </si>
 </sst>
 </file>
@@ -694,7 +697,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -708,6 +711,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2817,7 +2822,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -2842,18 +2847,30 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="B2" t="b">
         <v>1</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="9"/>
+      <c r="D2" s="10" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="5"/>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/structure.xlsx
+++ b/structure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sgr/GitHub/pac-submission-form/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B168C2-DD0D-064B-B4E0-4E33DE3C97DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B80E7C-7EF5-CA44-99AE-F75265730CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="201">
   <si>
     <t>field_id</t>
   </si>
@@ -76,6 +76,13 @@
   </si>
   <si>
     <t>submission_kind</t>
+  </si>
+  <si>
+    <t>The PAC supports activity writing across all stages of development. What is your estimate for the stage of your activity?
+• ACTIVITY IDEAS are ideas, intial drafts, rough activities. Authors are seeking collaborators to work on these ideas to develop activities.
+• ACTIVITIES FOR REVIEW are complete activities. Authors are seeking formative feedback to improve the quality of the activity. 
+• ACTIVITIES FOR TESTING are complete learning cycle or application activities that are ready for widespread classroom testing. Authors are seeking classroom testing feedback to optimize the activity.  
+• APPROVED ACTIVITIES are polished activities that have been revised based on classroom testing and meet the The POGIL Project's standards for a "high-quality activity."</t>
   </si>
   <si>
     <t>info</t>
@@ -252,6 +259,12 @@
     <t>tel</t>
   </si>
   <si>
+    <t>author_institution</t>
+  </si>
+  <si>
+    <t>Institution</t>
+  </si>
+  <si>
     <t>activity_type</t>
   </si>
   <si>
@@ -372,49 +385,46 @@
     <t>500 words or less</t>
   </si>
   <si>
-    <t>image_authorship_mode</t>
-  </si>
-  <si>
-    <t>image_source</t>
-  </si>
-  <si>
-    <t>Image Authorship</t>
-  </si>
-  <si>
-    <t>blanket_author:I am the author of all images in the activity|specify:Specify image authorship individually</t>
+    <t>copyright_authorship_mode</t>
+  </si>
+  <si>
+    <t>copyright_attribution</t>
+  </si>
+  <si>
+    <t>Copyrighted Materials</t>
+  </si>
+  <si>
+    <t>blanket_author:I am the sole author of all materials in this activity|specify:Specify authorship individually</t>
   </si>
   <si>
     <t>approved_activity</t>
   </si>
   <si>
-    <t>image_description</t>
-  </si>
-  <si>
-    <t>image_source_group</t>
-  </si>
-  <si>
-    <t>Image</t>
-  </si>
-  <si>
-    <t>A short description or filename identifying the image.</t>
-  </si>
-  <si>
-    <t>image_role</t>
-  </si>
-  <si>
-    <t>Image Credit</t>
-  </si>
-  <si>
-    <t>author:I am the author of this image|source:I am not the author of this image. Image source:</t>
-  </si>
-  <si>
-    <t>image_source_detail</t>
+    <t>item_description</t>
+  </si>
+  <si>
+    <t>copyright_item_group</t>
+  </si>
+  <si>
+    <t>Brief description or filename of the copyrighted material (e.g. Figure 3 from Smith 2020, or data_table.csv)</t>
+  </si>
+  <si>
+    <t>item_role</t>
+  </si>
+  <si>
+    <t>Authorship</t>
+  </si>
+  <si>
+    <t>author:I am the author of this material|source:I am not the author of this material. Source:</t>
+  </si>
+  <si>
+    <t>item_source_detail</t>
   </si>
   <si>
     <t>Source (URL or description)</t>
   </si>
   <si>
-    <t>image_role == 'source'</t>
+    <t>item_role == 'source'</t>
   </si>
   <si>
     <t>ai_use_intro</t>
@@ -571,7 +581,7 @@
     <t>Classroom Testing &amp; Revision</t>
   </si>
   <si>
-    <t>Image Source</t>
+    <t>Copyright &amp; Attribution</t>
   </si>
   <si>
     <t>Generative AI Use</t>
@@ -598,10 +608,13 @@
     <t>+ Add another author</t>
   </si>
   <si>
-    <t>+ Add image</t>
-  </si>
-  <si>
-    <t>image_authorship_mode == 'specify'</t>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>+ Add item</t>
+  </si>
+  <si>
+    <t>copyright_authorship_mode == 'specify'</t>
   </si>
   <si>
     <t>+ Add content objective</t>
@@ -628,17 +641,12 @@
     <t>Start of editorial content: submission kind</t>
   </si>
   <si>
-    <t>The PAC supports activity writing across all stages of development. What is your estimate for the stage of your activity?
-• ACTIVITY IDEAS are ideas, intial drafts, rough activities. Authors are seeking collaborators to work on these ideas to develop activities.
-• ACTIVITIES FOR REVIEW are complete activities. Authors are seeking formative feedback to improve the quality of the activity. 
-• ACTIVITIES FOR TESTING are complete learning cycle or application activities that are ready for widespread classroom testing. Authors are seeking classroom testing feedback to optimize the activity.  
-• APPROVED ACTIVITIES are polished activities that have been revised based on classroom testing and meet the The POGIL Project's standards for a "high-quality activity."</t>
-  </si>
-  <si>
-    <t>author_institution</t>
-  </si>
-  <si>
-    <t>Institution</t>
+    <t>copyright_intro</t>
+  </si>
+  <si>
+    <t>The standards for including copyrighted materials changes as activities move toward Approval. 
+• APPROVED ACTIVITIES: the author(s) should hold copyright on all materials OR specifically identify the origin of materials that would require a license. 
+• REVIEW and TESTING: Activities may use copyrighted materials with proper attribution under Fair Use.</t>
   </si>
 </sst>
 </file>
@@ -1051,95 +1059,95 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -1162,12 +1170,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1195,10 +1203,10 @@
         <v>3</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>10</v>
@@ -1206,7 +1214,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B2" s="5">
         <v>1</v>
@@ -1215,10 +1223,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -1232,15 +1240,15 @@
         <v>8</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -1249,15 +1257,15 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -1266,15 +1274,15 @@
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B6" s="5">
         <v>5</v>
@@ -1283,15 +1291,15 @@
         <v>2</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B7" s="5">
         <v>6</v>
@@ -1300,15 +1308,15 @@
         <v>3</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -1317,15 +1325,15 @@
         <v>4</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -1334,15 +1342,15 @@
         <v>5</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B10" s="5">
         <v>9</v>
@@ -1351,15 +1359,15 @@
         <v>6</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B11" s="5">
         <v>10</v>
@@ -1368,15 +1376,15 @@
         <v>7</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12">
         <v>11</v>
@@ -1385,10 +1393,10 @@
         <v>11</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1422,16 +1430,16 @@
         <v>3</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>9</v>
@@ -1442,96 +1450,96 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="C2" s="5">
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E2" s="5">
         <v>1</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="28" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C3" s="5">
         <v>2</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>121</v>
+        <v>188</v>
       </c>
       <c r="E3" s="5">
         <v>0</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C4" s="5">
         <v>2</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E4" s="5">
         <v>1</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C5" s="5">
         <v>3</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
@@ -1543,7 +1551,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1622,21 +1630,21 @@
         <v>1</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>196</v>
+        <v>17</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" s="5"/>
       <c r="K2" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
@@ -1645,7 +1653,7 @@
     </row>
     <row r="3" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>16</v>
@@ -1655,57 +1663,57 @@
         <v>2</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J3" s="5"/>
       <c r="K3" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L3" s="5"/>
       <c r="N3" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O3" s="5"/>
     </row>
     <row r="4" spans="1:15" ht="154" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5">
         <v>1</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J4" s="5"/>
       <c r="K4" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L4" s="5"/>
       <c r="N4" s="5"/>
@@ -1713,70 +1721,70 @@
     </row>
     <row r="5" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5">
         <v>2</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J5" s="5"/>
       <c r="K5" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="56" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5">
         <v>1</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J6" s="5"/>
       <c r="K6" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
@@ -1785,33 +1793,33 @@
     </row>
     <row r="7" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5">
         <v>2</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L7" s="5"/>
       <c r="N7" s="5"/>
@@ -1819,31 +1827,31 @@
     </row>
     <row r="8" spans="1:15" ht="56" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5">
         <v>1</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
@@ -1852,33 +1860,33 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5">
         <v>2</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
@@ -1887,33 +1895,33 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5">
         <v>3</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
@@ -1922,35 +1930,35 @@
     </row>
     <row r="11" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5">
         <v>4</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
@@ -1959,35 +1967,35 @@
     </row>
     <row r="12" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5">
         <v>5</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L12" s="5"/>
       <c r="M12" s="5"/>
@@ -1996,35 +2004,35 @@
     </row>
     <row r="13" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5">
         <v>6</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
@@ -2033,35 +2041,35 @@
     </row>
     <row r="14" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5">
         <v>7</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
@@ -2070,33 +2078,33 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D15" s="5">
         <v>1</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
@@ -2105,33 +2113,33 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D16" s="5">
         <v>2</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
@@ -2140,33 +2148,33 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D17" s="5">
         <v>3</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J17" s="5"/>
       <c r="K17" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
@@ -2175,33 +2183,33 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>197</v>
+        <v>75</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" s="5">
         <v>4</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>198</v>
+        <v>76</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J18" s="5"/>
       <c r="K18" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
@@ -2210,70 +2218,70 @@
     </row>
     <row r="19" spans="1:15" ht="70" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="5">
         <v>1</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L19" s="5"/>
       <c r="M19" s="5" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="N19" s="5"/>
       <c r="O19" s="5"/>
     </row>
     <row r="20" spans="1:15" ht="140" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5">
         <v>3</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J20" s="5"/>
       <c r="K20" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
@@ -2282,62 +2290,62 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D21">
         <v>3.5</v>
       </c>
       <c r="E21" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F21" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H21" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L21" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="5">
         <v>4</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J22" s="5"/>
       <c r="K22" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
@@ -2346,66 +2354,66 @@
     </row>
     <row r="23" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5">
         <v>5</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J23" s="5"/>
       <c r="K23" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
       <c r="O23" s="5"/>
     </row>
-    <row r="24" spans="1:15" ht="42" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="5">
         <v>6</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
@@ -2414,31 +2422,31 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="5">
         <v>1</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J25" s="5"/>
       <c r="K25" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L25" s="5"/>
       <c r="M25" s="5"/>
@@ -2447,31 +2455,31 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="5">
         <v>2</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J26" s="5"/>
       <c r="K26" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L26" s="5"/>
       <c r="M26" s="5"/>
@@ -2480,33 +2488,33 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D27" s="5">
         <v>3</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L27" s="5"/>
       <c r="M27" s="5"/>
@@ -2515,33 +2523,33 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D28" s="5">
         <v>4</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J28" s="5"/>
       <c r="K28" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L28" s="5"/>
       <c r="M28" s="5"/>
@@ -2550,106 +2558,94 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5">
         <v>5</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J29" s="5"/>
       <c r="K29" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L29" s="5"/>
       <c r="M29" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="N29" s="5"/>
       <c r="O29" s="5"/>
     </row>
     <row r="30" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5">
         <v>1</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J30" s="5"/>
       <c r="K30" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L30" s="5"/>
       <c r="M30" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="N30" s="5"/>
       <c r="O30" s="5"/>
     </row>
     <row r="31" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>114</v>
+        <v>199</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5">
         <v>1</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J31" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="K31" s="5" t="s">
-        <v>19</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
       <c r="L31" s="5"/>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
@@ -2657,289 +2653,326 @@
     </row>
     <row r="32" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5">
+        <v>2</v>
+      </c>
+      <c r="E32" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C32" s="5" t="s">
+      <c r="F32" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G32" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="D32" s="5">
-        <v>1</v>
-      </c>
-      <c r="E32" s="5" t="s">
+      <c r="H32" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J32" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="F32" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I32" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J32" s="5"/>
       <c r="K32" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L32" s="5"/>
-      <c r="M32" s="5" t="s">
-        <v>122</v>
-      </c>
+      <c r="M32" s="5"/>
       <c r="N32" s="5"/>
       <c r="O32" s="5"/>
     </row>
     <row r="33" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="D33" s="5">
+        <v>3</v>
+      </c>
+      <c r="E33" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D33" s="5">
-        <v>2</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>124</v>
-      </c>
       <c r="F33" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>125</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="G33" s="5"/>
       <c r="H33" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L33" s="5"/>
-      <c r="M33" s="5"/>
+      <c r="M33" s="5" t="s">
+        <v>124</v>
+      </c>
       <c r="N33" s="5"/>
       <c r="O33" s="5"/>
     </row>
-    <row r="34" spans="1:15" ht="306" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D34" s="5">
         <v>3</v>
       </c>
       <c r="E34" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G34" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="F34" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="G34" s="5"/>
       <c r="H34" s="5" t="s">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J34" s="5"/>
       <c r="K34" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="L34" s="5" t="s">
-        <v>128</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="L34" s="5"/>
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
       <c r="O34" s="5"/>
     </row>
-    <row r="35" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D35" s="5">
+        <v>4</v>
+      </c>
+      <c r="E35" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5">
-        <v>1</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>131</v>
-      </c>
       <c r="F35" s="5" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5" t="s">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J35" s="5"/>
       <c r="K35" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="L35" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="L35" s="5" t="s">
+        <v>130</v>
+      </c>
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
       <c r="O35" s="5"/>
     </row>
-    <row r="36" spans="1:15" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>132</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>130</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36" s="5" t="s">
         <v>133</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>134</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="G36" s="5"/>
       <c r="H36" s="5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J36" s="5"/>
       <c r="K36" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L36" s="5"/>
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
       <c r="O36" s="5"/>
     </row>
-    <row r="37" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G37" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="F37" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>137</v>
-      </c>
       <c r="H37" s="5" t="s">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J37" s="5"/>
       <c r="K37" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="L37" s="5" t="s">
-        <v>138</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="L37" s="5"/>
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
       <c r="O37" s="5"/>
     </row>
-    <row r="38" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="G38" s="5"/>
+        <v>45</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>139</v>
+      </c>
       <c r="H38" s="5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L38" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
       <c r="O38" s="5"/>
     </row>
-    <row r="39" spans="1:15" ht="42" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
         <v>141</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J39" s="5"/>
       <c r="K39" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="L39" s="5"/>
-      <c r="M39" s="5" t="s">
-        <v>144</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="L39" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="M39" s="5"/>
       <c r="N39" s="5"/>
       <c r="O39" s="5"/>
+    </row>
+    <row r="40" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5">
+        <v>1</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L40" s="5"/>
+      <c r="M40" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2959,40 +2992,40 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B2" t="b">
         <v>1</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="9" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" t="b">
         <v>1</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">

--- a/structure.xlsx
+++ b/structure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sgr/GitHub/pac-submission-form/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B80E7C-7EF5-CA44-99AE-F75265730CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E68D9FF8-5940-6844-9800-4BC90FB58F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="201">
   <si>
     <t>field_id</t>
   </si>
@@ -2640,12 +2640,20 @@
       <c r="E31" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="F31" s="5"/>
+      <c r="F31" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
+      <c r="H31" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
+      <c r="K31" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="L31" s="5"/>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>

--- a/structure.xlsx
+++ b/structure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sgr/GitHub/pac-submission-form/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E68D9FF8-5940-6844-9800-4BC90FB58F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D810C408-69FF-6944-97EA-1CFED998780F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1619,7 +1619,7 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="9" t="s">
         <v>15</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -1812,7 +1812,7 @@
         <v>39</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>19</v>

--- a/structure.xlsx
+++ b/structure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sgr/GitHub/pac-submission-form/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D810C408-69FF-6944-97EA-1CFED998780F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65942516-7468-B348-BA8C-C657054B94D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -78,13 +78,6 @@
     <t>submission_kind</t>
   </si>
   <si>
-    <t>The PAC supports activity writing across all stages of development. What is your estimate for the stage of your activity?
-• ACTIVITY IDEAS are ideas, intial drafts, rough activities. Authors are seeking collaborators to work on these ideas to develop activities.
-• ACTIVITIES FOR REVIEW are complete activities. Authors are seeking formative feedback to improve the quality of the activity. 
-• ACTIVITIES FOR TESTING are complete learning cycle or application activities that are ready for widespread classroom testing. Authors are seeking classroom testing feedback to optimize the activity.  
-• APPROVED ACTIVITIES are polished activities that have been revised based on classroom testing and meet the The POGIL Project's standards for a "high-quality activity."</t>
-  </si>
-  <si>
     <t>info</t>
   </si>
   <si>
@@ -118,12 +111,6 @@
     <t>kind_of_feedback</t>
   </si>
   <si>
-    <t>The PAC offers several kinds of activity feedback.
-• TRADITIONAL REVIEW: Reviewers provide written feedback based on the appropriate rubric.
-• COLLABORATIVE ACTIVITY FEEDBACK: Authors meet virtually and share feedback with each other in a facilitated session.
-• CLASSROOM TESTING: Activities are sent to testers, who provide feedback based on their classroom experiences.</t>
-  </si>
-  <si>
     <t>review_kind</t>
   </si>
   <si>
@@ -413,9 +400,6 @@
   </si>
   <si>
     <t>Authorship</t>
-  </si>
-  <si>
-    <t>author:I am the author of this material|source:I am not the author of this material. Source:</t>
   </si>
   <si>
     <t>item_source_detail</t>
@@ -647,6 +631,24 @@
     <t>The standards for including copyrighted materials changes as activities move toward Approval. 
 • APPROVED ACTIVITIES: the author(s) should hold copyright on all materials OR specifically identify the origin of materials that would require a license. 
 • REVIEW and TESTING: Activities may use copyrighted materials with proper attribution under Fair Use.</t>
+  </si>
+  <si>
+    <t>The PAC supports activity writing across all stages of development.
+• ACTIVITY IDEAS are ideas, initial drafts, rough activities. Authors are seeking collaborators to work on these ideas to develop activities.
+• ACTIVITIES FOR REVIEW are complete activities. Authors are seeking formative feedback to improve the quality of the activity. 
+• ACTIVITIES FOR TESTING are complete learning cycle or application activities that are ready for widespread classroom testing. Authors are seeking classroom testing feedback to optimize the activity.  
+• APPROVED ACTIVITIES are polished activities that have been revised based on classroom testing and meet the The POGIL Project's standards for a "high-quality activity."
+What is your estimate for the stage of your activity?</t>
+  </si>
+  <si>
+    <t>The PAC offers several kinds of activity feedback.
+• TRADITIONAL REVIEW: Reviewers provide written feedback based on the appropriate rubric.
+• COLLABORATIVE ACTIVITY FEEDBACK: Authors meet virtually and share feedback with each other in a facilitated session.
+• CLASSROOM TESTING: Activities are sent to testers, who provide feedback based on their classroom experiences.
+What kind of review would you like?</t>
+  </si>
+  <si>
+    <t>author:I am the author of this material|source:I am not the author of this material.</t>
   </si>
 </sst>
 </file>
@@ -1059,95 +1061,95 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -1170,12 +1172,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1203,10 +1205,10 @@
         <v>3</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>10</v>
@@ -1214,7 +1216,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B2" s="5">
         <v>1</v>
@@ -1223,10 +1225,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -1240,15 +1242,15 @@
         <v>8</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -1257,15 +1259,15 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -1274,15 +1276,15 @@
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B6" s="5">
         <v>5</v>
@@ -1291,15 +1293,15 @@
         <v>2</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B7" s="5">
         <v>6</v>
@@ -1308,15 +1310,15 @@
         <v>3</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -1325,15 +1327,15 @@
         <v>4</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -1342,15 +1344,15 @@
         <v>5</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B10" s="5">
         <v>9</v>
@@ -1359,15 +1361,15 @@
         <v>6</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B11" s="5">
         <v>10</v>
@@ -1376,15 +1378,15 @@
         <v>7</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B12">
         <v>11</v>
@@ -1393,10 +1395,10 @@
         <v>11</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1430,16 +1432,16 @@
         <v>3</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>182</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>185</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>9</v>
@@ -1450,96 +1452,96 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C2" s="5">
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E2" s="5">
         <v>1</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:9" ht="28" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C3" s="5">
         <v>2</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E3" s="5">
         <v>0</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C4" s="5">
         <v>2</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E4" s="5">
         <v>1</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C5" s="5">
         <v>3</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
@@ -1630,21 +1632,21 @@
         <v>1</v>
       </c>
       <c r="E2" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>17</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>18</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J2" s="5"/>
       <c r="K2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
@@ -1653,7 +1655,7 @@
     </row>
     <row r="3" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>16</v>
@@ -1663,57 +1665,57 @@
         <v>2</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>25</v>
-      </c>
       <c r="I3" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J3" s="5"/>
       <c r="K3" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L3" s="5"/>
       <c r="N3" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O3" s="5"/>
     </row>
     <row r="4" spans="1:15" ht="154" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
         <v>27</v>
-      </c>
-      <c r="B4" t="s">
-        <v>28</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5">
         <v>1</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>29</v>
+        <v>199</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J4" s="5"/>
       <c r="K4" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L4" s="5"/>
       <c r="N4" s="5"/>
@@ -1721,70 +1723,70 @@
     </row>
     <row r="5" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5">
         <v>2</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J5" s="5"/>
       <c r="K5" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="56" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5">
         <v>1</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J6" s="5"/>
       <c r="K6" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
@@ -1793,33 +1795,33 @@
     </row>
     <row r="7" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5">
         <v>2</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L7" s="5"/>
       <c r="N7" s="5"/>
@@ -1827,31 +1829,31 @@
     </row>
     <row r="8" spans="1:15" ht="56" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5">
         <v>1</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
@@ -1860,33 +1862,33 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5">
         <v>2</v>
       </c>
       <c r="E9" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>46</v>
-      </c>
       <c r="H9" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
@@ -1895,33 +1897,33 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5">
         <v>3</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
@@ -1930,35 +1932,35 @@
     </row>
     <row r="11" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5">
         <v>4</v>
       </c>
       <c r="E11" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>53</v>
-      </c>
       <c r="K11" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
@@ -1967,35 +1969,35 @@
     </row>
     <row r="12" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5">
         <v>5</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L12" s="5"/>
       <c r="M12" s="5"/>
@@ -2004,35 +2006,35 @@
     </row>
     <row r="13" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5">
         <v>6</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
@@ -2041,35 +2043,35 @@
     </row>
     <row r="14" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5">
         <v>7</v>
       </c>
       <c r="E14" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>63</v>
-      </c>
       <c r="K14" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
@@ -2078,33 +2080,33 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>66</v>
       </c>
       <c r="D15" s="5">
         <v>1</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
@@ -2113,33 +2115,33 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D16" s="5">
         <v>2</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
@@ -2148,33 +2150,33 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D17" s="5">
         <v>3</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J17" s="5"/>
       <c r="K17" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
@@ -2183,33 +2185,33 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D18" s="5">
         <v>4</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J18" s="5"/>
       <c r="K18" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
@@ -2218,70 +2220,70 @@
     </row>
     <row r="19" spans="1:15" ht="70" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="5">
         <v>1</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L19" s="5"/>
       <c r="M19" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="N19" s="5"/>
       <c r="O19" s="5"/>
     </row>
     <row r="20" spans="1:15" ht="140" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5">
         <v>3</v>
       </c>
       <c r="E20" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="F20" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>85</v>
-      </c>
       <c r="H20" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J20" s="5"/>
       <c r="K20" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
@@ -2290,62 +2292,62 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D21">
         <v>3.5</v>
       </c>
       <c r="E21" t="s">
+        <v>85</v>
+      </c>
+      <c r="F21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H21" t="s">
+        <v>86</v>
+      </c>
+      <c r="I21" t="s">
+        <v>18</v>
+      </c>
+      <c r="K21" t="s">
+        <v>19</v>
+      </c>
+      <c r="L21" t="s">
         <v>87</v>
-      </c>
-      <c r="F21" t="s">
-        <v>68</v>
-      </c>
-      <c r="H21" t="s">
-        <v>88</v>
-      </c>
-      <c r="I21" t="s">
-        <v>19</v>
-      </c>
-      <c r="K21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L21" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="5">
         <v>4</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J22" s="5"/>
       <c r="K22" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
@@ -2354,31 +2356,31 @@
     </row>
     <row r="23" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5">
         <v>5</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J23" s="5"/>
       <c r="K23" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
@@ -2387,33 +2389,33 @@
     </row>
     <row r="24" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="5">
         <v>6</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
@@ -2422,31 +2424,31 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="5">
         <v>1</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J25" s="5"/>
       <c r="K25" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L25" s="5"/>
       <c r="M25" s="5"/>
@@ -2455,31 +2457,31 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="5">
         <v>2</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J26" s="5"/>
       <c r="K26" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L26" s="5"/>
       <c r="M26" s="5"/>
@@ -2488,33 +2490,33 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D27" s="5">
         <v>3</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L27" s="5"/>
       <c r="M27" s="5"/>
@@ -2523,33 +2525,33 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D28" s="5">
         <v>4</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J28" s="5"/>
       <c r="K28" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L28" s="5"/>
       <c r="M28" s="5"/>
@@ -2558,101 +2560,101 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5">
         <v>5</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J29" s="5"/>
       <c r="K29" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L29" s="5"/>
       <c r="M29" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="N29" s="5"/>
       <c r="O29" s="5"/>
     </row>
     <row r="30" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5">
         <v>1</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J30" s="5"/>
       <c r="K30" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L30" s="5"/>
       <c r="M30" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="N30" s="5"/>
       <c r="O30" s="5"/>
     </row>
     <row r="31" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5">
         <v>1</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J31" s="5"/>
       <c r="K31" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L31" s="5"/>
       <c r="M31" s="5"/>
@@ -2661,35 +2663,35 @@
     </row>
     <row r="32" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5">
         <v>2</v>
       </c>
       <c r="E32" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J32" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="F32" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I32" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J32" s="5" t="s">
-        <v>121</v>
-      </c>
       <c r="K32" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L32" s="5"/>
       <c r="M32" s="5"/>
@@ -2698,72 +2700,72 @@
     </row>
     <row r="33" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D33" s="5">
         <v>3</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L33" s="5"/>
       <c r="M33" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="N33" s="5"/>
       <c r="O33" s="5"/>
     </row>
     <row r="34" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D34" s="5">
         <v>3</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>127</v>
+        <v>200</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J34" s="5"/>
       <c r="K34" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L34" s="5"/>
       <c r="M34" s="5"/>
@@ -2772,36 +2774,36 @@
     </row>
     <row r="35" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D35" s="5">
         <v>4</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J35" s="5"/>
       <c r="K35" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L35" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
@@ -2809,31 +2811,31 @@
     </row>
     <row r="36" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="5">
         <v>1</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J36" s="5"/>
       <c r="K36" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L36" s="5"/>
       <c r="M36" s="5"/>
@@ -2842,33 +2844,33 @@
     </row>
     <row r="37" spans="1:15" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="5">
         <v>2</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J37" s="5"/>
       <c r="K37" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L37" s="5"/>
       <c r="M37" s="5"/>
@@ -2877,36 +2879,36 @@
     </row>
     <row r="38" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="5">
         <v>3</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L38" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
@@ -2914,34 +2916,34 @@
     </row>
     <row r="39" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="5">
         <v>4</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J39" s="5"/>
       <c r="K39" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L39" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
@@ -2949,35 +2951,35 @@
     </row>
     <row r="40" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="5">
         <v>1</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J40" s="5"/>
       <c r="K40" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L40" s="5"/>
       <c r="M40" s="5" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="N40" s="5"/>
       <c r="O40" s="5"/>
@@ -3000,40 +3002,40 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>193</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B2" t="b">
         <v>1</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" t="b">
         <v>1</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">

--- a/structure.xlsx
+++ b/structure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sgr/GitHub/pac-submission-form/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65942516-7468-B348-BA8C-C657054B94D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4CD5A4C-A787-3849-A5F7-1C071DA1472F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="208">
   <si>
     <t>field_id</t>
   </si>
@@ -649,6 +649,27 @@
   </si>
   <si>
     <t>author:I am the author of this material|source:I am not the author of this material.</t>
+  </si>
+  <si>
+    <t>copyright_transfer</t>
+  </si>
+  <si>
+    <t>Copyright Transfer Acknowledgement</t>
+  </si>
+  <si>
+    <t>copyright_transfer_intro</t>
+  </si>
+  <si>
+    <t>Approval of an activity is accompanied by the transfer of copyright to The POGIL Project and minting of a doi making it permanently citable.</t>
+  </si>
+  <si>
+    <t>copyright_transfer_acknowledgement</t>
+  </si>
+  <si>
+    <t>acknowledged: I acknowledge that the copyright of an Approved Activity will be transferred to The POGIL Project.</t>
+  </si>
+  <si>
+    <t>Copyright Transfer</t>
   </si>
 </sst>
 </file>
@@ -1187,7 +1208,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -1389,16 +1410,33 @@
         <v>39</v>
       </c>
       <c r="B12">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>178</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="28" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="B13">
+        <v>11</v>
+      </c>
+      <c r="C13">
+        <v>11</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -1553,7 +1591,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -2984,6 +3022,65 @@
       <c r="N40" s="5"/>
       <c r="O40" s="5"/>
     </row>
+    <row r="41" spans="1:15" ht="42" x14ac:dyDescent="0.2">
+      <c r="A41" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="D41" s="5">
+        <v>1</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J41" s="5"/>
+      <c r="K41" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+      <c r="A42" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="D42" s="5">
+        <v>2</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="H42" t="b">
+        <v>0</v>
+      </c>
+      <c r="I42" t="b">
+        <v>0</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="K42" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/structure.xlsx
+++ b/structure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sgr/GitHub/pac-submission-form/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4CD5A4C-A787-3849-A5F7-1C071DA1472F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E57B6B-1734-3C40-BD12-91E8D1F75A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -147,9 +147,6 @@
     <t>check_list</t>
   </si>
   <si>
-    <t>Documents marked * will be required during the upload. Ensure you have each required document in the indicated file format. (The submission form pdf and json are created by this web app when you click download.)</t>
-  </si>
-  <si>
     <t>submission_form_pdf</t>
   </si>
   <si>
@@ -670,6 +667,9 @@
   </si>
   <si>
     <t>Copyright Transfer</t>
+  </si>
+  <si>
+    <t>The following checklist will help you identify the documents that you will need during the upload process. Documents marked * will be required during the upload. Ensure you have each required document in the indicated file format. (The submission form pdf and json are created by this web app when you click download.)</t>
   </si>
 </sst>
 </file>
@@ -1082,95 +1082,95 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>159</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>163</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>165</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -1226,10 +1226,10 @@
         <v>3</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>10</v>
@@ -1237,7 +1237,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B2" s="5">
         <v>1</v>
@@ -1246,7 +1246,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>19</v>
@@ -1263,7 +1263,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>19</v>
@@ -1280,10 +1280,10 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -1300,12 +1300,12 @@
         <v>36</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B6" s="5">
         <v>5</v>
@@ -1314,7 +1314,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>19</v>
@@ -1322,7 +1322,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B7" s="5">
         <v>6</v>
@@ -1331,7 +1331,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>19</v>
@@ -1339,7 +1339,7 @@
     </row>
     <row r="8" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -1348,15 +1348,15 @@
         <v>4</v>
       </c>
       <c r="D8" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>173</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -1365,15 +1365,15 @@
         <v>5</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B10" s="5">
         <v>9</v>
@@ -1382,15 +1382,15 @@
         <v>6</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B11" s="5">
         <v>10</v>
@@ -1399,10 +1399,10 @@
         <v>7</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -1416,7 +1416,7 @@
         <v>12</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>19</v>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="13" spans="1:5" ht="28" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B13">
         <v>11</v>
@@ -1433,10 +1433,10 @@
         <v>11</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -1470,16 +1470,16 @@
         <v>3</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>181</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>182</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>9</v>
@@ -1490,96 +1490,96 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C2" s="5">
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E2" s="5">
         <v>1</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:9" ht="28" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C3" s="5">
         <v>2</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E3" s="5">
         <v>0</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>186</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C4" s="5">
         <v>2</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E4" s="5">
         <v>1</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C5" s="5">
         <v>3</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
@@ -1670,7 +1670,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>17</v>
@@ -1739,7 +1739,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>17</v>
@@ -1877,7 +1877,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>40</v>
+        <v>207</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>17</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>39</v>
@@ -1910,13 +1910,13 @@
         <v>2</v>
       </c>
       <c r="E9" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="G9" s="5" t="s">
         <v>43</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>44</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>24</v>
@@ -1935,7 +1935,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>39</v>
@@ -1945,13 +1945,13 @@
         <v>3</v>
       </c>
       <c r="E10" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>46</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>47</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>24</v>
@@ -1970,7 +1970,7 @@
     </row>
     <row r="11" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>39</v>
@@ -1980,22 +1980,22 @@
         <v>4</v>
       </c>
       <c r="E11" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G11" s="5" t="s">
+      <c r="H11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" s="5" t="s">
         <v>50</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>51</v>
       </c>
       <c r="K11" s="5" t="s">
         <v>19</v>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="12" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>39</v>
@@ -2017,14 +2017,14 @@
         <v>5</v>
       </c>
       <c r="E12" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>54</v>
-      </c>
       <c r="H12" s="5" t="s">
         <v>18</v>
       </c>
@@ -2032,7 +2032,7 @@
         <v>18</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K12" s="5" t="s">
         <v>19</v>
@@ -2044,7 +2044,7 @@
     </row>
     <row r="13" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>39</v>
@@ -2054,14 +2054,14 @@
         <v>6</v>
       </c>
       <c r="E13" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="H13" s="5" t="s">
         <v>18</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>18</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K13" s="5" t="s">
         <v>19</v>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="14" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>39</v>
@@ -2091,22 +2091,22 @@
         <v>7</v>
       </c>
       <c r="E14" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G14" s="5" t="s">
+      <c r="H14" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>61</v>
       </c>
       <c r="K14" s="5" t="s">
         <v>19</v>
@@ -2118,22 +2118,22 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="D15" s="5">
         <v>1</v>
       </c>
       <c r="E15" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>66</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
@@ -2153,22 +2153,22 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B16" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="D16" s="5">
         <v>2</v>
       </c>
       <c r="E16" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5" t="s">
@@ -2188,22 +2188,22 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="D17" s="5">
         <v>3</v>
       </c>
       <c r="E17" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>71</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>72</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
@@ -2223,22 +2223,22 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B18" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="D18" s="5">
         <v>4</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
@@ -2258,23 +2258,23 @@
     </row>
     <row r="19" spans="1:15" ht="70" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>76</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="5">
         <v>1</v>
       </c>
       <c r="E19" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>77</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>78</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>24</v>
@@ -2288,30 +2288,30 @@
       </c>
       <c r="L19" s="5"/>
       <c r="M19" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N19" s="5"/>
       <c r="O19" s="5"/>
     </row>
     <row r="20" spans="1:15" ht="140" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5">
         <v>3</v>
       </c>
       <c r="E20" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F20" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="G20" s="5" t="s">
         <v>82</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>83</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>24</v>
@@ -2330,52 +2330,52 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21">
         <v>3.5</v>
       </c>
       <c r="E21" t="s">
+        <v>84</v>
+      </c>
+      <c r="F21" t="s">
+        <v>65</v>
+      </c>
+      <c r="H21" t="s">
         <v>85</v>
       </c>
-      <c r="F21" t="s">
-        <v>66</v>
-      </c>
-      <c r="H21" t="s">
+      <c r="I21" t="s">
+        <v>18</v>
+      </c>
+      <c r="K21" t="s">
+        <v>19</v>
+      </c>
+      <c r="L21" t="s">
         <v>86</v>
-      </c>
-      <c r="I21" t="s">
-        <v>18</v>
-      </c>
-      <c r="K21" t="s">
-        <v>19</v>
-      </c>
-      <c r="L21" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="5">
         <v>4</v>
       </c>
       <c r="E22" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>90</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>24</v>
@@ -2394,20 +2394,20 @@
     </row>
     <row r="23" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5">
         <v>5</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
@@ -2427,23 +2427,23 @@
     </row>
     <row r="24" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="5">
         <v>6</v>
       </c>
       <c r="E24" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>94</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>95</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>24</v>
@@ -2462,20 +2462,20 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B25" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="5">
         <v>1</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5" t="s">
@@ -2495,20 +2495,20 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="5">
         <v>2</v>
       </c>
       <c r="E26" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5" t="s">
@@ -2528,22 +2528,22 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>102</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>103</v>
       </c>
       <c r="D27" s="5">
         <v>3</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5" t="s">
@@ -2563,22 +2563,22 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>105</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>106</v>
       </c>
       <c r="D28" s="5">
         <v>4</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5" t="s">
@@ -2598,20 +2598,20 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5">
         <v>5</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5" t="s">
@@ -2626,27 +2626,27 @@
       </c>
       <c r="L29" s="5"/>
       <c r="M29" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N29" s="5"/>
       <c r="O29" s="5"/>
     </row>
     <row r="30" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>111</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>112</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5">
         <v>1</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5" t="s">
@@ -2661,24 +2661,24 @@
       </c>
       <c r="L30" s="5"/>
       <c r="M30" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N30" s="5"/>
       <c r="O30" s="5"/>
     </row>
     <row r="31" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5">
         <v>1</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>17</v>
@@ -2701,32 +2701,32 @@
     </row>
     <row r="32" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>115</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>116</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5">
         <v>2</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>22</v>
       </c>
       <c r="G32" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J32" s="5" t="s">
         <v>118</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I32" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J32" s="5" t="s">
-        <v>119</v>
       </c>
       <c r="K32" s="5" t="s">
         <v>19</v>
@@ -2738,22 +2738,22 @@
     </row>
     <row r="33" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>120</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>121</v>
       </c>
       <c r="D33" s="5">
         <v>3</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5" t="s">
@@ -2768,32 +2768,32 @@
       </c>
       <c r="L33" s="5"/>
       <c r="M33" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="N33" s="5"/>
       <c r="O33" s="5"/>
     </row>
     <row r="34" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D34" s="5">
         <v>3</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>22</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H34" s="5" t="s">
         <v>24</v>
@@ -2812,26 +2812,26 @@
     </row>
     <row r="35" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D35" s="5">
         <v>4</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I35" s="5" t="s">
         <v>18</v>
@@ -2841,7 +2841,7 @@
         <v>19</v>
       </c>
       <c r="L35" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
@@ -2849,17 +2849,17 @@
     </row>
     <row r="36" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>128</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>129</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="5">
         <v>1</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>17</v>
@@ -2882,23 +2882,23 @@
     </row>
     <row r="37" spans="1:15" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="5">
         <v>2</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>22</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H37" s="5" t="s">
         <v>24</v>
@@ -2917,26 +2917,26 @@
     </row>
     <row r="38" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="5">
         <v>3</v>
       </c>
       <c r="E38" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G38" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="F38" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>136</v>
-      </c>
       <c r="H38" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I38" s="5" t="s">
         <v>18</v>
@@ -2946,7 +2946,7 @@
         <v>19</v>
       </c>
       <c r="L38" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
@@ -2954,24 +2954,24 @@
     </row>
     <row r="39" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="5">
         <v>4</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I39" s="5" t="s">
         <v>18</v>
@@ -2981,7 +2981,7 @@
         <v>19</v>
       </c>
       <c r="L39" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
@@ -2989,20 +2989,20 @@
     </row>
     <row r="40" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B40" s="5" t="s">
         <v>140</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>141</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="5">
         <v>1</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5" t="s">
@@ -3017,23 +3017,23 @@
       </c>
       <c r="L40" s="5"/>
       <c r="M40" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N40" s="5"/>
       <c r="O40" s="5"/>
     </row>
     <row r="41" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D41" s="5">
         <v>1</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>17</v>
@@ -3051,22 +3051,22 @@
     </row>
     <row r="42" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D42" s="5">
         <v>2</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H42" t="b">
         <v>0</v>
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K42" s="5" t="s">
         <v>19</v>
@@ -3099,28 +3099,28 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>192</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B2" t="b">
         <v>1</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">

--- a/structure.xlsx
+++ b/structure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sgr/GitHub/pac-submission-form/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E57B6B-1734-3C40-BD12-91E8D1F75A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2190374E-33DB-5D41-B50E-40170DED4471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -273,9 +273,6 @@
     <t>select</t>
   </si>
   <si>
-    <t>anatomy_physiology:Anatomy &amp; Physiology|astronomy:Astronomy|biology:Biology|chemistry:Chemistry|computer_science:Computer Science|economics:Economics|environmental_science:Environmental Science|exercise_science:Exercise Science|fine_arts:Fine Arts|general:General|general_education:General Education|general_science:General Science|language_arts:Language Arts|mathematics:Mathematics|music:Music|neuroscience:Neuroscience|physics:Physics|psychology:Psychology|statistics:Statistics|other:Other</t>
-  </si>
-  <si>
     <t>discipline_other</t>
   </si>
   <si>
@@ -292,9 +289,6 @@
   </si>
   <si>
     <t>Setting</t>
-  </si>
-  <si>
-    <t>laboratory:Laboratory|classroom:Classroom</t>
   </si>
   <si>
     <t>course</t>
@@ -670,6 +664,12 @@
   </si>
   <si>
     <t>The following checklist will help you identify the documents that you will need during the upload process. Documents marked * will be required during the upload. Ensure you have each required document in the indicated file format. (The submission form pdf and json are created by this web app when you click download.)</t>
+  </si>
+  <si>
+    <t>classroom:Classroom|laboratory:Laboratory|workshop:Workshop</t>
+  </si>
+  <si>
+    <t>anatomy_physiology:Anatomy &amp; Physiology|astronomy:Astronomy|biology:Biology|chemistry:Chemistry|computer_science:Computer Science|economics:Economics|environmental_science:Environmental Science|exercise_science:Exercise  Science|fine_arts:Fine Arts|general:General|general_education:General Education|general_science:General Science|language_arts:Language Arts|mathematics:Mathematics|music:Music|neuroscience:Neuroscience|physics:Physics|professional_development:Professional Development|psychology:Psychology|statistics:Statistics|other:Other</t>
   </si>
 </sst>
 </file>
@@ -1082,95 +1082,95 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -1226,10 +1226,10 @@
         <v>3</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>10</v>
@@ -1246,7 +1246,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>19</v>
@@ -1263,7 +1263,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>19</v>
@@ -1280,7 +1280,7 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>50</v>
@@ -1305,7 +1305,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B6" s="5">
         <v>5</v>
@@ -1314,7 +1314,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>19</v>
@@ -1331,7 +1331,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>19</v>
@@ -1339,7 +1339,7 @@
     </row>
     <row r="8" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -1348,15 +1348,15 @@
         <v>4</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -1365,15 +1365,15 @@
         <v>5</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B10" s="5">
         <v>9</v>
@@ -1382,7 +1382,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>50</v>
@@ -1390,7 +1390,7 @@
     </row>
     <row r="11" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B11" s="5">
         <v>10</v>
@@ -1399,7 +1399,7 @@
         <v>7</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>50</v>
@@ -1416,7 +1416,7 @@
         <v>12</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>19</v>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="13" spans="1:5" ht="28" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B13">
         <v>11</v>
@@ -1433,10 +1433,10 @@
         <v>11</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -1470,16 +1470,16 @@
         <v>3</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>179</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>181</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>9</v>
@@ -1499,87 +1499,87 @@
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E2" s="5">
         <v>1</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:9" ht="28" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C3" s="5">
         <v>2</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E3" s="5">
         <v>0</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C4" s="5">
         <v>2</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E4" s="5">
         <v>1</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C5" s="5">
         <v>3</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
@@ -1670,7 +1670,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>17</v>
@@ -1739,7 +1739,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>17</v>
@@ -1877,7 +1877,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>17</v>
@@ -2311,7 +2311,7 @@
         <v>81</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>24</v>
@@ -2330,7 +2330,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B21" t="s">
         <v>75</v>
@@ -2339,27 +2339,27 @@
         <v>3.5</v>
       </c>
       <c r="E21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F21" t="s">
         <v>65</v>
       </c>
       <c r="H21" t="s">
+        <v>84</v>
+      </c>
+      <c r="I21" t="s">
+        <v>18</v>
+      </c>
+      <c r="K21" t="s">
+        <v>19</v>
+      </c>
+      <c r="L21" t="s">
         <v>85</v>
-      </c>
-      <c r="I21" t="s">
-        <v>18</v>
-      </c>
-      <c r="K21" t="s">
-        <v>19</v>
-      </c>
-      <c r="L21" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>75</v>
@@ -2369,13 +2369,13 @@
         <v>4</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>42</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>89</v>
+        <v>206</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>24</v>
@@ -2394,7 +2394,7 @@
     </row>
     <row r="23" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>75</v>
@@ -2404,7 +2404,7 @@
         <v>5</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>65</v>
@@ -2427,7 +2427,7 @@
     </row>
     <row r="24" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>75</v>
@@ -2437,13 +2437,13 @@
         <v>6</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>42</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>24</v>
@@ -2462,17 +2462,17 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="5">
         <v>1</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>65</v>
@@ -2495,20 +2495,20 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="5">
         <v>2</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5" t="s">
@@ -2528,19 +2528,19 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D27" s="5">
         <v>3</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>65</v>
@@ -2563,19 +2563,19 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D28" s="5">
         <v>4</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>65</v>
@@ -2598,17 +2598,17 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5">
         <v>5</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>65</v>
@@ -2626,27 +2626,27 @@
       </c>
       <c r="L29" s="5"/>
       <c r="M29" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="N29" s="5"/>
       <c r="O29" s="5"/>
     </row>
     <row r="30" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5">
         <v>1</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5" t="s">
@@ -2661,24 +2661,24 @@
       </c>
       <c r="L30" s="5"/>
       <c r="M30" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="N30" s="5"/>
       <c r="O30" s="5"/>
     </row>
     <row r="31" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5">
         <v>1</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>17</v>
@@ -2701,23 +2701,23 @@
     </row>
     <row r="32" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5">
         <v>2</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>22</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>18</v>
@@ -2726,7 +2726,7 @@
         <v>18</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="K32" s="5" t="s">
         <v>19</v>
@@ -2738,19 +2738,19 @@
     </row>
     <row r="33" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D33" s="5">
         <v>3</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>65</v>
@@ -2768,32 +2768,32 @@
       </c>
       <c r="L33" s="5"/>
       <c r="M33" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="N33" s="5"/>
       <c r="O33" s="5"/>
     </row>
     <row r="34" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D34" s="5">
         <v>3</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>22</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H34" s="5" t="s">
         <v>24</v>
@@ -2812,26 +2812,26 @@
     </row>
     <row r="35" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D35" s="5">
         <v>4</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>65</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I35" s="5" t="s">
         <v>18</v>
@@ -2841,7 +2841,7 @@
         <v>19</v>
       </c>
       <c r="L35" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
@@ -2849,17 +2849,17 @@
     </row>
     <row r="36" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="5">
         <v>1</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>17</v>
@@ -2882,23 +2882,23 @@
     </row>
     <row r="37" spans="1:15" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="5">
         <v>2</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>22</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H37" s="5" t="s">
         <v>24</v>
@@ -2917,26 +2917,26 @@
     </row>
     <row r="38" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="5">
         <v>3</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>42</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I38" s="5" t="s">
         <v>18</v>
@@ -2946,7 +2946,7 @@
         <v>19</v>
       </c>
       <c r="L38" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
@@ -2954,24 +2954,24 @@
     </row>
     <row r="39" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="5">
         <v>4</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I39" s="5" t="s">
         <v>18</v>
@@ -2981,7 +2981,7 @@
         <v>19</v>
       </c>
       <c r="L39" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
@@ -2989,20 +2989,20 @@
     </row>
     <row r="40" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="5">
         <v>1</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5" t="s">
@@ -3017,23 +3017,23 @@
       </c>
       <c r="L40" s="5"/>
       <c r="M40" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N40" s="5"/>
       <c r="O40" s="5"/>
     </row>
     <row r="41" spans="1:15" ht="42" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D41" s="5">
         <v>1</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>17</v>
@@ -3051,22 +3051,22 @@
     </row>
     <row r="42" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D42" s="5">
         <v>2</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>42</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H42" t="b">
         <v>0</v>
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="K42" s="5" t="s">
         <v>19</v>
@@ -3099,16 +3099,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>190</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
